--- a/assets/Items_for_Replenishment.xlsx
+++ b/assets/Items_for_Replenishment.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F6234B-44D5-4D94-94DE-AFD351EDCDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="5" name="Items" state="visible" r:id="rId4"/>
+    <sheet name="Items" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Items!$A$1:$B$1</definedName>
@@ -28,29 +29,29 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="0"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <charset val="238"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -62,7 +63,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -96,17 +97,17 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -410,6323 +411,6323 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C789"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B789"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>72760</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>74532</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
         <v>1344</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>76560</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>626</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>82379</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>84662</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>86979</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>968</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>87154</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>87813</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>506</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>87814</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>87844</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>87855</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>88478</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>88571</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>394</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>88810</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <v>658</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>90828</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="2">
         <v>310</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>90829</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="2">
         <v>540</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>90830</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="2">
         <v>4371</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>90831</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="2">
         <v>700</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>91015</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="2">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>91101</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>92425</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="2">
         <v>904</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>92688</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="2">
         <v>1118</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>92728</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="2">
         <v>910</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>92730</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="2">
         <v>1420</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>92731</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="2">
         <v>1310</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>93165</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="2">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>93286</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="2">
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>93307</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>93329</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="2">
         <v>2668</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>93332</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="2">
         <v>600</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>93333</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="2">
         <v>1906</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>94076</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="2">
         <v>2006</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>94319</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>94320</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="2">
         <v>940</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>94321</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="2">
         <v>270</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>94322</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="2">
         <v>1050</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>94425</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="2">
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>94916</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="2">
         <v>3956</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>94917</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="2">
         <v>3594</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>95947</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="2">
         <v>2724</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>96269</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>96893</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>96894</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>96901</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>96933</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>97517</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>97518</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>97525</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="2">
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>97526</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="2">
         <v>220</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>97527</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="2">
         <v>244</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>97528</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="2">
         <v>216</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>97529</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="2">
         <v>144</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>97530</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>97534</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>97538</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>97540</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>97543</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>97544</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>97545</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>97546</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>97547</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>97610</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>97612</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>97614</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>97617</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>97630</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>97631</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="2">
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>97632</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>97650</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>97668</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>97669</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>97676</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>97678</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>97680</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>97888</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>98211</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="2">
         <v>3050</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>98212</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="2">
         <v>2990</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>98213</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="2">
         <v>2990</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>98600</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="2">
         <v>550</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>98601</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="2">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>98602</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="2">
         <v>600</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>98657</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="2">
         <v>750</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>460</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>3764</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="2">
         <v>576</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>3775</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="2">
         <v>2262</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>3780</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>3786</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="2">
         <v>342</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>3798</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="2">
         <v>180</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>3809</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="2">
         <v>792</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>3817</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="2">
         <v>324</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>3821</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="2">
         <v>774</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>3827</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="2">
         <v>216</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>3833</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="2">
         <v>1656</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>36371</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="2">
         <v>2108</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>38326</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="2">
         <v>264</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>59296</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="2">
         <v>300</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>68947</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="2">
         <v>2256</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>68948</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="2">
         <v>528</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>68949</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="2">
         <v>816</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>68950</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="2">
         <v>528</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>68952</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="2">
         <v>552</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>68953</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="2">
         <v>576</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>68954</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="2">
         <v>528</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>68955</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="2">
         <v>816</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>68956</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="2">
         <v>528</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>68957</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="2">
         <v>528</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>68958</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="2">
         <v>852</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>68959</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="2">
         <v>576</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>68960</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="2">
         <v>576</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>70451</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="2">
         <v>3870</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>72604</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>73723</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="2">
         <v>1284</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>74359</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="2">
         <v>1278</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>83192</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="2">
         <v>144</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>97514</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>97515</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="2">
         <v>156</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>6881</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="2">
         <v>141</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>9858</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="2">
         <v>140</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>9859</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="2">
         <v>363</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>9963</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="2">
         <v>492</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>16075</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="2">
         <v>316</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>66614</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="2">
         <v>250</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>66615</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>66616</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="2">
         <v>143</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>68877</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="2">
         <v>102</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>68878</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="2">
         <v>315</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>68879</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="2">
         <v>450</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
         <v>68880</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="2">
         <v>316</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
         <v>80319</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
         <v>84851</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="2">
         <v>498</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
         <v>84852</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="2">
         <v>533</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>84853</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="2">
         <v>364</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
         <v>84854</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="2">
         <v>404</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
         <v>84855</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="2">
         <v>321</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
         <v>85743</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="2">
         <v>360</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
         <v>85744</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
         <v>86015</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="2">
         <v>270</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
         <v>86016</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
         <v>86265</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="2">
         <v>445</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
         <v>86266</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="2">
         <v>683</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
         <v>86267</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
         <v>86268</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="2">
         <v>541</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
         <v>86269</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="2">
         <v>252</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
         <v>86285</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="2">
         <v>363</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
         <v>86286</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="2">
         <v>776</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
         <v>86287</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="2">
         <v>802</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
         <v>86288</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="2">
         <v>578</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
         <v>86289</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="2">
         <v>321</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
         <v>87346</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="2">
         <v>307</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
         <v>87406</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
         <v>87408</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
         <v>87410</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
         <v>87416</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="2">
         <v>584</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
         <v>87417</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="2">
         <v>403</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
         <v>87418</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="2">
         <v>89</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
         <v>87419</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="2">
         <v>176</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
         <v>87420</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
         <v>87882</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="2">
         <v>748</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
         <v>87883</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="2">
         <v>518</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
         <v>87884</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="2">
         <v>170</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
         <v>87885</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="2">
         <v>198</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
         <v>87886</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="2">
         <v>207</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
         <v>87932</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="2">
         <v>963</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
         <v>87934</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="2">
         <v>707</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
         <v>87937</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="2">
         <v>657</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
         <v>87938</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="2">
         <v>864</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
         <v>87939</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="2">
         <v>513</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
         <v>87941</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="2">
         <v>113</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
         <v>88653</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="2">
         <v>479</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
         <v>88654</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171" s="2">
         <v>515</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
         <v>88655</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="2">
         <v>609</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
         <v>88656</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
         <v>88657</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="2">
         <v>124</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
         <v>89338</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
         <v>89339</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="2">
         <v>163</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
         <v>89982</v>
       </c>
-      <c r="B177" s="4">
+      <c r="B177" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
         <v>89983</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
         <v>89984</v>
       </c>
-      <c r="B179" s="4">
+      <c r="B179" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
         <v>89985</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
         <v>89986</v>
       </c>
-      <c r="B181" s="4">
+      <c r="B181" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
         <v>90566</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="2">
         <v>684</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
         <v>90567</v>
       </c>
-      <c r="B183" s="4">
+      <c r="B183" s="2">
         <v>185</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
         <v>90568</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="2">
         <v>480</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
         <v>90569</v>
       </c>
-      <c r="B185" s="4">
+      <c r="B185" s="2">
         <v>305</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
         <v>90570</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="2">
         <v>251</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
         <v>90789</v>
       </c>
-      <c r="B187" s="4">
+      <c r="B187" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
         <v>90790</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
         <v>90791</v>
       </c>
-      <c r="B189" s="4">
+      <c r="B189" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
         <v>90792</v>
       </c>
-      <c r="B190" s="4">
+      <c r="B190" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
         <v>90922</v>
       </c>
-      <c r="B191" s="4">
+      <c r="B191" s="2">
         <v>831</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
         <v>90923</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="2">
         <v>796</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
         <v>90924</v>
       </c>
-      <c r="B193" s="4">
+      <c r="B193" s="2">
         <v>381</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
         <v>90925</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="2">
         <v>304</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
         <v>90926</v>
       </c>
-      <c r="B195" s="4">
+      <c r="B195" s="2">
         <v>243</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
         <v>91206</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
         <v>91208</v>
       </c>
-      <c r="B197" s="4">
+      <c r="B197" s="2">
         <v>91</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
         <v>91209</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="2">
         <v>113</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
         <v>91279</v>
       </c>
-      <c r="B199" s="4">
+      <c r="B199" s="2">
         <v>654</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
         <v>91280</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="2">
         <v>747</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
         <v>91281</v>
       </c>
-      <c r="B201" s="4">
+      <c r="B201" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
         <v>91765</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="2">
         <v>791</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
         <v>91766</v>
       </c>
-      <c r="B203" s="4">
+      <c r="B203" s="2">
         <v>545</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
         <v>91768</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
         <v>91769</v>
       </c>
-      <c r="B205" s="4">
+      <c r="B205" s="2">
         <v>171</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
         <v>91815</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="2">
         <v>656</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
         <v>91816</v>
       </c>
-      <c r="B207" s="4">
+      <c r="B207" s="2">
         <v>1225</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
         <v>91817</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="2">
         <v>431</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
         <v>91818</v>
       </c>
-      <c r="B209" s="4">
+      <c r="B209" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
         <v>91819</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
         <v>91895</v>
       </c>
-      <c r="B211" s="4">
+      <c r="B211" s="2">
         <v>207</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
         <v>91896</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
         <v>92283</v>
       </c>
-      <c r="B213" s="4">
+      <c r="B213" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
         <v>92284</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="2">
         <v>102</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
         <v>92285</v>
       </c>
-      <c r="B215" s="4">
+      <c r="B215" s="2">
         <v>187</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
         <v>92288</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="2">
         <v>1156</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
         <v>92289</v>
       </c>
-      <c r="B217" s="4">
+      <c r="B217" s="2">
         <v>995</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
         <v>92290</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="2">
         <v>649</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
         <v>92291</v>
       </c>
-      <c r="B219" s="4">
+      <c r="B219" s="2">
         <v>484</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
         <v>92292</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="2">
         <v>240</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
         <v>92409</v>
       </c>
-      <c r="B221" s="4">
+      <c r="B221" s="2">
         <v>549</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
         <v>92410</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="2">
         <v>576</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
         <v>92411</v>
       </c>
-      <c r="B223" s="4">
+      <c r="B223" s="2">
         <v>438</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
         <v>92412</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="2">
         <v>559</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
         <v>92413</v>
       </c>
-      <c r="B225" s="4">
+      <c r="B225" s="2">
         <v>246</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
         <v>92542</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="2">
         <v>335</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
         <v>92543</v>
       </c>
-      <c r="B227" s="4">
+      <c r="B227" s="2">
         <v>203</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
         <v>92544</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="2">
         <v>58</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
         <v>92545</v>
       </c>
-      <c r="B229" s="4">
+      <c r="B229" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
         <v>92546</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="2">
         <v>58</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
         <v>92590</v>
       </c>
-      <c r="B231" s="4">
+      <c r="B231" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
         <v>92591</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
         <v>92592</v>
       </c>
-      <c r="B233" s="4">
+      <c r="B233" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
         <v>93238</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="2">
         <v>1529</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
         <v>93239</v>
       </c>
-      <c r="B235" s="4">
+      <c r="B235" s="2">
         <v>1227</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
         <v>93240</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="2">
         <v>847</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
         <v>93241</v>
       </c>
-      <c r="B237" s="4">
+      <c r="B237" s="2">
         <v>926</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
         <v>93242</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="2">
         <v>544</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
         <v>94139</v>
       </c>
-      <c r="B239" s="4">
+      <c r="B239" s="2">
         <v>1760</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
         <v>94140</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="2">
         <v>1942</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
         <v>94141</v>
       </c>
-      <c r="B241" s="4">
+      <c r="B241" s="2">
         <v>447</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
         <v>94142</v>
       </c>
-      <c r="B242" s="4">
+      <c r="B242" s="2">
         <v>781</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
         <v>94143</v>
       </c>
-      <c r="B243" s="4">
+      <c r="B243" s="2">
         <v>57</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
         <v>94592</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="2">
         <v>776</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
         <v>94593</v>
       </c>
-      <c r="B245" s="4">
+      <c r="B245" s="2">
         <v>680</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
         <v>94594</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="2">
         <v>548</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
         <v>94595</v>
       </c>
-      <c r="B247" s="4">
+      <c r="B247" s="2">
         <v>402</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
         <v>94596</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="2">
         <v>226</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
         <v>95082</v>
       </c>
-      <c r="B249" s="4">
+      <c r="B249" s="2">
         <v>925</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
         <v>95083</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="2">
         <v>790</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
         <v>95084</v>
       </c>
-      <c r="B251" s="4">
+      <c r="B251" s="2">
         <v>480</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
         <v>95085</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="2">
         <v>344</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
         <v>95086</v>
       </c>
-      <c r="B253" s="4">
+      <c r="B253" s="2">
         <v>315</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
         <v>95973</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
         <v>95976</v>
       </c>
-      <c r="B255" s="4">
+      <c r="B255" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
         <v>95977</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
         <v>96073</v>
       </c>
-      <c r="B257" s="4">
+      <c r="B257" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
         <v>96075</v>
       </c>
-      <c r="B258" s="4">
+      <c r="B258" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
         <v>96083</v>
       </c>
-      <c r="B259" s="4">
+      <c r="B259" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
         <v>96084</v>
       </c>
-      <c r="B260" s="4">
+      <c r="B260" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="3">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
         <v>96085</v>
       </c>
-      <c r="B261" s="4">
+      <c r="B261" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="3">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
         <v>96086</v>
       </c>
-      <c r="B262" s="4">
+      <c r="B262" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="3">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
         <v>96087</v>
       </c>
-      <c r="B263" s="4">
+      <c r="B263" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="3">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
         <v>96093</v>
       </c>
-      <c r="B264" s="4">
+      <c r="B264" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="3">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
         <v>96094</v>
       </c>
-      <c r="B265" s="4">
+      <c r="B265" s="2">
         <v>51</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="3">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
         <v>96095</v>
       </c>
-      <c r="B266" s="4">
+      <c r="B266" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="3">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
         <v>96096</v>
       </c>
-      <c r="B267" s="4">
+      <c r="B267" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="3">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
         <v>96097</v>
       </c>
-      <c r="B268" s="4">
+      <c r="B268" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="3">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
         <v>96098</v>
       </c>
-      <c r="B269" s="4">
+      <c r="B269" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="3">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
         <v>96099</v>
       </c>
-      <c r="B270" s="4">
+      <c r="B270" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="3">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
         <v>96100</v>
       </c>
-      <c r="B271" s="4">
+      <c r="B271" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="3">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
         <v>96101</v>
       </c>
-      <c r="B272" s="4">
+      <c r="B272" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="3">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
         <v>96102</v>
       </c>
-      <c r="B273" s="4">
+      <c r="B273" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="3">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
         <v>96103</v>
       </c>
-      <c r="B274" s="4">
+      <c r="B274" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" s="3">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
         <v>96104</v>
       </c>
-      <c r="B275" s="4">
+      <c r="B275" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" s="3">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
         <v>96105</v>
       </c>
-      <c r="B276" s="4">
+      <c r="B276" s="2">
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" s="3">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
         <v>96106</v>
       </c>
-      <c r="B277" s="4">
+      <c r="B277" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" s="3">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
         <v>96107</v>
       </c>
-      <c r="B278" s="4">
+      <c r="B278" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" s="3">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
         <v>96108</v>
       </c>
-      <c r="B279" s="4">
+      <c r="B279" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" s="3">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
         <v>96109</v>
       </c>
-      <c r="B280" s="4">
+      <c r="B280" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="3">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
         <v>96110</v>
       </c>
-      <c r="B281" s="4">
+      <c r="B281" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="3">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
         <v>96111</v>
       </c>
-      <c r="B282" s="4">
+      <c r="B282" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="3">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
         <v>96112</v>
       </c>
-      <c r="B283" s="4">
+      <c r="B283" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="3">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
         <v>96113</v>
       </c>
-      <c r="B284" s="4">
+      <c r="B284" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="3">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
         <v>96114</v>
       </c>
-      <c r="B285" s="4">
+      <c r="B285" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" s="3">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
         <v>96115</v>
       </c>
-      <c r="B286" s="4">
+      <c r="B286" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" s="3">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
         <v>96116</v>
       </c>
-      <c r="B287" s="4">
+      <c r="B287" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" s="3">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
         <v>96117</v>
       </c>
-      <c r="B288" s="4">
+      <c r="B288" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="3">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
         <v>96118</v>
       </c>
-      <c r="B289" s="4">
+      <c r="B289" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="3">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
         <v>96119</v>
       </c>
-      <c r="B290" s="4">
+      <c r="B290" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="3">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
         <v>96120</v>
       </c>
-      <c r="B291" s="4">
+      <c r="B291" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="3">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
         <v>96121</v>
       </c>
-      <c r="B292" s="4">
+      <c r="B292" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="3">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
         <v>96122</v>
       </c>
-      <c r="B293" s="4">
+      <c r="B293" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="3">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
         <v>96123</v>
       </c>
-      <c r="B294" s="4">
+      <c r="B294" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="3">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
         <v>96124</v>
       </c>
-      <c r="B295" s="4">
+      <c r="B295" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="3">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
         <v>96125</v>
       </c>
-      <c r="B296" s="4">
+      <c r="B296" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="3">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
         <v>96126</v>
       </c>
-      <c r="B297" s="4">
+      <c r="B297" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="3">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
         <v>96127</v>
       </c>
-      <c r="B298" s="4">
+      <c r="B298" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="3">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
         <v>96128</v>
       </c>
-      <c r="B299" s="4">
+      <c r="B299" s="2">
         <v>91</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="3">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
         <v>96129</v>
       </c>
-      <c r="B300" s="4">
+      <c r="B300" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" s="3">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
         <v>96130</v>
       </c>
-      <c r="B301" s="4">
+      <c r="B301" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" s="3">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
         <v>96131</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" s="3">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
         <v>96132</v>
       </c>
-      <c r="B303" s="4">
+      <c r="B303" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" s="3">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
         <v>96133</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="3">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
         <v>96134</v>
       </c>
-      <c r="B305" s="4">
+      <c r="B305" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="3">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
         <v>96135</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="3">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
         <v>96136</v>
       </c>
-      <c r="B307" s="4">
+      <c r="B307" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="3">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" s="1">
         <v>96137</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="3">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" s="1">
         <v>96144</v>
       </c>
-      <c r="B309" s="4">
+      <c r="B309" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="3">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" s="1">
         <v>96170</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="3">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" s="1">
         <v>96178</v>
       </c>
-      <c r="B311" s="4">
+      <c r="B311" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" s="3">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
         <v>96179</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" s="3">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" s="1">
         <v>96180</v>
       </c>
-      <c r="B313" s="4">
+      <c r="B313" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" s="3">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" s="1">
         <v>96788</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" s="3">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
         <v>96798</v>
       </c>
-      <c r="B315" s="4">
+      <c r="B315" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" s="3">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
         <v>96799</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" s="3">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
         <v>96800</v>
       </c>
-      <c r="B317" s="4">
+      <c r="B317" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" s="3">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
         <v>96812</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" s="3">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
         <v>96813</v>
       </c>
-      <c r="B319" s="4">
+      <c r="B319" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" s="3">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
         <v>96818</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" s="3">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
         <v>96819</v>
       </c>
-      <c r="B321" s="4">
+      <c r="B321" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" s="3">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
         <v>96820</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" s="3">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
         <v>96821</v>
       </c>
-      <c r="B323" s="4">
+      <c r="B323" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" s="3">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" s="1">
         <v>96822</v>
       </c>
-      <c r="B324" s="4">
+      <c r="B324" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" s="3">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
         <v>96834</v>
       </c>
-      <c r="B325" s="4">
+      <c r="B325" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" s="3">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
         <v>97298</v>
       </c>
-      <c r="B326" s="4">
+      <c r="B326" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" s="3">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
         <v>97299</v>
       </c>
-      <c r="B327" s="4">
+      <c r="B327" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" s="3">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
         <v>97300</v>
       </c>
-      <c r="B328" s="4">
+      <c r="B328" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" s="3">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
         <v>97301</v>
       </c>
-      <c r="B329" s="4">
+      <c r="B329" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" s="3">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" s="1">
         <v>97302</v>
       </c>
-      <c r="B330" s="4">
+      <c r="B330" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" s="3">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" s="1">
         <v>97308</v>
       </c>
-      <c r="B331" s="4">
+      <c r="B331" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" s="3">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" s="1">
         <v>97309</v>
       </c>
-      <c r="B332" s="4">
+      <c r="B332" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" s="3">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" s="1">
         <v>97310</v>
       </c>
-      <c r="B333" s="4">
+      <c r="B333" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" s="3">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
         <v>97311</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" s="3">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
         <v>97312</v>
       </c>
-      <c r="B335" s="4">
+      <c r="B335" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" s="3">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
         <v>97314</v>
       </c>
-      <c r="B336" s="4">
+      <c r="B336" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A337" s="3">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
         <v>97317</v>
       </c>
-      <c r="B337" s="4">
+      <c r="B337" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A338" s="3">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
         <v>97318</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A339" s="3">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
         <v>97319</v>
       </c>
-      <c r="B339" s="4">
+      <c r="B339" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A340" s="3">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
         <v>97320</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A341" s="3">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
         <v>97323</v>
       </c>
-      <c r="B341" s="4">
+      <c r="B341" s="2">
         <v>57</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A342" s="3">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
         <v>97324</v>
       </c>
-      <c r="B342" s="4">
+      <c r="B342" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A343" s="3">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
         <v>97325</v>
       </c>
-      <c r="B343" s="4">
+      <c r="B343" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A344" s="3">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
         <v>97327</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A345" s="3">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
         <v>97330</v>
       </c>
-      <c r="B345" s="4">
+      <c r="B345" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A346" s="3">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
         <v>97333</v>
       </c>
-      <c r="B346" s="4">
+      <c r="B346" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A347" s="3">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
         <v>97334</v>
       </c>
-      <c r="B347" s="4">
+      <c r="B347" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A348" s="3">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
         <v>97335</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349" s="3">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
         <v>97336</v>
       </c>
-      <c r="B349" s="4">
+      <c r="B349" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" s="3">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
         <v>97337</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="3">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
         <v>97343</v>
       </c>
-      <c r="B351" s="4">
+      <c r="B351" s="2">
         <v>53</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352" s="3">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
         <v>97344</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A353" s="3">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
         <v>97345</v>
       </c>
-      <c r="B353" s="4">
+      <c r="B353" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A354" s="3">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
         <v>97346</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" s="3">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
         <v>97348</v>
       </c>
-      <c r="B355" s="4">
+      <c r="B355" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A356" s="3">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
         <v>97349</v>
       </c>
-      <c r="B356" s="4">
+      <c r="B356" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A357" s="3">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
         <v>97350</v>
       </c>
-      <c r="B357" s="4">
+      <c r="B357" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A358" s="3">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
         <v>97351</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A359" s="3">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
         <v>97352</v>
       </c>
-      <c r="B359" s="4">
+      <c r="B359" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A360" s="3">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
         <v>97353</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="2">
         <v>67</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A361" s="3">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
         <v>97354</v>
       </c>
-      <c r="B361" s="4">
+      <c r="B361" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A362" s="3">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
         <v>97355</v>
       </c>
-      <c r="B362" s="4">
+      <c r="B362" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A363" s="3">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
         <v>97356</v>
       </c>
-      <c r="B363" s="4">
+      <c r="B363" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A364" s="3">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" s="1">
         <v>97357</v>
       </c>
-      <c r="B364" s="4">
+      <c r="B364" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A365" s="3">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" s="1">
         <v>97358</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B365" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A366" s="3">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" s="1">
         <v>97359</v>
       </c>
-      <c r="B366" s="4">
+      <c r="B366" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A367" s="3">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" s="1">
         <v>97360</v>
       </c>
-      <c r="B367" s="4">
+      <c r="B367" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A368" s="3">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" s="1">
         <v>97365</v>
       </c>
-      <c r="B368" s="4">
+      <c r="B368" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A369" s="3">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" s="1">
         <v>97367</v>
       </c>
-      <c r="B369" s="4">
+      <c r="B369" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A370" s="3">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
         <v>97370</v>
       </c>
-      <c r="B370" s="4">
+      <c r="B370" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A371" s="3">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
         <v>97373</v>
       </c>
-      <c r="B371" s="4">
+      <c r="B371" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A372" s="3">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
         <v>97374</v>
       </c>
-      <c r="B372" s="4">
+      <c r="B372" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A373" s="3">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
         <v>97375</v>
       </c>
-      <c r="B373" s="4">
+      <c r="B373" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A374" s="3">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
         <v>97376</v>
       </c>
-      <c r="B374" s="4">
+      <c r="B374" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A375" s="3">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
         <v>97377</v>
       </c>
-      <c r="B375" s="4">
+      <c r="B375" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A376" s="3">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
         <v>97378</v>
       </c>
-      <c r="B376" s="4">
+      <c r="B376" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A377" s="3">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
         <v>97379</v>
       </c>
-      <c r="B377" s="4">
+      <c r="B377" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A378" s="3">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
         <v>97380</v>
       </c>
-      <c r="B378" s="4">
+      <c r="B378" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A379" s="3">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
         <v>97381</v>
       </c>
-      <c r="B379" s="4">
+      <c r="B379" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A380" s="3">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
         <v>97382</v>
       </c>
-      <c r="B380" s="4">
+      <c r="B380" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A381" s="3">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
         <v>97383</v>
       </c>
-      <c r="B381" s="4">
+      <c r="B381" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A382" s="3">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
         <v>97384</v>
       </c>
-      <c r="B382" s="4">
+      <c r="B382" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A383" s="3">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
         <v>97386</v>
       </c>
-      <c r="B383" s="4">
+      <c r="B383" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A384" s="3">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
         <v>97388</v>
       </c>
-      <c r="B384" s="4">
+      <c r="B384" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A385" s="3">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
         <v>97389</v>
       </c>
-      <c r="B385" s="4">
+      <c r="B385" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A386" s="3">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
         <v>97390</v>
       </c>
-      <c r="B386" s="4">
+      <c r="B386" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A387" s="3">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" s="1">
         <v>97391</v>
       </c>
-      <c r="B387" s="4">
+      <c r="B387" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A388" s="3">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" s="1">
         <v>97392</v>
       </c>
-      <c r="B388" s="4">
+      <c r="B388" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389" s="3">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" s="1">
         <v>97393</v>
       </c>
-      <c r="B389" s="4">
+      <c r="B389" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A390" s="3">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" s="1">
         <v>97424</v>
       </c>
-      <c r="B390" s="4">
+      <c r="B390" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A391" s="3">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" s="1">
         <v>97425</v>
       </c>
-      <c r="B391" s="4">
+      <c r="B391" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A392" s="3">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" s="1">
         <v>97426</v>
       </c>
-      <c r="B392" s="4">
+      <c r="B392" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A393" s="3">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" s="1">
         <v>97429</v>
       </c>
-      <c r="B393" s="4">
+      <c r="B393" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A394" s="3">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" s="1">
         <v>97430</v>
       </c>
-      <c r="B394" s="4">
+      <c r="B394" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A395" s="3">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" s="1">
         <v>97431</v>
       </c>
-      <c r="B395" s="4">
+      <c r="B395" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396" s="3">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" s="1">
         <v>97432</v>
       </c>
-      <c r="B396" s="4">
+      <c r="B396" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A397" s="3">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" s="1">
         <v>97434</v>
       </c>
-      <c r="B397" s="4">
+      <c r="B397" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A398" s="3">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" s="1">
         <v>97436</v>
       </c>
-      <c r="B398" s="4">
+      <c r="B398" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A399" s="3">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" s="1">
         <v>97439</v>
       </c>
-      <c r="B399" s="4">
+      <c r="B399" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400" s="3">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" s="1">
         <v>97440</v>
       </c>
-      <c r="B400" s="4">
+      <c r="B400" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401" s="3">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" s="1">
         <v>97441</v>
       </c>
-      <c r="B401" s="4">
+      <c r="B401" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A402" s="3">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" s="1">
         <v>97442</v>
       </c>
-      <c r="B402" s="4">
+      <c r="B402" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A403" s="3">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" s="1">
         <v>97444</v>
       </c>
-      <c r="B403" s="4">
+      <c r="B403" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A404" s="3">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" s="1">
         <v>97445</v>
       </c>
-      <c r="B404" s="4">
+      <c r="B404" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A405" s="3">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" s="1">
         <v>97447</v>
       </c>
-      <c r="B405" s="4">
+      <c r="B405" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" s="3">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" s="1">
         <v>97448</v>
       </c>
-      <c r="B406" s="4">
+      <c r="B406" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A407" s="3">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" s="1">
         <v>97449</v>
       </c>
-      <c r="B407" s="4">
+      <c r="B407" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A408" s="3">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
         <v>97450</v>
       </c>
-      <c r="B408" s="4">
+      <c r="B408" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A409" s="3">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
         <v>97454</v>
       </c>
-      <c r="B409" s="4">
+      <c r="B409" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" s="3">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
         <v>97455</v>
       </c>
-      <c r="B410" s="4">
+      <c r="B410" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" s="3">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
         <v>97457</v>
       </c>
-      <c r="B411" s="4">
+      <c r="B411" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" s="3">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
         <v>97458</v>
       </c>
-      <c r="B412" s="4">
+      <c r="B412" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413" s="3">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
         <v>97460</v>
       </c>
-      <c r="B413" s="4">
+      <c r="B413" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A414" s="3">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
         <v>97472</v>
       </c>
-      <c r="B414" s="4">
+      <c r="B414" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" s="3">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
         <v>97484</v>
       </c>
-      <c r="B415" s="4">
+      <c r="B415" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A416" s="3">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" s="1">
         <v>97492</v>
       </c>
-      <c r="B416" s="4">
+      <c r="B416" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A417" s="3">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" s="1">
         <v>97493</v>
       </c>
-      <c r="B417" s="4">
+      <c r="B417" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A418" s="3">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418" s="1">
         <v>97494</v>
       </c>
-      <c r="B418" s="4">
+      <c r="B418" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A419" s="3">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419" s="1">
         <v>97495</v>
       </c>
-      <c r="B419" s="4">
+      <c r="B419" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A420" s="3">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420" s="1">
         <v>97501</v>
       </c>
-      <c r="B420" s="4">
+      <c r="B420" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A421" s="3">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421" s="1">
         <v>97502</v>
       </c>
-      <c r="B421" s="4">
+      <c r="B421" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A422" s="3">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422" s="1">
         <v>97503</v>
       </c>
-      <c r="B422" s="4">
+      <c r="B422" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A423" s="3">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423" s="1">
         <v>97504</v>
       </c>
-      <c r="B423" s="4">
+      <c r="B423" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A424" s="3">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424" s="1">
         <v>97505</v>
       </c>
-      <c r="B424" s="4">
+      <c r="B424" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A425" s="3">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425" s="1">
         <v>97797</v>
       </c>
-      <c r="B425" s="4">
+      <c r="B425" s="2">
         <v>103</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426" s="3">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426" s="1">
         <v>97798</v>
       </c>
-      <c r="B426" s="4">
+      <c r="B426" s="2">
         <v>103</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A427" s="3">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427" s="1">
         <v>97799</v>
       </c>
-      <c r="B427" s="4">
+      <c r="B427" s="2">
         <v>70</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A428" s="3">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428" s="1">
         <v>97800</v>
       </c>
-      <c r="B428" s="4">
+      <c r="B428" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A429" s="3">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429" s="1">
         <v>97801</v>
       </c>
-      <c r="B429" s="4">
+      <c r="B429" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A430" s="3">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430" s="1">
         <v>97802</v>
       </c>
-      <c r="B430" s="4">
+      <c r="B430" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A431" s="3">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431" s="1">
         <v>97803</v>
       </c>
-      <c r="B431" s="4">
+      <c r="B431" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A432" s="3">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432" s="1">
         <v>97804</v>
       </c>
-      <c r="B432" s="4">
+      <c r="B432" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433" s="3">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" s="1">
         <v>97805</v>
       </c>
-      <c r="B433" s="4">
+      <c r="B433" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A434" s="3">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" s="1">
         <v>97806</v>
       </c>
-      <c r="B434" s="4">
+      <c r="B434" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A435" s="3">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" s="1">
         <v>97812</v>
       </c>
-      <c r="B435" s="4">
+      <c r="B435" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436" s="3">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" s="1">
         <v>97813</v>
       </c>
-      <c r="B436" s="4">
+      <c r="B436" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A437" s="3">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437" s="1">
         <v>97814</v>
       </c>
-      <c r="B437" s="4">
+      <c r="B437" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A438" s="3">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438" s="1">
         <v>97815</v>
       </c>
-      <c r="B438" s="4">
+      <c r="B438" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A439" s="3">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439" s="1">
         <v>97816</v>
       </c>
-      <c r="B439" s="4">
+      <c r="B439" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A440" s="3">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440" s="1">
         <v>97817</v>
       </c>
-      <c r="B440" s="4">
+      <c r="B440" s="2">
         <v>108</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A441" s="3">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441" s="1">
         <v>97818</v>
       </c>
-      <c r="B441" s="4">
+      <c r="B441" s="2">
         <v>119</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A442" s="3">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442" s="1">
         <v>97819</v>
       </c>
-      <c r="B442" s="4">
+      <c r="B442" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A443" s="3">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443" s="1">
         <v>97820</v>
       </c>
-      <c r="B443" s="4">
+      <c r="B443" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A444" s="3">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444" s="1">
         <v>97821</v>
       </c>
-      <c r="B444" s="4">
+      <c r="B444" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A445" s="3">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445" s="1">
         <v>97823</v>
       </c>
-      <c r="B445" s="4">
+      <c r="B445" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A446" s="3">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446" s="1">
         <v>20839</v>
       </c>
-      <c r="B446" s="4">
+      <c r="B446" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A447" s="3">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447" s="1">
         <v>20840</v>
       </c>
-      <c r="B447" s="4">
+      <c r="B447" s="2">
         <v>2580</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448" s="3">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448" s="1">
         <v>20841</v>
       </c>
-      <c r="B448" s="4">
+      <c r="B448" s="2">
         <v>960</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A449" s="3">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A449" s="1">
         <v>20846</v>
       </c>
-      <c r="B449" s="4">
+      <c r="B449" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A450" s="3">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A450" s="1">
         <v>28063</v>
       </c>
-      <c r="B450" s="4">
+      <c r="B450" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A451" s="3">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A451" s="1">
         <v>34299</v>
       </c>
-      <c r="B451" s="4">
+      <c r="B451" s="2">
         <v>740</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A452" s="3">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A452" s="1">
         <v>44701</v>
       </c>
-      <c r="B452" s="4">
+      <c r="B452" s="2">
         <v>480</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A453" s="3">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A453" s="1">
         <v>57140</v>
       </c>
-      <c r="B453" s="4">
+      <c r="B453" s="2">
         <v>120</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A454" s="3">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A454" s="1">
         <v>60005</v>
       </c>
-      <c r="B454" s="4">
+      <c r="B454" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A455" s="3">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455" s="1">
         <v>65318</v>
       </c>
-      <c r="B455" s="4">
+      <c r="B455" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" s="3">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A456" s="1">
         <v>68293</v>
       </c>
-      <c r="B456" s="4">
+      <c r="B456" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A457" s="3">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A457" s="1">
         <v>68651</v>
       </c>
-      <c r="B457" s="4">
+      <c r="B457" s="2">
         <v>192</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A458" s="3">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A458" s="1">
         <v>69369</v>
       </c>
-      <c r="B458" s="4">
+      <c r="B458" s="2">
         <v>624</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A459" s="3">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A459" s="1">
         <v>69372</v>
       </c>
-      <c r="B459" s="4">
+      <c r="B459" s="2">
         <v>2328</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460" s="3">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A460" s="1">
         <v>69373</v>
       </c>
-      <c r="B460" s="4">
+      <c r="B460" s="2">
         <v>2604</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461" s="3">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A461" s="1">
         <v>69378</v>
       </c>
-      <c r="B461" s="4">
+      <c r="B461" s="2">
         <v>384</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462" s="3">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A462" s="1">
         <v>69380</v>
       </c>
-      <c r="B462" s="4">
+      <c r="B462" s="2">
         <v>1764</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A463" s="3">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A463" s="1">
         <v>69382</v>
       </c>
-      <c r="B463" s="4">
+      <c r="B463" s="2">
         <v>1224</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A464" s="3">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A464" s="1">
         <v>69389</v>
       </c>
-      <c r="B464" s="4">
+      <c r="B464" s="2">
         <v>2376</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A465" s="3">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A465" s="1">
         <v>69393</v>
       </c>
-      <c r="B465" s="4">
+      <c r="B465" s="2">
         <v>156</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466" s="3">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A466" s="1">
         <v>69394</v>
       </c>
-      <c r="B466" s="4">
+      <c r="B466" s="2">
         <v>516</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A467" s="3">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A467" s="1">
         <v>69948</v>
       </c>
-      <c r="B467" s="4">
+      <c r="B467" s="2">
         <v>864</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" s="3">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A468" s="1">
         <v>69949</v>
       </c>
-      <c r="B468" s="4">
+      <c r="B468" s="2">
         <v>312</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A469" s="3">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A469" s="1">
         <v>71232</v>
       </c>
-      <c r="B469" s="4">
+      <c r="B469" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A470" s="3">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A470" s="1">
         <v>74158</v>
       </c>
-      <c r="B470" s="4">
+      <c r="B470" s="2">
         <v>1356</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A471" s="3">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A471" s="1">
         <v>74160</v>
       </c>
-      <c r="B471" s="4">
+      <c r="B471" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A472" s="3">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A472" s="1">
         <v>74163</v>
       </c>
-      <c r="B472" s="4">
+      <c r="B472" s="2">
         <v>540</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A473" s="3">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A473" s="1">
         <v>83233</v>
       </c>
-      <c r="B473" s="4">
+      <c r="B473" s="2">
         <v>660</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A474" s="3">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A474" s="1">
         <v>87171</v>
       </c>
-      <c r="B474" s="4">
+      <c r="B474" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A475" s="3">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A475" s="1">
         <v>91515</v>
       </c>
-      <c r="B475" s="4">
+      <c r="B475" s="2">
         <v>66</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A476" s="3">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A476" s="1">
         <v>91732</v>
       </c>
-      <c r="B476" s="4">
+      <c r="B476" s="2">
         <v>400</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A477" s="3">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A477" s="1">
         <v>92742</v>
       </c>
-      <c r="B477" s="4">
+      <c r="B477" s="2">
         <v>144</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A478" s="3">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A478" s="1">
         <v>92767</v>
       </c>
-      <c r="B478" s="4">
+      <c r="B478" s="2">
         <v>1971</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A479" s="3">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A479" s="1">
         <v>93027</v>
       </c>
-      <c r="B479" s="4">
+      <c r="B479" s="2">
         <v>810</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A480" s="3">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A480" s="1">
         <v>93036</v>
       </c>
-      <c r="B480" s="4">
+      <c r="B480" s="2">
         <v>1008</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A481" s="3">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A481" s="1">
         <v>94355</v>
       </c>
-      <c r="B481" s="4">
+      <c r="B481" s="2">
         <v>176</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A482" s="3">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A482" s="1">
         <v>94356</v>
       </c>
-      <c r="B482" s="4">
+      <c r="B482" s="2">
         <v>380</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A483" s="3">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A483" s="1">
         <v>94357</v>
       </c>
-      <c r="B483" s="4">
+      <c r="B483" s="2">
         <v>392</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A484" s="3">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A484" s="1">
         <v>94358</v>
       </c>
-      <c r="B484" s="4">
+      <c r="B484" s="2">
         <v>404</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A485" s="3">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A485" s="1">
         <v>94404</v>
       </c>
-      <c r="B485" s="4">
+      <c r="B485" s="2">
         <v>884</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486" s="3">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A486" s="1">
         <v>94643</v>
       </c>
-      <c r="B486" s="4">
+      <c r="B486" s="2">
         <v>408</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A487" s="3">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A487" s="1">
         <v>94718</v>
       </c>
-      <c r="B487" s="4">
+      <c r="B487" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A488" s="3">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A488" s="1">
         <v>95618</v>
       </c>
-      <c r="B488" s="4">
+      <c r="B488" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A489" s="3">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A489" s="1">
         <v>95667</v>
       </c>
-      <c r="B489" s="4">
+      <c r="B489" s="2">
         <v>168</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A490" s="3">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A490" s="1">
         <v>95670</v>
       </c>
-      <c r="B490" s="4">
+      <c r="B490" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A491" s="3">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A491" s="1">
         <v>95924</v>
       </c>
-      <c r="B491" s="4">
+      <c r="B491" s="2">
         <v>51</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A492" s="3">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A492" s="1">
         <v>95927</v>
       </c>
-      <c r="B492" s="4">
+      <c r="B492" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A493" s="3">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A493" s="1">
         <v>95929</v>
       </c>
-      <c r="B493" s="4">
+      <c r="B493" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A494" s="3">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A494" s="1">
         <v>95931</v>
       </c>
-      <c r="B494" s="4">
+      <c r="B494" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A495" s="3">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A495" s="1">
         <v>96331</v>
       </c>
-      <c r="B495" s="4">
+      <c r="B495" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A496" s="3">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A496" s="1">
         <v>96443</v>
       </c>
-      <c r="B496" s="4">
+      <c r="B496" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A497" s="3">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A497" s="1">
         <v>96444</v>
       </c>
-      <c r="B497" s="4">
+      <c r="B497" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A498" s="3">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A498" s="1">
         <v>96453</v>
       </c>
-      <c r="B498" s="4">
+      <c r="B498" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A499" s="3">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A499" s="1">
         <v>96496</v>
       </c>
-      <c r="B499" s="4">
+      <c r="B499" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A500" s="3">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A500" s="1">
         <v>96519</v>
       </c>
-      <c r="B500" s="4">
+      <c r="B500" s="2">
         <v>840</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A501" s="3">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A501" s="1">
         <v>96710</v>
       </c>
-      <c r="B501" s="4">
+      <c r="B501" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A502" s="3">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A502" s="1">
         <v>97126</v>
       </c>
-      <c r="B502" s="4">
+      <c r="B502" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A503" s="3">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A503" s="1">
         <v>97127</v>
       </c>
-      <c r="B503" s="4">
+      <c r="B503" s="2">
         <v>156</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A504" s="3">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A504" s="1">
         <v>97129</v>
       </c>
-      <c r="B504" s="4">
+      <c r="B504" s="2">
         <v>128</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A505" s="3">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A505" s="1">
         <v>97130</v>
       </c>
-      <c r="B505" s="4">
+      <c r="B505" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A506" s="3">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A506" s="1">
         <v>97131</v>
       </c>
-      <c r="B506" s="4">
+      <c r="B506" s="2">
         <v>144</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A507" s="3">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A507" s="1">
         <v>97133</v>
       </c>
-      <c r="B507" s="4">
+      <c r="B507" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A508" s="3">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A508" s="1">
         <v>97135</v>
       </c>
-      <c r="B508" s="4">
+      <c r="B508" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A509" s="3">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A509" s="1">
         <v>97552</v>
       </c>
-      <c r="B509" s="4">
+      <c r="B509" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A510" s="3">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A510" s="1">
         <v>97553</v>
       </c>
-      <c r="B510" s="4">
+      <c r="B510" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A511" s="3">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A511" s="1">
         <v>97554</v>
       </c>
-      <c r="B511" s="4">
+      <c r="B511" s="2">
         <v>344</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A512" s="3">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A512" s="1">
         <v>97555</v>
       </c>
-      <c r="B512" s="4">
+      <c r="B512" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A513" s="3">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A513" s="1">
         <v>97557</v>
       </c>
-      <c r="B513" s="4">
+      <c r="B513" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A514" s="3">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A514" s="1">
         <v>97558</v>
       </c>
-      <c r="B514" s="4">
+      <c r="B514" s="2">
         <v>132</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A515" s="3">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A515" s="1">
         <v>97559</v>
       </c>
-      <c r="B515" s="4">
+      <c r="B515" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A516" s="3">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A516" s="1">
         <v>97560</v>
       </c>
-      <c r="B516" s="4">
+      <c r="B516" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A517" s="3">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A517" s="1">
         <v>97561</v>
       </c>
-      <c r="B517" s="4">
+      <c r="B517" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A518" s="3">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A518" s="1">
         <v>97562</v>
       </c>
-      <c r="B518" s="4">
+      <c r="B518" s="2">
         <v>324</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A519" s="3">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A519" s="1">
         <v>97563</v>
       </c>
-      <c r="B519" s="4">
+      <c r="B519" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A520" s="3">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A520" s="1">
         <v>97564</v>
       </c>
-      <c r="B520" s="4">
+      <c r="B520" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A521" s="3">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A521" s="1">
         <v>97565</v>
       </c>
-      <c r="B521" s="4">
+      <c r="B521" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A522" s="3">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A522" s="1">
         <v>97566</v>
       </c>
-      <c r="B522" s="4">
+      <c r="B522" s="2">
         <v>119</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A523" s="3">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A523" s="1">
         <v>97567</v>
       </c>
-      <c r="B523" s="4">
+      <c r="B523" s="2">
         <v>202</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A524" s="3">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A524" s="1">
         <v>97568</v>
       </c>
-      <c r="B524" s="4">
+      <c r="B524" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A525" s="3">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A525" s="1">
         <v>97569</v>
       </c>
-      <c r="B525" s="4">
+      <c r="B525" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A526" s="3">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A526" s="1">
         <v>97570</v>
       </c>
-      <c r="B526" s="4">
+      <c r="B526" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A527" s="3">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A527" s="1">
         <v>97571</v>
       </c>
-      <c r="B527" s="4">
+      <c r="B527" s="2">
         <v>102</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A528" s="3">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A528" s="1">
         <v>97572</v>
       </c>
-      <c r="B528" s="4">
+      <c r="B528" s="2">
         <v>176</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A529" s="3">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A529" s="1">
         <v>97573</v>
       </c>
-      <c r="B529" s="4">
+      <c r="B529" s="2">
         <v>228</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A530" s="3">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A530" s="1">
         <v>97574</v>
       </c>
-      <c r="B530" s="4">
+      <c r="B530" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A531" s="3">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A531" s="1">
         <v>97575</v>
       </c>
-      <c r="B531" s="4">
+      <c r="B531" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A532" s="3">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A532" s="1">
         <v>97576</v>
       </c>
-      <c r="B532" s="4">
+      <c r="B532" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A533" s="3">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A533" s="1">
         <v>97577</v>
       </c>
-      <c r="B533" s="4">
+      <c r="B533" s="2">
         <v>86</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A534" s="3">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A534" s="1">
         <v>97578</v>
       </c>
-      <c r="B534" s="4">
+      <c r="B534" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A535" s="3">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A535" s="1">
         <v>97579</v>
       </c>
-      <c r="B535" s="4">
+      <c r="B535" s="2">
         <v>116</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A536" s="3">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A536" s="1">
         <v>97587</v>
       </c>
-      <c r="B536" s="4">
+      <c r="B536" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A537" s="3">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A537" s="1">
         <v>97588</v>
       </c>
-      <c r="B537" s="4">
+      <c r="B537" s="2">
         <v>146</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A538" s="3">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A538" s="1">
         <v>97590</v>
       </c>
-      <c r="B538" s="4">
+      <c r="B538" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A539" s="3">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A539" s="1">
         <v>97592</v>
       </c>
-      <c r="B539" s="4">
+      <c r="B539" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A540" s="3">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A540" s="1">
         <v>97595</v>
       </c>
-      <c r="B540" s="4">
+      <c r="B540" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A541" s="3">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A541" s="1">
         <v>97596</v>
       </c>
-      <c r="B541" s="4">
+      <c r="B541" s="2">
         <v>396</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A542" s="3">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A542" s="1">
         <v>97597</v>
       </c>
-      <c r="B542" s="4">
+      <c r="B542" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A543" s="3">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A543" s="1">
         <v>97598</v>
       </c>
-      <c r="B543" s="4">
+      <c r="B543" s="2">
         <v>66</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A544" s="3">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A544" s="1">
         <v>97599</v>
       </c>
-      <c r="B544" s="4">
+      <c r="B544" s="2">
         <v>96</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A545" s="3">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A545" s="1">
         <v>97600</v>
       </c>
-      <c r="B545" s="4">
+      <c r="B545" s="2">
         <v>171</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A546" s="3">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A546" s="1">
         <v>97601</v>
       </c>
-      <c r="B546" s="4">
+      <c r="B546" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A547" s="3">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A547" s="1">
         <v>97602</v>
       </c>
-      <c r="B547" s="4">
+      <c r="B547" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A548" s="3">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A548" s="1">
         <v>97603</v>
       </c>
-      <c r="B548" s="4">
+      <c r="B548" s="2">
         <v>87</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A549" s="3">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A549" s="1">
         <v>97604</v>
       </c>
-      <c r="B549" s="4">
+      <c r="B549" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A550" s="3">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A550" s="1">
         <v>97605</v>
       </c>
-      <c r="B550" s="4">
+      <c r="B550" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A551" s="3">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A551" s="1">
         <v>97606</v>
       </c>
-      <c r="B551" s="4">
+      <c r="B551" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A552" s="3">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A552" s="1">
         <v>97607</v>
       </c>
-      <c r="B552" s="4">
+      <c r="B552" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A553" s="3">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A553" s="1">
         <v>97608</v>
       </c>
-      <c r="B553" s="4">
+      <c r="B553" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A554" s="3">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A554" s="1">
         <v>97624</v>
       </c>
-      <c r="B554" s="4">
+      <c r="B554" s="2">
         <v>189</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A555" s="3">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A555" s="1">
         <v>97625</v>
       </c>
-      <c r="B555" s="4">
+      <c r="B555" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A556" s="3">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A556" s="1">
         <v>97626</v>
       </c>
-      <c r="B556" s="4">
+      <c r="B556" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A557" s="3">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A557" s="1">
         <v>97627</v>
       </c>
-      <c r="B557" s="4">
+      <c r="B557" s="2">
         <v>87</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A558" s="3">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A558" s="1">
         <v>97628</v>
       </c>
-      <c r="B558" s="4">
+      <c r="B558" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A559" s="3">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A559" s="1">
         <v>97629</v>
       </c>
-      <c r="B559" s="4">
+      <c r="B559" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A560" s="3">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A560" s="1">
         <v>97652</v>
       </c>
-      <c r="B560" s="4">
+      <c r="B560" s="2">
         <v>103</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A561" s="3">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A561" s="1">
         <v>97653</v>
       </c>
-      <c r="B561" s="4">
+      <c r="B561" s="2">
         <v>131</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A562" s="3">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A562" s="1">
         <v>97654</v>
       </c>
-      <c r="B562" s="4">
+      <c r="B562" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A563" s="3">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A563" s="1">
         <v>97881</v>
       </c>
-      <c r="B563" s="4">
+      <c r="B563" s="2">
         <v>720</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A564" s="3">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A564" s="1">
         <v>97882</v>
       </c>
-      <c r="B564" s="4">
+      <c r="B564" s="2">
         <v>688</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A565" s="3">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A565" s="1">
         <v>7722</v>
       </c>
-      <c r="B565" s="4">
+      <c r="B565" s="2">
         <v>936</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A566" s="3">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A566" s="1">
         <v>33427</v>
       </c>
-      <c r="B566" s="4">
+      <c r="B566" s="2">
         <v>780</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A567" s="3">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A567" s="1">
         <v>59285</v>
       </c>
-      <c r="B567" s="4">
+      <c r="B567" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A568" s="3">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A568" s="1">
         <v>78372</v>
       </c>
-      <c r="B568" s="4">
+      <c r="B568" s="2">
         <v>740</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A569" s="3">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A569" s="1">
         <v>84540</v>
       </c>
-      <c r="B569" s="4">
+      <c r="B569" s="2">
         <v>4480</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A570" s="3">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A570" s="1">
         <v>89097</v>
       </c>
-      <c r="B570" s="4">
+      <c r="B570" s="2">
         <v>515</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A571" s="3">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A571" s="1">
         <v>92811</v>
       </c>
-      <c r="B571" s="4">
+      <c r="B571" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A572" s="3">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A572" s="1">
         <v>94746</v>
       </c>
-      <c r="B572" s="4">
+      <c r="B572" s="2">
         <v>834</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A573" s="3">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A573" s="1">
         <v>95346</v>
       </c>
-      <c r="B573" s="4">
+      <c r="B573" s="2">
         <v>2592</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A574" s="3">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A574" s="1">
         <v>95588</v>
       </c>
-      <c r="B574" s="4">
+      <c r="B574" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A575" s="3">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A575" s="1">
         <v>95795</v>
       </c>
-      <c r="B575" s="4">
+      <c r="B575" s="2">
         <v>1452</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A576" s="3">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A576" s="1">
         <v>96895</v>
       </c>
-      <c r="B576" s="4">
+      <c r="B576" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A577" s="3">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A577" s="1">
         <v>96896</v>
       </c>
-      <c r="B577" s="4">
+      <c r="B577" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A578" s="3">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A578" s="1">
         <v>96898</v>
       </c>
-      <c r="B578" s="4">
+      <c r="B578" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A579" s="3">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A579" s="1">
         <v>96989</v>
       </c>
-      <c r="B579" s="4">
+      <c r="B579" s="2">
         <v>2000</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A580" s="3">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A580" s="1">
         <v>97519</v>
       </c>
-      <c r="B580" s="4">
+      <c r="B580" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A581" s="3">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A581" s="1">
         <v>97633</v>
       </c>
-      <c r="B581" s="4">
+      <c r="B581" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A582" s="3">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A582" s="1">
         <v>97635</v>
       </c>
-      <c r="B582" s="4">
+      <c r="B582" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A583" s="3">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A583" s="1">
         <v>97639</v>
       </c>
-      <c r="B583" s="4">
+      <c r="B583" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A584" s="3">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A584" s="1">
         <v>97640</v>
       </c>
-      <c r="B584" s="4">
+      <c r="B584" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A585" s="3">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A585" s="1">
         <v>97642</v>
       </c>
-      <c r="B585" s="4">
+      <c r="B585" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A586" s="3">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A586" s="1">
         <v>97644</v>
       </c>
-      <c r="B586" s="4">
+      <c r="B586" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A587" s="3">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A587" s="1">
         <v>97645</v>
       </c>
-      <c r="B587" s="4">
+      <c r="B587" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A588" s="3">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A588" s="1">
         <v>97662</v>
       </c>
-      <c r="B588" s="4">
+      <c r="B588" s="2">
         <v>390</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A589" s="3">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A589" s="1">
         <v>97663</v>
       </c>
-      <c r="B589" s="4">
+      <c r="B589" s="2">
         <v>460</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A590" s="3">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A590" s="1">
         <v>97664</v>
       </c>
-      <c r="B590" s="4">
+      <c r="B590" s="2">
         <v>360</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A591" s="3">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A591" s="1">
         <v>97665</v>
       </c>
-      <c r="B591" s="4">
+      <c r="B591" s="2">
         <v>6000</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A592" s="3">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A592" s="1">
         <v>98539</v>
       </c>
-      <c r="B592" s="4">
+      <c r="B592" s="2">
         <v>420</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A593" s="3">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A593" s="1">
         <v>98540</v>
       </c>
-      <c r="B593" s="4">
+      <c r="B593" s="2">
         <v>420</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A594" s="3">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A594" s="1">
         <v>98541</v>
       </c>
-      <c r="B594" s="4">
+      <c r="B594" s="2">
         <v>420</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A595" s="3">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A595" s="1">
         <v>99389</v>
       </c>
-      <c r="B595" s="4">
+      <c r="B595" s="2">
         <v>948</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A596" s="3">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A596" s="1">
         <v>9646</v>
       </c>
-      <c r="B596" s="4">
+      <c r="B596" s="2">
         <v>2424</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A597" s="3">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A597" s="1">
         <v>24874</v>
       </c>
-      <c r="B597" s="4">
+      <c r="B597" s="2">
         <v>1988</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A598" s="3">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A598" s="1">
         <v>53546</v>
       </c>
-      <c r="B598" s="4">
+      <c r="B598" s="2">
         <v>1728</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A599" s="3">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A599" s="1">
         <v>59014</v>
       </c>
-      <c r="B599" s="4">
+      <c r="B599" s="2">
         <v>990</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A600" s="3">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A600" s="1">
         <v>65788</v>
       </c>
-      <c r="B600" s="4">
+      <c r="B600" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A601" s="3">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A601" s="1">
         <v>65800</v>
       </c>
-      <c r="B601" s="4">
+      <c r="B601" s="2">
         <v>308</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A602" s="3">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A602" s="1">
         <v>65802</v>
       </c>
-      <c r="B602" s="4">
+      <c r="B602" s="2">
         <v>158</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A603" s="3">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A603" s="1">
         <v>65803</v>
       </c>
-      <c r="B603" s="4">
+      <c r="B603" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A604" s="3">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A604" s="1">
         <v>65805</v>
       </c>
-      <c r="B604" s="4">
+      <c r="B604" s="2">
         <v>538</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A605" s="3">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A605" s="1">
         <v>65948</v>
       </c>
-      <c r="B605" s="4">
+      <c r="B605" s="2">
         <v>392</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A606" s="3">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A606" s="1">
         <v>66663</v>
       </c>
-      <c r="B606" s="4">
+      <c r="B606" s="2">
         <v>870</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A607" s="3">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A607" s="1">
         <v>68463</v>
       </c>
-      <c r="B607" s="4">
+      <c r="B607" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A608" s="3">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A608" s="1">
         <v>70620</v>
       </c>
-      <c r="B608" s="4">
+      <c r="B608" s="2">
         <v>1008</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A609" s="3">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A609" s="1">
         <v>72153</v>
       </c>
-      <c r="B609" s="4">
+      <c r="B609" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A610" s="3">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A610" s="1">
         <v>72157</v>
       </c>
-      <c r="B610" s="4">
+      <c r="B610" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A611" s="3">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A611" s="1">
         <v>74779</v>
       </c>
-      <c r="B611" s="4">
+      <c r="B611" s="2">
         <v>1864</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A612" s="3">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A612" s="1">
         <v>75920</v>
       </c>
-      <c r="B612" s="4">
+      <c r="B612" s="2">
         <v>880</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A613" s="3">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A613" s="1">
         <v>75922</v>
       </c>
-      <c r="B613" s="4">
+      <c r="B613" s="2">
         <v>766</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A614" s="3">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A614" s="1">
         <v>75923</v>
       </c>
-      <c r="B614" s="4">
+      <c r="B614" s="2">
         <v>888</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A615" s="3">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A615" s="1">
         <v>75924</v>
       </c>
-      <c r="B615" s="4">
+      <c r="B615" s="2">
         <v>1038</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A616" s="3">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A616" s="1">
         <v>76063</v>
       </c>
-      <c r="B616" s="4">
+      <c r="B616" s="2">
         <v>1030</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A617" s="3">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A617" s="1">
         <v>76064</v>
       </c>
-      <c r="B617" s="4">
+      <c r="B617" s="2">
         <v>1128</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A618" s="3">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A618" s="1">
         <v>76065</v>
       </c>
-      <c r="B618" s="4">
+      <c r="B618" s="2">
         <v>1648</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A619" s="3">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A619" s="1">
         <v>76066</v>
       </c>
-      <c r="B619" s="4">
+      <c r="B619" s="2">
         <v>1864</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A620" s="3">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A620" s="1">
         <v>76067</v>
       </c>
-      <c r="B620" s="4">
+      <c r="B620" s="2">
         <v>1540</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A621" s="3">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A621" s="1">
         <v>77697</v>
       </c>
-      <c r="B621" s="4">
+      <c r="B621" s="2">
         <v>970</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A622" s="3">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A622" s="1">
         <v>78624</v>
       </c>
-      <c r="B622" s="4">
+      <c r="B622" s="2">
         <v>108</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A623" s="3">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A623" s="1">
         <v>78625</v>
       </c>
-      <c r="B623" s="4">
+      <c r="B623" s="2">
         <v>202</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A624" s="3">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A624" s="1">
         <v>78626</v>
       </c>
-      <c r="B624" s="4">
+      <c r="B624" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A625" s="3">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A625" s="1">
         <v>78627</v>
       </c>
-      <c r="B625" s="4">
+      <c r="B625" s="2">
         <v>106</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A626" s="3">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A626" s="1">
         <v>78628</v>
       </c>
-      <c r="B626" s="4">
+      <c r="B626" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A627" s="3">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A627" s="1">
         <v>78629</v>
       </c>
-      <c r="B627" s="4">
+      <c r="B627" s="2">
         <v>112</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A628" s="3">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A628" s="1">
         <v>78630</v>
       </c>
-      <c r="B628" s="4">
+      <c r="B628" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A629" s="3">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A629" s="1">
         <v>78632</v>
       </c>
-      <c r="B629" s="4">
+      <c r="B629" s="2">
         <v>142</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A630" s="3">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A630" s="1">
         <v>78633</v>
       </c>
-      <c r="B630" s="4">
+      <c r="B630" s="2">
         <v>196</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A631" s="3">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A631" s="1">
         <v>78634</v>
       </c>
-      <c r="B631" s="4">
+      <c r="B631" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A632" s="3">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A632" s="1">
         <v>78635</v>
       </c>
-      <c r="B632" s="4">
+      <c r="B632" s="2">
         <v>104</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A633" s="3">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A633" s="1">
         <v>80655</v>
       </c>
-      <c r="B633" s="4">
+      <c r="B633" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A634" s="3">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A634" s="1">
         <v>80657</v>
       </c>
-      <c r="B634" s="4">
+      <c r="B634" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A635" s="3">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A635" s="1">
         <v>80660</v>
       </c>
-      <c r="B635" s="4">
+      <c r="B635" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A636" s="3">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A636" s="1">
         <v>80662</v>
       </c>
-      <c r="B636" s="4">
+      <c r="B636" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A637" s="3">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A637" s="1">
         <v>80677</v>
       </c>
-      <c r="B637" s="4">
+      <c r="B637" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A638" s="3">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A638" s="1">
         <v>80679</v>
       </c>
-      <c r="B638" s="4">
+      <c r="B638" s="2">
         <v>798</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A639" s="3">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A639" s="1">
         <v>80680</v>
       </c>
-      <c r="B639" s="4">
+      <c r="B639" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A640" s="3">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A640" s="1">
         <v>80684</v>
       </c>
-      <c r="B640" s="4">
+      <c r="B640" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A641" s="3">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A641" s="1">
         <v>80685</v>
       </c>
-      <c r="B641" s="4">
+      <c r="B641" s="2">
         <v>420</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A642" s="3">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A642" s="1">
         <v>82833</v>
       </c>
-      <c r="B642" s="4">
+      <c r="B642" s="2">
         <v>206</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A643" s="3">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A643" s="1">
         <v>82834</v>
       </c>
-      <c r="B643" s="4">
+      <c r="B643" s="2">
         <v>158</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A644" s="3">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A644" s="1">
         <v>84801</v>
       </c>
-      <c r="B644" s="4">
+      <c r="B644" s="2">
         <v>304</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A645" s="3">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A645" s="1">
         <v>84802</v>
       </c>
-      <c r="B645" s="4">
+      <c r="B645" s="2">
         <v>454</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A646" s="3">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A646" s="1">
         <v>84803</v>
       </c>
-      <c r="B646" s="4">
+      <c r="B646" s="2">
         <v>344</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A647" s="3">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A647" s="1">
         <v>84804</v>
       </c>
-      <c r="B647" s="4">
+      <c r="B647" s="2">
         <v>154</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A648" s="3">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A648" s="1">
         <v>84807</v>
       </c>
-      <c r="B648" s="4">
+      <c r="B648" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A649" s="3">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A649" s="1">
         <v>86538</v>
       </c>
-      <c r="B649" s="4">
+      <c r="B649" s="2">
         <v>486</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A650" s="3">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A650" s="1">
         <v>87263</v>
       </c>
-      <c r="B650" s="4">
+      <c r="B650" s="2">
         <v>330</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A651" s="3">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A651" s="1">
         <v>87325</v>
       </c>
-      <c r="B651" s="4">
+      <c r="B651" s="2">
         <v>900</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A652" s="3">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A652" s="1">
         <v>87326</v>
       </c>
-      <c r="B652" s="4">
+      <c r="B652" s="2">
         <v>936</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A653" s="3">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A653" s="1">
         <v>87901</v>
       </c>
-      <c r="B653" s="4">
+      <c r="B653" s="2">
         <v>1538</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A654" s="3">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A654" s="1">
         <v>87903</v>
       </c>
-      <c r="B654" s="4">
+      <c r="B654" s="2">
         <v>158</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A655" s="3">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A655" s="1">
         <v>88350</v>
       </c>
-      <c r="B655" s="4">
+      <c r="B655" s="2">
         <v>838</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A656" s="3">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A656" s="1">
         <v>88360</v>
       </c>
-      <c r="B656" s="4">
+      <c r="B656" s="2">
         <v>1020</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A657" s="3">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A657" s="1">
         <v>88400</v>
       </c>
-      <c r="B657" s="4">
+      <c r="B657" s="2">
         <v>1430</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A658" s="3">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A658" s="1">
         <v>89190</v>
       </c>
-      <c r="B658" s="4">
+      <c r="B658" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A659" s="3">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A659" s="1">
         <v>89191</v>
       </c>
-      <c r="B659" s="4">
+      <c r="B659" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A660" s="3">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A660" s="1">
         <v>89192</v>
       </c>
-      <c r="B660" s="4">
+      <c r="B660" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A661" s="3">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A661" s="1">
         <v>89194</v>
       </c>
-      <c r="B661" s="4">
+      <c r="B661" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A662" s="3">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A662" s="1">
         <v>89196</v>
       </c>
-      <c r="B662" s="4">
+      <c r="B662" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A663" s="3">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A663" s="1">
         <v>90109</v>
       </c>
-      <c r="B663" s="4">
+      <c r="B663" s="2">
         <v>1864</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A664" s="3">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A664" s="1">
         <v>90497</v>
       </c>
-      <c r="B664" s="4">
+      <c r="B664" s="2">
         <v>316</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A665" s="3">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A665" s="1">
         <v>90973</v>
       </c>
-      <c r="B665" s="4">
+      <c r="B665" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A666" s="3">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A666" s="1">
         <v>91653</v>
       </c>
-      <c r="B666" s="4">
+      <c r="B666" s="2">
         <v>804</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A667" s="3">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A667" s="1">
         <v>91665</v>
       </c>
-      <c r="B667" s="4">
+      <c r="B667" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A668" s="3">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A668" s="1">
         <v>91678</v>
       </c>
-      <c r="B668" s="4">
+      <c r="B668" s="2">
         <v>774</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A669" s="3">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A669" s="1">
         <v>92172</v>
       </c>
-      <c r="B669" s="4">
+      <c r="B669" s="2">
         <v>152</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A670" s="3">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A670" s="1">
         <v>92176</v>
       </c>
-      <c r="B670" s="4">
+      <c r="B670" s="2">
         <v>1490</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A671" s="3">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A671" s="1">
         <v>92184</v>
       </c>
-      <c r="B671" s="4">
+      <c r="B671" s="2">
         <v>213</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A672" s="3">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A672" s="1">
         <v>92463</v>
       </c>
-      <c r="B672" s="4">
+      <c r="B672" s="2">
         <v>244</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A673" s="3">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A673" s="1">
         <v>92815</v>
       </c>
-      <c r="B673" s="4">
+      <c r="B673" s="2">
         <v>608</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A674" s="3">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A674" s="1">
         <v>92822</v>
       </c>
-      <c r="B674" s="4">
+      <c r="B674" s="2">
         <v>220</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A675" s="3">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A675" s="1">
         <v>92823</v>
       </c>
-      <c r="B675" s="4">
+      <c r="B675" s="2">
         <v>220</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A676" s="3">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A676" s="1">
         <v>92836</v>
       </c>
-      <c r="B676" s="4">
+      <c r="B676" s="2">
         <v>300</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A677" s="3">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A677" s="1">
         <v>92959</v>
       </c>
-      <c r="B677" s="4">
+      <c r="B677" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A678" s="3">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A678" s="1">
         <v>92962</v>
       </c>
-      <c r="B678" s="4">
+      <c r="B678" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A679" s="3">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A679" s="1">
         <v>92968</v>
       </c>
-      <c r="B679" s="4">
+      <c r="B679" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A680" s="3">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A680" s="1">
         <v>92984</v>
       </c>
-      <c r="B680" s="4">
+      <c r="B680" s="2">
         <v>250</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A681" s="3">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A681" s="1">
         <v>93016</v>
       </c>
-      <c r="B681" s="4">
+      <c r="B681" s="2">
         <v>756</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A682" s="3">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A682" s="1">
         <v>93067</v>
       </c>
-      <c r="B682" s="4">
+      <c r="B682" s="2">
         <v>1024</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A683" s="3">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A683" s="1">
         <v>93073</v>
       </c>
-      <c r="B683" s="4">
+      <c r="B683" s="2">
         <v>1370</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A684" s="3">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A684" s="1">
         <v>94314</v>
       </c>
-      <c r="B684" s="4">
+      <c r="B684" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A685" s="3">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A685" s="1">
         <v>94317</v>
       </c>
-      <c r="B685" s="4">
+      <c r="B685" s="2">
         <v>2456</v>
       </c>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A686" s="3">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A686" s="1">
         <v>94683</v>
       </c>
-      <c r="B686" s="4">
+      <c r="B686" s="2">
         <v>249</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A687" s="3">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A687" s="1">
         <v>94821</v>
       </c>
-      <c r="B687" s="4">
+      <c r="B687" s="2">
         <v>1014</v>
       </c>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A688" s="3">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A688" s="1">
         <v>94830</v>
       </c>
-      <c r="B688" s="4">
+      <c r="B688" s="2">
         <v>1042</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A689" s="3">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A689" s="1">
         <v>94835</v>
       </c>
-      <c r="B689" s="4">
+      <c r="B689" s="2">
         <v>866</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A690" s="3">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A690" s="1">
         <v>95202</v>
       </c>
-      <c r="B690" s="4">
+      <c r="B690" s="2">
         <v>302</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A691" s="3">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A691" s="1">
         <v>95211</v>
       </c>
-      <c r="B691" s="4">
+      <c r="B691" s="2">
         <v>398</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A692" s="3">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A692" s="1">
         <v>95536</v>
       </c>
-      <c r="B692" s="4">
+      <c r="B692" s="2">
         <v>1228</v>
       </c>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A693" s="3">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A693" s="1">
         <v>95538</v>
       </c>
-      <c r="B693" s="4">
+      <c r="B693" s="2">
         <v>1282</v>
       </c>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A694" s="3">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A694" s="1">
         <v>95715</v>
       </c>
-      <c r="B694" s="4">
+      <c r="B694" s="2">
         <v>2080</v>
       </c>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A695" s="3">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A695" s="1">
         <v>95731</v>
       </c>
-      <c r="B695" s="4">
+      <c r="B695" s="2">
         <v>528</v>
       </c>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A696" s="3">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A696" s="1">
         <v>95732</v>
       </c>
-      <c r="B696" s="4">
+      <c r="B696" s="2">
         <v>900</v>
       </c>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A697" s="3">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A697" s="1">
         <v>95739</v>
       </c>
-      <c r="B697" s="4">
+      <c r="B697" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A698" s="3">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A698" s="1">
         <v>95740</v>
       </c>
-      <c r="B698" s="4">
+      <c r="B698" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A699" s="3">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A699" s="1">
         <v>95741</v>
       </c>
-      <c r="B699" s="4">
+      <c r="B699" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A700" s="3">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A700" s="1">
         <v>95765</v>
       </c>
-      <c r="B700" s="4">
+      <c r="B700" s="2">
         <v>634</v>
       </c>
     </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A701" s="3">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A701" s="1">
         <v>95768</v>
       </c>
-      <c r="B701" s="4">
+      <c r="B701" s="2">
         <v>534</v>
       </c>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A702" s="3">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A702" s="1">
         <v>95769</v>
       </c>
-      <c r="B702" s="4">
+      <c r="B702" s="2">
         <v>1158</v>
       </c>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A703" s="3">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A703" s="1">
         <v>95770</v>
       </c>
-      <c r="B703" s="4">
+      <c r="B703" s="2">
         <v>488</v>
       </c>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A704" s="3">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A704" s="1">
         <v>95772</v>
       </c>
-      <c r="B704" s="4">
+      <c r="B704" s="2">
         <v>508</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A705" s="3">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A705" s="1">
         <v>95774</v>
       </c>
-      <c r="B705" s="4">
+      <c r="B705" s="2">
         <v>636</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A706" s="3">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A706" s="1">
         <v>95781</v>
       </c>
-      <c r="B706" s="4">
+      <c r="B706" s="2">
         <v>666</v>
       </c>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A707" s="3">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A707" s="1">
         <v>95887</v>
       </c>
-      <c r="B707" s="4">
+      <c r="B707" s="2">
         <v>172</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A708" s="3">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A708" s="1">
         <v>95907</v>
       </c>
-      <c r="B708" s="4">
+      <c r="B708" s="2">
         <v>192</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A709" s="3">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A709" s="1">
         <v>95911</v>
       </c>
-      <c r="B709" s="4">
+      <c r="B709" s="2">
         <v>466</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A710" s="3">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A710" s="1">
         <v>96507</v>
       </c>
-      <c r="B710" s="4">
+      <c r="B710" s="2">
         <v>526</v>
       </c>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A711" s="3">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A711" s="1">
         <v>96508</v>
       </c>
-      <c r="B711" s="4">
+      <c r="B711" s="2">
         <v>968</v>
       </c>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A712" s="3">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A712" s="1">
         <v>96510</v>
       </c>
-      <c r="B712" s="4">
+      <c r="B712" s="2">
         <v>446</v>
       </c>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A713" s="3">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A713" s="1">
         <v>96517</v>
       </c>
-      <c r="B713" s="4">
+      <c r="B713" s="2">
         <v>334</v>
       </c>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A714" s="3">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A714" s="1">
         <v>96539</v>
       </c>
-      <c r="B714" s="4">
+      <c r="B714" s="2">
         <v>1168</v>
       </c>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A715" s="3">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A715" s="1">
         <v>96611</v>
       </c>
-      <c r="B715" s="4">
+      <c r="B715" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A716" s="3">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A716" s="1">
         <v>97700</v>
       </c>
-      <c r="B716" s="4">
+      <c r="B716" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A717" s="3">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A717" s="1">
         <v>97701</v>
       </c>
-      <c r="B717" s="4">
+      <c r="B717" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A718" s="3">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A718" s="1">
         <v>97702</v>
       </c>
-      <c r="B718" s="4">
+      <c r="B718" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A719" s="3">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A719" s="1">
         <v>97703</v>
       </c>
-      <c r="B719" s="4">
+      <c r="B719" s="2">
         <v>112</v>
       </c>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A720" s="3">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A720" s="1">
         <v>97705</v>
       </c>
-      <c r="B720" s="4">
+      <c r="B720" s="2">
         <v>58</v>
       </c>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A721" s="3">
+    <row r="721" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A721" s="1">
         <v>97706</v>
       </c>
-      <c r="B721" s="4">
+      <c r="B721" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A722" s="3">
+    <row r="722" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A722" s="1">
         <v>97707</v>
       </c>
-      <c r="B722" s="4">
+      <c r="B722" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A723" s="3">
+    <row r="723" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A723" s="1">
         <v>97708</v>
       </c>
-      <c r="B723" s="4">
+      <c r="B723" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A724" s="3">
+    <row r="724" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A724" s="1">
         <v>97709</v>
       </c>
-      <c r="B724" s="4">
+      <c r="B724" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A725" s="3">
+    <row r="725" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A725" s="1">
         <v>97710</v>
       </c>
-      <c r="B725" s="4">
+      <c r="B725" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A726" s="3">
+    <row r="726" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A726" s="1">
         <v>97711</v>
       </c>
-      <c r="B726" s="4">
+      <c r="B726" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A727" s="3">
+    <row r="727" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A727" s="1">
         <v>97712</v>
       </c>
-      <c r="B727" s="4">
+      <c r="B727" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A728" s="3">
+    <row r="728" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A728" s="1">
         <v>97713</v>
       </c>
-      <c r="B728" s="4">
+      <c r="B728" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A729" s="3">
+    <row r="729" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A729" s="1">
         <v>97714</v>
       </c>
-      <c r="B729" s="4">
+      <c r="B729" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A730" s="3">
+    <row r="730" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A730" s="1">
         <v>97715</v>
       </c>
-      <c r="B730" s="4">
+      <c r="B730" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A731" s="3">
+    <row r="731" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A731" s="1">
         <v>97717</v>
       </c>
-      <c r="B731" s="4">
+      <c r="B731" s="2">
         <v>136</v>
       </c>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A732" s="3">
+    <row r="732" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A732" s="1">
         <v>97718</v>
       </c>
-      <c r="B732" s="4">
+      <c r="B732" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A733" s="3">
+    <row r="733" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A733" s="1">
         <v>97720</v>
       </c>
-      <c r="B733" s="4">
+      <c r="B733" s="2">
         <v>136</v>
       </c>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A734" s="3">
+    <row r="734" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A734" s="1">
         <v>97721</v>
       </c>
-      <c r="B734" s="4">
+      <c r="B734" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A735" s="3">
+    <row r="735" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A735" s="1">
         <v>97722</v>
       </c>
-      <c r="B735" s="4">
+      <c r="B735" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A736" s="3">
+    <row r="736" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A736" s="1">
         <v>97723</v>
       </c>
-      <c r="B736" s="4">
+      <c r="B736" s="2">
         <v>116</v>
       </c>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A737" s="3">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A737" s="1">
         <v>97724</v>
       </c>
-      <c r="B737" s="4">
+      <c r="B737" s="2">
         <v>86</v>
       </c>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A738" s="3">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A738" s="1">
         <v>97725</v>
       </c>
-      <c r="B738" s="4">
+      <c r="B738" s="2">
         <v>86</v>
       </c>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A739" s="3">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A739" s="1">
         <v>97726</v>
       </c>
-      <c r="B739" s="4">
+      <c r="B739" s="2">
         <v>66</v>
       </c>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A740" s="3">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A740" s="1">
         <v>97727</v>
       </c>
-      <c r="B740" s="4">
+      <c r="B740" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A741" s="3">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A741" s="1">
         <v>97728</v>
       </c>
-      <c r="B741" s="4">
+      <c r="B741" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A742" s="3">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A742" s="1">
         <v>97731</v>
       </c>
-      <c r="B742" s="4">
+      <c r="B742" s="2">
         <v>104</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A743" s="3">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A743" s="1">
         <v>97732</v>
       </c>
-      <c r="B743" s="4">
+      <c r="B743" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A744" s="3">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A744" s="1">
         <v>97733</v>
       </c>
-      <c r="B744" s="4">
+      <c r="B744" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A745" s="3">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A745" s="1">
         <v>97734</v>
       </c>
-      <c r="B745" s="4">
+      <c r="B745" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A746" s="3">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A746" s="1">
         <v>97735</v>
       </c>
-      <c r="B746" s="4">
+      <c r="B746" s="2">
         <v>98</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A747" s="3">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A747" s="1">
         <v>97736</v>
       </c>
-      <c r="B747" s="4">
+      <c r="B747" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A748" s="3">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A748" s="1">
         <v>97737</v>
       </c>
-      <c r="B748" s="4">
+      <c r="B748" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A749" s="3">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A749" s="1">
         <v>97738</v>
       </c>
-      <c r="B749" s="4">
+      <c r="B749" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A750" s="3">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A750" s="1">
         <v>97741</v>
       </c>
-      <c r="B750" s="4">
+      <c r="B750" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A751" s="3">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A751" s="1">
         <v>97742</v>
       </c>
-      <c r="B751" s="4">
+      <c r="B751" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A752" s="3">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A752" s="1">
         <v>97743</v>
       </c>
-      <c r="B752" s="4">
+      <c r="B752" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A753" s="3">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A753" s="1">
         <v>97744</v>
       </c>
-      <c r="B753" s="4">
+      <c r="B753" s="2">
         <v>96</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A754" s="3">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A754" s="1">
         <v>97745</v>
       </c>
-      <c r="B754" s="4">
+      <c r="B754" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A755" s="3">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A755" s="1">
         <v>97746</v>
       </c>
-      <c r="B755" s="4">
+      <c r="B755" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A756" s="3">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A756" s="1">
         <v>97747</v>
       </c>
-      <c r="B756" s="4">
+      <c r="B756" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A757" s="3">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A757" s="1">
         <v>97748</v>
       </c>
-      <c r="B757" s="4">
+      <c r="B757" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A758" s="3">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A758" s="1">
         <v>97749</v>
       </c>
-      <c r="B758" s="4">
+      <c r="B758" s="2">
         <v>62</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A759" s="3">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A759" s="1">
         <v>97750</v>
       </c>
-      <c r="B759" s="4">
+      <c r="B759" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A760" s="3">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A760" s="1">
         <v>97752</v>
       </c>
-      <c r="B760" s="4">
+      <c r="B760" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A761" s="3">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A761" s="1">
         <v>97754</v>
       </c>
-      <c r="B761" s="4">
+      <c r="B761" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A762" s="3">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A762" s="1">
         <v>97755</v>
       </c>
-      <c r="B762" s="4">
+      <c r="B762" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A763" s="3">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A763" s="1">
         <v>97756</v>
       </c>
-      <c r="B763" s="4">
+      <c r="B763" s="2">
         <v>142</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A764" s="3">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A764" s="1">
         <v>97757</v>
       </c>
-      <c r="B764" s="4">
+      <c r="B764" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A765" s="3">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A765" s="1">
         <v>97758</v>
       </c>
-      <c r="B765" s="4">
+      <c r="B765" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A766" s="3">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A766" s="1">
         <v>97761</v>
       </c>
-      <c r="B766" s="4">
+      <c r="B766" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A767" s="3">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A767" s="1">
         <v>97764</v>
       </c>
-      <c r="B767" s="4">
+      <c r="B767" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A768" s="3">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A768" s="1">
         <v>97765</v>
       </c>
-      <c r="B768" s="4">
+      <c r="B768" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A769" s="3">
+    <row r="769" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A769" s="1">
         <v>97767</v>
       </c>
-      <c r="B769" s="4">
+      <c r="B769" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A770" s="3">
+    <row r="770" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A770" s="1">
         <v>97768</v>
       </c>
-      <c r="B770" s="4">
+      <c r="B770" s="2">
         <v>150</v>
       </c>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A771" s="3">
+    <row r="771" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A771" s="1">
         <v>97770</v>
       </c>
-      <c r="B771" s="4">
+      <c r="B771" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A772" s="3">
+    <row r="772" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A772" s="1">
         <v>97771</v>
       </c>
-      <c r="B772" s="4">
+      <c r="B772" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A773" s="3">
+    <row r="773" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A773" s="1">
         <v>97773</v>
       </c>
-      <c r="B773" s="4">
+      <c r="B773" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A774" s="3">
+    <row r="774" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A774" s="1">
         <v>97774</v>
       </c>
-      <c r="B774" s="4">
+      <c r="B774" s="2">
         <v>64</v>
       </c>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A775" s="3">
+    <row r="775" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A775" s="1">
         <v>97775</v>
       </c>
-      <c r="B775" s="4">
+      <c r="B775" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A776" s="3">
+    <row r="776" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A776" s="1">
         <v>97776</v>
       </c>
-      <c r="B776" s="4">
+      <c r="B776" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A777" s="3">
+    <row r="777" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A777" s="1">
         <v>97777</v>
       </c>
-      <c r="B777" s="4">
+      <c r="B777" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A778" s="3">
+    <row r="778" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A778" s="1">
         <v>97780</v>
       </c>
-      <c r="B778" s="4">
+      <c r="B778" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A779" s="3">
+    <row r="779" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A779" s="1">
         <v>97781</v>
       </c>
-      <c r="B779" s="4">
+      <c r="B779" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A780" s="3">
+    <row r="780" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A780" s="1">
         <v>97783</v>
       </c>
-      <c r="B780" s="4">
+      <c r="B780" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A781" s="3">
+    <row r="781" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A781" s="1">
         <v>97784</v>
       </c>
-      <c r="B781" s="4">
+      <c r="B781" s="2">
         <v>108</v>
       </c>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A782" s="3">
+    <row r="782" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A782" s="1">
         <v>97785</v>
       </c>
-      <c r="B782" s="4">
+      <c r="B782" s="2">
         <v>124</v>
       </c>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A783" s="3">
+    <row r="783" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A783" s="1">
         <v>97787</v>
       </c>
-      <c r="B783" s="4">
+      <c r="B783" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A784" s="3">
+    <row r="784" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A784" s="1">
         <v>97788</v>
       </c>
-      <c r="B784" s="4">
+      <c r="B784" s="2">
         <v>158</v>
       </c>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A785" s="3">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A785" s="1">
         <v>97789</v>
       </c>
-      <c r="B785" s="4">
+      <c r="B785" s="2">
         <v>102</v>
       </c>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A786" s="3">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A786" s="1">
         <v>97790</v>
       </c>
-      <c r="B786" s="4">
+      <c r="B786" s="2">
         <v>126</v>
       </c>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A787" s="3">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A787" s="1">
         <v>97791</v>
       </c>
-      <c r="B787" s="4">
+      <c r="B787" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A788" s="3">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A788" s="1">
         <v>97792</v>
       </c>
-      <c r="B788" s="4">
+      <c r="B788" s="2">
         <v>114</v>
       </c>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A789" s="3">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A789" s="1">
         <v>97793</v>
       </c>
-      <c r="B789" s="4">
+      <c r="B789" s="2">
         <v>112</v>
       </c>
     </row>

--- a/assets/Items_for_Replenishment.xlsx
+++ b/assets/Items_for_Replenishment.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F6234B-44D5-4D94-94DE-AFD351EDCDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{16F6234B-44D5-4D94-94DE-AFD351EDCDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC57D7B9-1BAC-4361-AB3F-D0AC315D0514}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Items!$A$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -95,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -108,6 +121,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -413,10 +438,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B789"/>
+  <dimension ref="A1:B961"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -429,551 +455,551 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>72760</v>
+        <v>46496</v>
       </c>
       <c r="B2" s="2">
-        <v>2</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>74532</v>
+        <v>55847</v>
       </c>
       <c r="B3" s="2">
-        <v>1344</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>76560</v>
+        <v>68563</v>
       </c>
       <c r="B4" s="2">
-        <v>626</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>82379</v>
+        <v>74532</v>
       </c>
       <c r="B5" s="2">
-        <v>2</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>84662</v>
+        <v>76560</v>
       </c>
       <c r="B6" s="2">
-        <v>10</v>
+        <v>598</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>86979</v>
+        <v>78699</v>
       </c>
       <c r="B7" s="2">
-        <v>968</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>87154</v>
+        <v>80815</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>87813</v>
+        <v>82379</v>
       </c>
       <c r="B9" s="2">
-        <v>506</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>87814</v>
+        <v>82595</v>
       </c>
       <c r="B10" s="2">
-        <v>8</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>87844</v>
+        <v>84559</v>
       </c>
       <c r="B11" s="2">
-        <v>42</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>87855</v>
+        <v>84662</v>
       </c>
       <c r="B12" s="2">
-        <v>210</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>88478</v>
+        <v>86979</v>
       </c>
       <c r="B13" s="2">
-        <v>210</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>88571</v>
+        <v>87151</v>
       </c>
       <c r="B14" s="2">
-        <v>394</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>88810</v>
+        <v>87154</v>
       </c>
       <c r="B15" s="2">
-        <v>658</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>90828</v>
+        <v>87813</v>
       </c>
       <c r="B16" s="2">
-        <v>310</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>90829</v>
+        <v>87814</v>
       </c>
       <c r="B17" s="2">
-        <v>540</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>90830</v>
+        <v>87844</v>
       </c>
       <c r="B18" s="2">
-        <v>4371</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>90831</v>
+        <v>88245</v>
       </c>
       <c r="B19" s="2">
-        <v>700</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>91015</v>
+        <v>88478</v>
       </c>
       <c r="B20" s="2">
-        <v>400</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>91101</v>
+        <v>88571</v>
       </c>
       <c r="B21" s="2">
-        <v>2</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>92425</v>
+        <v>88609</v>
       </c>
       <c r="B22" s="2">
-        <v>904</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>92688</v>
+        <v>88810</v>
       </c>
       <c r="B23" s="2">
-        <v>1118</v>
+        <v>624</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>92728</v>
+        <v>89952</v>
       </c>
       <c r="B24" s="2">
-        <v>910</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>92730</v>
+        <v>90828</v>
       </c>
       <c r="B25" s="2">
-        <v>1420</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>92731</v>
+        <v>90829</v>
       </c>
       <c r="B26" s="2">
-        <v>1310</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>93165</v>
+        <v>90830</v>
       </c>
       <c r="B27" s="2">
-        <v>58</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>93286</v>
+        <v>90831</v>
       </c>
       <c r="B28" s="2">
-        <v>178</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>93307</v>
+        <v>91015</v>
       </c>
       <c r="B29" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>93329</v>
+        <v>91290</v>
       </c>
       <c r="B30" s="2">
-        <v>2668</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>93332</v>
+        <v>92425</v>
       </c>
       <c r="B31" s="2">
-        <v>600</v>
+        <v>686</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>93333</v>
+        <v>92688</v>
       </c>
       <c r="B32" s="2">
-        <v>1906</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>94076</v>
+        <v>92725</v>
       </c>
       <c r="B33" s="2">
-        <v>2006</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>94319</v>
+        <v>92728</v>
       </c>
       <c r="B34" s="2">
-        <v>200</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>94320</v>
+        <v>92730</v>
       </c>
       <c r="B35" s="2">
-        <v>940</v>
+        <v>640</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>94321</v>
+        <v>92731</v>
       </c>
       <c r="B36" s="2">
-        <v>270</v>
+        <v>970</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>94322</v>
+        <v>93286</v>
       </c>
       <c r="B37" s="2">
-        <v>1050</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>94425</v>
+        <v>93311</v>
       </c>
       <c r="B38" s="2">
-        <v>264</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>94916</v>
+        <v>93329</v>
       </c>
       <c r="B39" s="2">
-        <v>3956</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>94917</v>
+        <v>93332</v>
       </c>
       <c r="B40" s="2">
-        <v>3594</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>95947</v>
+        <v>93333</v>
       </c>
       <c r="B41" s="2">
-        <v>2724</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>96269</v>
+        <v>94076</v>
       </c>
       <c r="B42" s="2">
-        <v>6</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>96893</v>
+        <v>94319</v>
       </c>
       <c r="B43" s="2">
-        <v>106</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>96894</v>
+        <v>94320</v>
       </c>
       <c r="B44" s="2">
-        <v>74</v>
+        <v>650</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>96901</v>
+        <v>94321</v>
       </c>
       <c r="B45" s="2">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>96933</v>
+        <v>94322</v>
       </c>
       <c r="B46" s="2">
-        <v>4</v>
+        <v>970</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>97517</v>
+        <v>94916</v>
       </c>
       <c r="B47" s="2">
-        <v>12</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>97518</v>
+        <v>94917</v>
       </c>
       <c r="B48" s="2">
-        <v>4</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>97525</v>
+        <v>95677</v>
       </c>
       <c r="B49" s="2">
-        <v>130</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>97526</v>
+        <v>95815</v>
       </c>
       <c r="B50" s="2">
-        <v>220</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>97527</v>
+        <v>95947</v>
       </c>
       <c r="B51" s="2">
-        <v>244</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>97528</v>
+        <v>96269</v>
       </c>
       <c r="B52" s="2">
-        <v>216</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>97529</v>
+        <v>96893</v>
       </c>
       <c r="B53" s="2">
-        <v>144</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>97530</v>
+        <v>96894</v>
       </c>
       <c r="B54" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>97534</v>
+        <v>96901</v>
       </c>
       <c r="B55" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>97538</v>
+        <v>97525</v>
       </c>
       <c r="B56" s="2">
-        <v>4</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>97540</v>
+        <v>97526</v>
       </c>
       <c r="B57" s="2">
-        <v>6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>97543</v>
+        <v>97527</v>
       </c>
       <c r="B58" s="2">
-        <v>76</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>97544</v>
+        <v>97529</v>
       </c>
       <c r="B59" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>97545</v>
+        <v>97543</v>
       </c>
       <c r="B60" s="2">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>97546</v>
+        <v>97544</v>
       </c>
       <c r="B61" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>97547</v>
+        <v>97545</v>
       </c>
       <c r="B62" s="2">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>97610</v>
+        <v>97546</v>
       </c>
       <c r="B63" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>97612</v>
+        <v>97547</v>
       </c>
       <c r="B64" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>97614</v>
+        <v>97610</v>
       </c>
       <c r="B65" s="2">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>97617</v>
+        <v>97618</v>
       </c>
       <c r="B66" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>97630</v>
+        <v>97631</v>
       </c>
       <c r="B67" s="2">
-        <v>80</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>97631</v>
+        <v>97669</v>
       </c>
       <c r="B68" s="2">
-        <v>88</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>97632</v>
+        <v>97678</v>
       </c>
       <c r="B69" s="2">
-        <v>82</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>97650</v>
+        <v>97680</v>
       </c>
       <c r="B70" s="2">
         <v>2</v>
@@ -981,50 +1007,50 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>97668</v>
+        <v>97690</v>
       </c>
       <c r="B71" s="2">
-        <v>84</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>97669</v>
+        <v>97691</v>
       </c>
       <c r="B72" s="2">
-        <v>8</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>97676</v>
+        <v>97696</v>
       </c>
       <c r="B73" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>97678</v>
+        <v>97699</v>
       </c>
       <c r="B74" s="2">
-        <v>2</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>97680</v>
+        <v>97889</v>
       </c>
       <c r="B75" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>97888</v>
+        <v>97892</v>
       </c>
       <c r="B76" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -1032,7 +1058,7 @@
         <v>98211</v>
       </c>
       <c r="B77" s="2">
-        <v>3050</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -1040,7 +1066,7 @@
         <v>98212</v>
       </c>
       <c r="B78" s="2">
-        <v>2990</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -1048,812 +1074,812 @@
         <v>98213</v>
       </c>
       <c r="B79" s="2">
-        <v>2990</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>98600</v>
+        <v>98405</v>
       </c>
       <c r="B80" s="2">
-        <v>550</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>98601</v>
+        <v>98406</v>
       </c>
       <c r="B81" s="2">
-        <v>600</v>
+        <v>62</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>98602</v>
+        <v>98408</v>
       </c>
       <c r="B82" s="2">
-        <v>600</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>98657</v>
+        <v>98409</v>
       </c>
       <c r="B83" s="2">
-        <v>750</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>460</v>
+        <v>98417</v>
       </c>
       <c r="B84" s="2">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>3764</v>
+        <v>98418</v>
       </c>
       <c r="B85" s="2">
-        <v>576</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>3775</v>
+        <v>98419</v>
       </c>
       <c r="B86" s="2">
-        <v>2262</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>3780</v>
+        <v>98420</v>
       </c>
       <c r="B87" s="2">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>3786</v>
+        <v>98421</v>
       </c>
       <c r="B88" s="2">
-        <v>342</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>3798</v>
+        <v>98422</v>
       </c>
       <c r="B89" s="2">
-        <v>180</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>3809</v>
+        <v>98423</v>
       </c>
       <c r="B90" s="2">
-        <v>792</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>3817</v>
+        <v>98424</v>
       </c>
       <c r="B91" s="2">
-        <v>324</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>3821</v>
+        <v>98430</v>
       </c>
       <c r="B92" s="2">
-        <v>774</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>3827</v>
+        <v>98432</v>
       </c>
       <c r="B93" s="2">
-        <v>216</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>3833</v>
+        <v>98600</v>
       </c>
       <c r="B94" s="2">
-        <v>1656</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>36371</v>
+        <v>98601</v>
       </c>
       <c r="B95" s="2">
-        <v>2108</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>38326</v>
+        <v>98602</v>
       </c>
       <c r="B96" s="2">
-        <v>264</v>
+        <v>490</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>59296</v>
+        <v>98657</v>
       </c>
       <c r="B97" s="2">
-        <v>300</v>
+        <v>510</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>68947</v>
+        <v>98658</v>
       </c>
       <c r="B98" s="2">
-        <v>2256</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>68948</v>
+        <v>99392</v>
       </c>
       <c r="B99" s="2">
-        <v>528</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>68949</v>
+        <v>99393</v>
       </c>
       <c r="B100" s="2">
-        <v>816</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>68950</v>
+        <v>99394</v>
       </c>
       <c r="B101" s="2">
-        <v>528</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>68952</v>
+        <v>99395</v>
       </c>
       <c r="B102" s="2">
-        <v>552</v>
+        <v>141</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>68953</v>
+        <v>3764</v>
       </c>
       <c r="B103" s="2">
-        <v>576</v>
+        <v>324</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>68954</v>
+        <v>3775</v>
       </c>
       <c r="B104" s="2">
-        <v>528</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>68955</v>
+        <v>3786</v>
       </c>
       <c r="B105" s="2">
-        <v>816</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>68956</v>
+        <v>3798</v>
       </c>
       <c r="B106" s="2">
-        <v>528</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>68957</v>
+        <v>3809</v>
       </c>
       <c r="B107" s="2">
-        <v>528</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>68958</v>
+        <v>3821</v>
       </c>
       <c r="B108" s="2">
-        <v>852</v>
+        <v>576</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>68959</v>
+        <v>3833</v>
       </c>
       <c r="B109" s="2">
-        <v>576</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>68960</v>
+        <v>16472</v>
       </c>
       <c r="B110" s="2">
-        <v>576</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>70451</v>
+        <v>36371</v>
       </c>
       <c r="B111" s="2">
-        <v>3870</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>72604</v>
+        <v>38326</v>
       </c>
       <c r="B112" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>73723</v>
+        <v>54955</v>
       </c>
       <c r="B113" s="2">
-        <v>1284</v>
+        <v>864</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>74359</v>
+        <v>59296</v>
       </c>
       <c r="B114" s="2">
-        <v>1278</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>83192</v>
+        <v>68947</v>
       </c>
       <c r="B115" s="2">
-        <v>144</v>
+        <v>690</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>97514</v>
+        <v>68950</v>
       </c>
       <c r="B116" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>97515</v>
+        <v>68956</v>
       </c>
       <c r="B117" s="2">
-        <v>156</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>6881</v>
+        <v>68959</v>
       </c>
       <c r="B118" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>9858</v>
+        <v>70451</v>
       </c>
       <c r="B119" s="2">
-        <v>140</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>9859</v>
+        <v>73723</v>
       </c>
       <c r="B120" s="2">
-        <v>363</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>9963</v>
+        <v>74359</v>
       </c>
       <c r="B121" s="2">
-        <v>492</v>
+        <v>864</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>16075</v>
+        <v>97512</v>
       </c>
       <c r="B122" s="2">
-        <v>316</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>66614</v>
+        <v>98426</v>
       </c>
       <c r="B123" s="2">
-        <v>250</v>
+        <v>134</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>66615</v>
+        <v>98427</v>
       </c>
       <c r="B124" s="2">
-        <v>37</v>
+        <v>312</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>66616</v>
+        <v>6881</v>
       </c>
       <c r="B125" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>68877</v>
+        <v>9858</v>
       </c>
       <c r="B126" s="2">
-        <v>102</v>
+        <v>33</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>68878</v>
+        <v>9859</v>
       </c>
       <c r="B127" s="2">
-        <v>315</v>
+        <v>210</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>68879</v>
+        <v>9963</v>
       </c>
       <c r="B128" s="2">
-        <v>450</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>68880</v>
+        <v>16075</v>
       </c>
       <c r="B129" s="2">
-        <v>316</v>
+        <v>278</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>80319</v>
+        <v>66615</v>
       </c>
       <c r="B130" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>84851</v>
+        <v>66616</v>
       </c>
       <c r="B131" s="2">
-        <v>498</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>84852</v>
+        <v>68877</v>
       </c>
       <c r="B132" s="2">
-        <v>533</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>84853</v>
+        <v>68878</v>
       </c>
       <c r="B133" s="2">
-        <v>364</v>
+        <v>183</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>84854</v>
+        <v>68879</v>
       </c>
       <c r="B134" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>84855</v>
+        <v>68880</v>
       </c>
       <c r="B135" s="2">
-        <v>321</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>85743</v>
+        <v>80319</v>
       </c>
       <c r="B136" s="2">
-        <v>360</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>85744</v>
+        <v>84851</v>
       </c>
       <c r="B137" s="2">
-        <v>14</v>
+        <v>371</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>86015</v>
+        <v>84852</v>
       </c>
       <c r="B138" s="2">
-        <v>270</v>
+        <v>355</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>86016</v>
+        <v>84853</v>
       </c>
       <c r="B139" s="2">
-        <v>106</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>86265</v>
+        <v>84854</v>
       </c>
       <c r="B140" s="2">
-        <v>445</v>
+        <v>312</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>86266</v>
+        <v>84855</v>
       </c>
       <c r="B141" s="2">
-        <v>683</v>
+        <v>250</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>86267</v>
+        <v>85743</v>
       </c>
       <c r="B142" s="2">
-        <v>38</v>
+        <v>321</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>86268</v>
+        <v>86015</v>
       </c>
       <c r="B143" s="2">
-        <v>541</v>
+        <v>209</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>86269</v>
+        <v>86016</v>
       </c>
       <c r="B144" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>86285</v>
+        <v>86265</v>
       </c>
       <c r="B145" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>86286</v>
+        <v>86266</v>
       </c>
       <c r="B146" s="2">
-        <v>776</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>86287</v>
+        <v>86267</v>
       </c>
       <c r="B147" s="2">
-        <v>802</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>86288</v>
+        <v>86268</v>
       </c>
       <c r="B148" s="2">
-        <v>578</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>86289</v>
+        <v>86269</v>
       </c>
       <c r="B149" s="2">
-        <v>321</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>87346</v>
+        <v>86285</v>
       </c>
       <c r="B150" s="2">
-        <v>307</v>
+        <v>59</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>87406</v>
+        <v>86286</v>
       </c>
       <c r="B151" s="2">
-        <v>1</v>
+        <v>623</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>87408</v>
+        <v>86287</v>
       </c>
       <c r="B152" s="2">
-        <v>38</v>
+        <v>660</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>87410</v>
+        <v>86288</v>
       </c>
       <c r="B153" s="2">
-        <v>13</v>
+        <v>493</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>87416</v>
+        <v>86289</v>
       </c>
       <c r="B154" s="2">
-        <v>584</v>
+        <v>237</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>87417</v>
+        <v>87346</v>
       </c>
       <c r="B155" s="2">
-        <v>403</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>87418</v>
+        <v>87406</v>
       </c>
       <c r="B156" s="2">
-        <v>89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>87419</v>
+        <v>87408</v>
       </c>
       <c r="B157" s="2">
-        <v>176</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>87420</v>
+        <v>87416</v>
       </c>
       <c r="B158" s="2">
-        <v>44</v>
+        <v>391</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>87882</v>
+        <v>87417</v>
       </c>
       <c r="B159" s="2">
-        <v>748</v>
+        <v>225</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>87883</v>
+        <v>87418</v>
       </c>
       <c r="B160" s="2">
-        <v>518</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>87884</v>
+        <v>87419</v>
       </c>
       <c r="B161" s="2">
-        <v>170</v>
+        <v>59</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>87885</v>
+        <v>87882</v>
       </c>
       <c r="B162" s="2">
-        <v>198</v>
+        <v>723</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>87886</v>
+        <v>87883</v>
       </c>
       <c r="B163" s="2">
-        <v>207</v>
+        <v>485</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>87932</v>
+        <v>87884</v>
       </c>
       <c r="B164" s="2">
-        <v>963</v>
+        <v>125</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>87934</v>
+        <v>87885</v>
       </c>
       <c r="B165" s="2">
-        <v>707</v>
+        <v>174</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>87937</v>
+        <v>87886</v>
       </c>
       <c r="B166" s="2">
-        <v>657</v>
+        <v>190</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>87938</v>
+        <v>87932</v>
       </c>
       <c r="B167" s="2">
-        <v>864</v>
+        <v>749</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>87939</v>
+        <v>87933</v>
       </c>
       <c r="B168" s="2">
-        <v>513</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>87941</v>
+        <v>87934</v>
       </c>
       <c r="B169" s="2">
-        <v>113</v>
+        <v>503</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>88653</v>
+        <v>87937</v>
       </c>
       <c r="B170" s="2">
-        <v>479</v>
+        <v>507</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>88654</v>
+        <v>87938</v>
       </c>
       <c r="B171" s="2">
-        <v>515</v>
+        <v>724</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>88655</v>
+        <v>87939</v>
       </c>
       <c r="B172" s="2">
-        <v>609</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>88656</v>
+        <v>87941</v>
       </c>
       <c r="B173" s="2">
-        <v>200</v>
+        <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>88657</v>
+        <v>88653</v>
       </c>
       <c r="B174" s="2">
-        <v>124</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>89338</v>
+        <v>88654</v>
       </c>
       <c r="B175" s="2">
-        <v>34</v>
+        <v>480</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>89339</v>
+        <v>88655</v>
       </c>
       <c r="B176" s="2">
-        <v>163</v>
+        <v>576</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>89982</v>
+        <v>88656</v>
       </c>
       <c r="B177" s="2">
-        <v>2</v>
+        <v>170</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>89983</v>
+        <v>88657</v>
       </c>
       <c r="B178" s="2">
-        <v>8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>89984</v>
+        <v>89339</v>
       </c>
       <c r="B179" s="2">
-        <v>80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>89985</v>
+        <v>89986</v>
       </c>
       <c r="B180" s="2">
         <v>1</v>
@@ -1861,615 +1887,615 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>89986</v>
+        <v>90566</v>
       </c>
       <c r="B181" s="2">
-        <v>18</v>
+        <v>544</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>90566</v>
+        <v>90567</v>
       </c>
       <c r="B182" s="2">
-        <v>684</v>
+        <v>34</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>90567</v>
+        <v>90568</v>
       </c>
       <c r="B183" s="2">
-        <v>185</v>
+        <v>401</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>90568</v>
+        <v>90569</v>
       </c>
       <c r="B184" s="2">
-        <v>480</v>
+        <v>257</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>90569</v>
+        <v>90570</v>
       </c>
       <c r="B185" s="2">
-        <v>305</v>
+        <v>212</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>90570</v>
+        <v>90792</v>
       </c>
       <c r="B186" s="2">
-        <v>251</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>90789</v>
+        <v>90922</v>
       </c>
       <c r="B187" s="2">
-        <v>6</v>
+        <v>730</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>90790</v>
+        <v>90923</v>
       </c>
       <c r="B188" s="2">
-        <v>4</v>
+        <v>684</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>90791</v>
+        <v>90924</v>
       </c>
       <c r="B189" s="2">
-        <v>18</v>
+        <v>278</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>90792</v>
+        <v>90925</v>
       </c>
       <c r="B190" s="2">
-        <v>1</v>
+        <v>216</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>90922</v>
+        <v>90926</v>
       </c>
       <c r="B191" s="2">
-        <v>831</v>
+        <v>182</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>90923</v>
+        <v>91208</v>
       </c>
       <c r="B192" s="2">
-        <v>796</v>
+        <v>39</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>90924</v>
+        <v>91209</v>
       </c>
       <c r="B193" s="2">
-        <v>381</v>
+        <v>55</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>90925</v>
+        <v>91279</v>
       </c>
       <c r="B194" s="2">
-        <v>304</v>
+        <v>562</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>90926</v>
+        <v>91280</v>
       </c>
       <c r="B195" s="2">
-        <v>243</v>
+        <v>658</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>91206</v>
+        <v>91765</v>
       </c>
       <c r="B196" s="2">
-        <v>1</v>
+        <v>389</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>91208</v>
+        <v>91766</v>
       </c>
       <c r="B197" s="2">
-        <v>91</v>
+        <v>182</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>91209</v>
+        <v>91769</v>
       </c>
       <c r="B198" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>91279</v>
+        <v>91815</v>
       </c>
       <c r="B199" s="2">
-        <v>654</v>
+        <v>335</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>91280</v>
+        <v>91816</v>
       </c>
       <c r="B200" s="2">
-        <v>747</v>
+        <v>990</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>91281</v>
+        <v>91817</v>
       </c>
       <c r="B201" s="2">
-        <v>3</v>
+        <v>280</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>91765</v>
+        <v>91818</v>
       </c>
       <c r="B202" s="2">
-        <v>791</v>
+        <v>22</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>91766</v>
+        <v>91819</v>
       </c>
       <c r="B203" s="2">
-        <v>545</v>
+        <v>37</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>91768</v>
+        <v>91895</v>
       </c>
       <c r="B204" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>91769</v>
+        <v>92284</v>
       </c>
       <c r="B205" s="2">
-        <v>171</v>
+        <v>29</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>91815</v>
+        <v>92285</v>
       </c>
       <c r="B206" s="2">
-        <v>656</v>
+        <v>131</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>91816</v>
+        <v>92288</v>
       </c>
       <c r="B207" s="2">
-        <v>1225</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>91817</v>
+        <v>92289</v>
       </c>
       <c r="B208" s="2">
-        <v>431</v>
+        <v>936</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>91818</v>
+        <v>92290</v>
       </c>
       <c r="B209" s="2">
-        <v>64</v>
+        <v>611</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>91819</v>
+        <v>92291</v>
       </c>
       <c r="B210" s="2">
-        <v>5</v>
+        <v>461</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>91895</v>
+        <v>92292</v>
       </c>
       <c r="B211" s="2">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>91896</v>
+        <v>92409</v>
       </c>
       <c r="B212" s="2">
-        <v>2</v>
+        <v>307</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>92283</v>
+        <v>92410</v>
       </c>
       <c r="B213" s="2">
-        <v>36</v>
+        <v>391</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>92284</v>
+        <v>92411</v>
       </c>
       <c r="B214" s="2">
-        <v>102</v>
+        <v>264</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>92285</v>
+        <v>92412</v>
       </c>
       <c r="B215" s="2">
-        <v>187</v>
+        <v>406</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>92288</v>
+        <v>92413</v>
       </c>
       <c r="B216" s="2">
-        <v>1156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>92289</v>
+        <v>92542</v>
       </c>
       <c r="B217" s="2">
-        <v>995</v>
+        <v>82</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>92290</v>
+        <v>92591</v>
       </c>
       <c r="B218" s="2">
-        <v>649</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>92291</v>
+        <v>93238</v>
       </c>
       <c r="B219" s="2">
-        <v>484</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>92292</v>
+        <v>93239</v>
       </c>
       <c r="B220" s="2">
-        <v>240</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>92409</v>
+        <v>93240</v>
       </c>
       <c r="B221" s="2">
-        <v>549</v>
+        <v>678</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>92410</v>
+        <v>93241</v>
       </c>
       <c r="B222" s="2">
-        <v>576</v>
+        <v>833</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>92411</v>
+        <v>93242</v>
       </c>
       <c r="B223" s="2">
-        <v>438</v>
+        <v>476</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>92412</v>
+        <v>94139</v>
       </c>
       <c r="B224" s="2">
-        <v>559</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>92413</v>
+        <v>94140</v>
       </c>
       <c r="B225" s="2">
-        <v>246</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>92542</v>
+        <v>94141</v>
       </c>
       <c r="B226" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>92543</v>
+        <v>94142</v>
       </c>
       <c r="B227" s="2">
-        <v>203</v>
+        <v>504</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>92544</v>
+        <v>94143</v>
       </c>
       <c r="B228" s="2">
-        <v>58</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>92545</v>
+        <v>94592</v>
       </c>
       <c r="B229" s="2">
-        <v>16</v>
+        <v>394</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>92546</v>
+        <v>94593</v>
       </c>
       <c r="B230" s="2">
-        <v>58</v>
+        <v>349</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>92590</v>
+        <v>94594</v>
       </c>
       <c r="B231" s="2">
-        <v>1</v>
+        <v>308</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>92591</v>
+        <v>94595</v>
       </c>
       <c r="B232" s="2">
-        <v>2</v>
+        <v>249</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>92592</v>
+        <v>94596</v>
       </c>
       <c r="B233" s="2">
-        <v>4</v>
+        <v>116</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>93238</v>
+        <v>95082</v>
       </c>
       <c r="B234" s="2">
-        <v>1529</v>
+        <v>206</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>93239</v>
+        <v>95083</v>
       </c>
       <c r="B235" s="2">
-        <v>1227</v>
+        <v>185</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>93240</v>
+        <v>95084</v>
       </c>
       <c r="B236" s="2">
-        <v>847</v>
+        <v>53</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>93241</v>
+        <v>95085</v>
       </c>
       <c r="B237" s="2">
-        <v>926</v>
+        <v>60</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>93242</v>
+        <v>95086</v>
       </c>
       <c r="B238" s="2">
-        <v>544</v>
+        <v>38</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>94139</v>
+        <v>95132</v>
       </c>
       <c r="B239" s="2">
-        <v>1760</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>94140</v>
+        <v>95133</v>
       </c>
       <c r="B240" s="2">
-        <v>1942</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>94141</v>
+        <v>95134</v>
       </c>
       <c r="B241" s="2">
-        <v>447</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>94142</v>
+        <v>95135</v>
       </c>
       <c r="B242" s="2">
-        <v>781</v>
+        <v>14</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>94143</v>
+        <v>95136</v>
       </c>
       <c r="B243" s="2">
-        <v>57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>94592</v>
+        <v>95973</v>
       </c>
       <c r="B244" s="2">
-        <v>776</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>94593</v>
+        <v>95976</v>
       </c>
       <c r="B245" s="2">
-        <v>680</v>
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>94594</v>
+        <v>95977</v>
       </c>
       <c r="B246" s="2">
-        <v>548</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>94595</v>
+        <v>96073</v>
       </c>
       <c r="B247" s="2">
-        <v>402</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>94596</v>
+        <v>96085</v>
       </c>
       <c r="B248" s="2">
-        <v>226</v>
+        <v>13</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>95082</v>
+        <v>96086</v>
       </c>
       <c r="B249" s="2">
-        <v>925</v>
+        <v>9</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>95083</v>
+        <v>96087</v>
       </c>
       <c r="B250" s="2">
-        <v>790</v>
+        <v>6</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>95084</v>
+        <v>96095</v>
       </c>
       <c r="B251" s="2">
-        <v>480</v>
+        <v>9</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>95085</v>
+        <v>96096</v>
       </c>
       <c r="B252" s="2">
-        <v>344</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>95086</v>
+        <v>96100</v>
       </c>
       <c r="B253" s="2">
-        <v>315</v>
+        <v>14</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>95973</v>
+        <v>96101</v>
       </c>
       <c r="B254" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>95976</v>
+        <v>96105</v>
       </c>
       <c r="B255" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>95977</v>
+        <v>96107</v>
       </c>
       <c r="B256" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>96073</v>
+        <v>96109</v>
       </c>
       <c r="B257" s="2">
         <v>1</v>
@@ -2477,127 +2503,127 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>96075</v>
+        <v>96114</v>
       </c>
       <c r="B258" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>96083</v>
+        <v>96117</v>
       </c>
       <c r="B259" s="2">
-        <v>64</v>
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>96084</v>
+        <v>96120</v>
       </c>
       <c r="B260" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>96085</v>
+        <v>96121</v>
       </c>
       <c r="B261" s="2">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>96086</v>
+        <v>96122</v>
       </c>
       <c r="B262" s="2">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>96087</v>
+        <v>96123</v>
       </c>
       <c r="B263" s="2">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>96093</v>
+        <v>96124</v>
       </c>
       <c r="B264" s="2">
-        <v>70</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>96094</v>
+        <v>96125</v>
       </c>
       <c r="B265" s="2">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>96095</v>
+        <v>96126</v>
       </c>
       <c r="B266" s="2">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>96096</v>
+        <v>96128</v>
       </c>
       <c r="B267" s="2">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>96097</v>
+        <v>96129</v>
       </c>
       <c r="B268" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>96098</v>
+        <v>96130</v>
       </c>
       <c r="B269" s="2">
-        <v>72</v>
+        <v>17</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>96099</v>
+        <v>96131</v>
       </c>
       <c r="B270" s="2">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>96100</v>
+        <v>96133</v>
       </c>
       <c r="B271" s="2">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>96101</v>
+        <v>96134</v>
       </c>
       <c r="B272" s="2">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>96102</v>
+        <v>96135</v>
       </c>
       <c r="B273" s="2">
         <v>23</v>
@@ -2605,287 +2631,287 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>96103</v>
+        <v>96136</v>
       </c>
       <c r="B274" s="2">
-        <v>70</v>
+        <v>14</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>96104</v>
+        <v>96170</v>
       </c>
       <c r="B275" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>96105</v>
+        <v>96178</v>
       </c>
       <c r="B276" s="2">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>96106</v>
+        <v>96788</v>
       </c>
       <c r="B277" s="2">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>96107</v>
+        <v>96800</v>
       </c>
       <c r="B278" s="2">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>96108</v>
+        <v>96812</v>
       </c>
       <c r="B279" s="2">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>96109</v>
+        <v>96813</v>
       </c>
       <c r="B280" s="2">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>96110</v>
+        <v>96818</v>
       </c>
       <c r="B281" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>96111</v>
+        <v>96819</v>
       </c>
       <c r="B282" s="2">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>96112</v>
+        <v>96821</v>
       </c>
       <c r="B283" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>96113</v>
+        <v>96834</v>
       </c>
       <c r="B284" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>96114</v>
+        <v>97308</v>
       </c>
       <c r="B285" s="2">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>96115</v>
+        <v>97310</v>
       </c>
       <c r="B286" s="2">
-        <v>52</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>96116</v>
+        <v>97312</v>
       </c>
       <c r="B287" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>96117</v>
+        <v>97319</v>
       </c>
       <c r="B288" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>96118</v>
+        <v>97324</v>
       </c>
       <c r="B289" s="2">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>96119</v>
+        <v>97327</v>
       </c>
       <c r="B290" s="2">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>96120</v>
+        <v>97330</v>
       </c>
       <c r="B291" s="2">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>96121</v>
+        <v>97343</v>
       </c>
       <c r="B292" s="2">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>96122</v>
+        <v>97346</v>
       </c>
       <c r="B293" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
-        <v>96123</v>
+        <v>97348</v>
       </c>
       <c r="B294" s="2">
-        <v>80</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
-        <v>96124</v>
+        <v>97352</v>
       </c>
       <c r="B295" s="2">
-        <v>82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
-        <v>96125</v>
+        <v>97353</v>
       </c>
       <c r="B296" s="2">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
-        <v>96126</v>
+        <v>97354</v>
       </c>
       <c r="B297" s="2">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
-        <v>96127</v>
+        <v>97355</v>
       </c>
       <c r="B298" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
-        <v>96128</v>
+        <v>97356</v>
       </c>
       <c r="B299" s="2">
-        <v>91</v>
+        <v>31</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
-        <v>96129</v>
+        <v>97357</v>
       </c>
       <c r="B300" s="2">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
-        <v>96130</v>
+        <v>97359</v>
       </c>
       <c r="B301" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
-        <v>96131</v>
+        <v>97360</v>
       </c>
       <c r="B302" s="2">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
-        <v>96132</v>
+        <v>97365</v>
       </c>
       <c r="B303" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
-        <v>96133</v>
+        <v>97367</v>
       </c>
       <c r="B304" s="2">
-        <v>83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
-        <v>96134</v>
+        <v>97382</v>
       </c>
       <c r="B305" s="2">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
-        <v>96135</v>
+        <v>97383</v>
       </c>
       <c r="B306" s="2">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
-        <v>96136</v>
+        <v>97384</v>
       </c>
       <c r="B307" s="2">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
-        <v>96137</v>
+        <v>97389</v>
       </c>
       <c r="B308" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>96144</v>
+        <v>97392</v>
       </c>
       <c r="B309" s="2">
         <v>1</v>
@@ -2893,7 +2919,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>96170</v>
+        <v>97393</v>
       </c>
       <c r="B310" s="2">
         <v>1</v>
@@ -2901,551 +2927,551 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
-        <v>96178</v>
+        <v>97430</v>
       </c>
       <c r="B311" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
-        <v>96179</v>
+        <v>97445</v>
       </c>
       <c r="B312" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
-        <v>96180</v>
+        <v>97449</v>
       </c>
       <c r="B313" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
-        <v>96788</v>
+        <v>97455</v>
       </c>
       <c r="B314" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
-        <v>96798</v>
+        <v>97472</v>
       </c>
       <c r="B315" s="2">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
-        <v>96799</v>
+        <v>97484</v>
       </c>
       <c r="B316" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>96800</v>
+        <v>97494</v>
       </c>
       <c r="B317" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>96812</v>
+        <v>97496</v>
       </c>
       <c r="B318" s="2">
-        <v>1</v>
+        <v>74</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>96813</v>
+        <v>97497</v>
       </c>
       <c r="B319" s="2">
-        <v>12</v>
+        <v>87</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>96818</v>
+        <v>97498</v>
       </c>
       <c r="B320" s="2">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>96819</v>
+        <v>97499</v>
       </c>
       <c r="B321" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>96820</v>
+        <v>97500</v>
       </c>
       <c r="B322" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>96821</v>
+        <v>97504</v>
       </c>
       <c r="B323" s="2">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>96822</v>
+        <v>97505</v>
       </c>
       <c r="B324" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>96834</v>
+        <v>97797</v>
       </c>
       <c r="B325" s="2">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>97298</v>
+        <v>97798</v>
       </c>
       <c r="B326" s="2">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>97299</v>
+        <v>97799</v>
       </c>
       <c r="B327" s="2">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>97300</v>
+        <v>97800</v>
       </c>
       <c r="B328" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>97301</v>
+        <v>97801</v>
       </c>
       <c r="B329" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>97302</v>
+        <v>97803</v>
       </c>
       <c r="B330" s="2">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>97308</v>
+        <v>97804</v>
       </c>
       <c r="B331" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>97309</v>
+        <v>97805</v>
       </c>
       <c r="B332" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>97310</v>
+        <v>97806</v>
       </c>
       <c r="B333" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>97311</v>
+        <v>97813</v>
       </c>
       <c r="B334" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>97312</v>
+        <v>97814</v>
       </c>
       <c r="B335" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>97314</v>
+        <v>97815</v>
       </c>
       <c r="B336" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>97317</v>
+        <v>97817</v>
       </c>
       <c r="B337" s="2">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>97318</v>
+        <v>97818</v>
       </c>
       <c r="B338" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
-        <v>97319</v>
+        <v>97819</v>
       </c>
       <c r="B339" s="2">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>97320</v>
+        <v>97832</v>
       </c>
       <c r="B340" s="2">
-        <v>23</v>
+        <v>87</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>97323</v>
+        <v>97833</v>
       </c>
       <c r="B341" s="2">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>97324</v>
+        <v>97834</v>
       </c>
       <c r="B342" s="2">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>97325</v>
+        <v>97835</v>
       </c>
       <c r="B343" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>97327</v>
+        <v>97836</v>
       </c>
       <c r="B344" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>97330</v>
+        <v>97863</v>
       </c>
       <c r="B345" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>97333</v>
+        <v>97864</v>
       </c>
       <c r="B346" s="2">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>97334</v>
+        <v>97871</v>
       </c>
       <c r="B347" s="2">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>97335</v>
+        <v>97872</v>
       </c>
       <c r="B348" s="2">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>97336</v>
+        <v>97873</v>
       </c>
       <c r="B349" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>97337</v>
+        <v>97874</v>
       </c>
       <c r="B350" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>97343</v>
+        <v>97875</v>
       </c>
       <c r="B351" s="2">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>97344</v>
+        <v>97876</v>
       </c>
       <c r="B352" s="2">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
-        <v>97345</v>
+        <v>97877</v>
       </c>
       <c r="B353" s="2">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
-        <v>97346</v>
+        <v>97878</v>
       </c>
       <c r="B354" s="2">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>97348</v>
+        <v>97879</v>
       </c>
       <c r="B355" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
-        <v>97349</v>
+        <v>97880</v>
       </c>
       <c r="B356" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
-        <v>97350</v>
+        <v>98272</v>
       </c>
       <c r="B357" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
-        <v>97351</v>
+        <v>98273</v>
       </c>
       <c r="B358" s="2">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
-        <v>97352</v>
+        <v>98274</v>
       </c>
       <c r="B359" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
-        <v>97353</v>
+        <v>98275</v>
       </c>
       <c r="B360" s="2">
-        <v>67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
-        <v>97354</v>
+        <v>98276</v>
       </c>
       <c r="B361" s="2">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
-        <v>97355</v>
+        <v>98277</v>
       </c>
       <c r="B362" s="2">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
-        <v>97356</v>
+        <v>98278</v>
       </c>
       <c r="B363" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
-        <v>97357</v>
+        <v>98279</v>
       </c>
       <c r="B364" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
-        <v>97358</v>
+        <v>98280</v>
       </c>
       <c r="B365" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
-        <v>97359</v>
+        <v>98281</v>
       </c>
       <c r="B366" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
-        <v>97360</v>
+        <v>98282</v>
       </c>
       <c r="B367" s="2">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
-        <v>97365</v>
+        <v>98283</v>
       </c>
       <c r="B368" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
-        <v>97367</v>
+        <v>98284</v>
       </c>
       <c r="B369" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
-        <v>97370</v>
+        <v>98285</v>
       </c>
       <c r="B370" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
-        <v>97373</v>
+        <v>98286</v>
       </c>
       <c r="B371" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
-        <v>97374</v>
+        <v>98287</v>
       </c>
       <c r="B372" s="2">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
-        <v>97375</v>
+        <v>98288</v>
       </c>
       <c r="B373" s="2">
-        <v>6</v>
+        <v>97</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
-        <v>97376</v>
+        <v>98289</v>
       </c>
       <c r="B374" s="2">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
-        <v>97377</v>
+        <v>98290</v>
       </c>
       <c r="B375" s="2">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
-        <v>97378</v>
+        <v>98291</v>
       </c>
       <c r="B376" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
-        <v>97379</v>
+        <v>98292</v>
       </c>
       <c r="B377" s="2">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
-        <v>97380</v>
+        <v>98293</v>
       </c>
       <c r="B378" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
-        <v>97381</v>
+        <v>98294</v>
       </c>
       <c r="B379" s="2">
         <v>1</v>
@@ -3453,927 +3479,927 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
-        <v>97382</v>
+        <v>98295</v>
       </c>
       <c r="B380" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
-        <v>97383</v>
+        <v>98297</v>
       </c>
       <c r="B381" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
-        <v>97384</v>
+        <v>98298</v>
       </c>
       <c r="B382" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
-        <v>97386</v>
+        <v>98299</v>
       </c>
       <c r="B383" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
-        <v>97388</v>
+        <v>98300</v>
       </c>
       <c r="B384" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
-        <v>97389</v>
+        <v>98301</v>
       </c>
       <c r="B385" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
-        <v>97390</v>
+        <v>98307</v>
       </c>
       <c r="B386" s="2">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
-        <v>97391</v>
+        <v>98308</v>
       </c>
       <c r="B387" s="2">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
-        <v>97392</v>
+        <v>98309</v>
       </c>
       <c r="B388" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
-        <v>97393</v>
+        <v>98310</v>
       </c>
       <c r="B389" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
-        <v>97424</v>
+        <v>98311</v>
       </c>
       <c r="B390" s="2">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
-        <v>97425</v>
+        <v>98332</v>
       </c>
       <c r="B391" s="2">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
-        <v>97426</v>
+        <v>98333</v>
       </c>
       <c r="B392" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
-        <v>97429</v>
+        <v>98334</v>
       </c>
       <c r="B393" s="2">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
-        <v>97430</v>
+        <v>98335</v>
       </c>
       <c r="B394" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
-        <v>97431</v>
+        <v>98336</v>
       </c>
       <c r="B395" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
-        <v>97432</v>
+        <v>98340</v>
       </c>
       <c r="B396" s="2">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
-        <v>97434</v>
+        <v>98341</v>
       </c>
       <c r="B397" s="2">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
-        <v>97436</v>
+        <v>98342</v>
       </c>
       <c r="B398" s="2">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
-        <v>97439</v>
+        <v>98343</v>
       </c>
       <c r="B399" s="2">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
-        <v>97440</v>
+        <v>98344</v>
       </c>
       <c r="B400" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
-        <v>97441</v>
+        <v>98345</v>
       </c>
       <c r="B401" s="2">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
-        <v>97442</v>
+        <v>98346</v>
       </c>
       <c r="B402" s="2">
-        <v>1</v>
+        <v>85</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
-        <v>97444</v>
+        <v>98347</v>
       </c>
       <c r="B403" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
-        <v>97445</v>
+        <v>98348</v>
       </c>
       <c r="B404" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
-        <v>97447</v>
+        <v>98349</v>
       </c>
       <c r="B405" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
-        <v>97448</v>
+        <v>98350</v>
       </c>
       <c r="B406" s="2">
-        <v>1</v>
+        <v>85</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
-        <v>97449</v>
+        <v>98351</v>
       </c>
       <c r="B407" s="2">
-        <v>8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
-        <v>97450</v>
+        <v>98352</v>
       </c>
       <c r="B408" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
-        <v>97454</v>
+        <v>98353</v>
       </c>
       <c r="B409" s="2">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
-        <v>97455</v>
+        <v>98354</v>
       </c>
       <c r="B410" s="2">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
-        <v>97457</v>
+        <v>98355</v>
       </c>
       <c r="B411" s="2">
-        <v>6</v>
+        <v>80</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
-        <v>97458</v>
+        <v>98356</v>
       </c>
       <c r="B412" s="2">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
-        <v>97460</v>
+        <v>98357</v>
       </c>
       <c r="B413" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
-        <v>97472</v>
+        <v>98358</v>
       </c>
       <c r="B414" s="2">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
-        <v>97484</v>
+        <v>98359</v>
       </c>
       <c r="B415" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
-        <v>97492</v>
+        <v>98360</v>
       </c>
       <c r="B416" s="2">
-        <v>14</v>
+        <v>100</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
-        <v>97493</v>
+        <v>98361</v>
       </c>
       <c r="B417" s="2">
-        <v>13</v>
+        <v>102</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
-        <v>97494</v>
+        <v>98362</v>
       </c>
       <c r="B418" s="2">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
-        <v>97495</v>
+        <v>98363</v>
       </c>
       <c r="B419" s="2">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
-        <v>97501</v>
+        <v>98364</v>
       </c>
       <c r="B420" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
-        <v>97502</v>
+        <v>98365</v>
       </c>
       <c r="B421" s="2">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
-        <v>97503</v>
+        <v>98366</v>
       </c>
       <c r="B422" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
-        <v>97504</v>
+        <v>98367</v>
       </c>
       <c r="B423" s="2">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
-        <v>97505</v>
+        <v>98368</v>
       </c>
       <c r="B424" s="2">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
-        <v>97797</v>
+        <v>98369</v>
       </c>
       <c r="B425" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
-        <v>97798</v>
+        <v>98370</v>
       </c>
       <c r="B426" s="2">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
-        <v>97799</v>
+        <v>98371</v>
       </c>
       <c r="B427" s="2">
-        <v>70</v>
+        <v>94</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
-        <v>97800</v>
+        <v>98372</v>
       </c>
       <c r="B428" s="2">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
-        <v>97801</v>
+        <v>98373</v>
       </c>
       <c r="B429" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
-        <v>97802</v>
+        <v>98374</v>
       </c>
       <c r="B430" s="2">
-        <v>82</v>
+        <v>24</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
-        <v>97803</v>
+        <v>98375</v>
       </c>
       <c r="B431" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
-        <v>97804</v>
+        <v>98376</v>
       </c>
       <c r="B432" s="2">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
-        <v>97805</v>
+        <v>98377</v>
       </c>
       <c r="B433" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
-        <v>97806</v>
+        <v>98378</v>
       </c>
       <c r="B434" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
-        <v>97812</v>
+        <v>98379</v>
       </c>
       <c r="B435" s="2">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
-        <v>97813</v>
+        <v>98380</v>
       </c>
       <c r="B436" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
-        <v>97814</v>
+        <v>98381</v>
       </c>
       <c r="B437" s="2">
-        <v>52</v>
+        <v>91</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
-        <v>97815</v>
+        <v>98382</v>
       </c>
       <c r="B438" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
-        <v>97816</v>
+        <v>98383</v>
       </c>
       <c r="B439" s="2">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
-        <v>97817</v>
+        <v>98384</v>
       </c>
       <c r="B440" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
-        <v>97818</v>
+        <v>98385</v>
       </c>
       <c r="B441" s="2">
-        <v>119</v>
+        <v>58</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
-        <v>97819</v>
+        <v>98386</v>
       </c>
       <c r="B442" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
-        <v>97820</v>
+        <v>98387</v>
       </c>
       <c r="B443" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
-        <v>97821</v>
+        <v>98388</v>
       </c>
       <c r="B444" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
-        <v>97823</v>
+        <v>98389</v>
       </c>
       <c r="B445" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
-        <v>20839</v>
+        <v>98390</v>
       </c>
       <c r="B446" s="2">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
-        <v>20840</v>
+        <v>98391</v>
       </c>
       <c r="B447" s="2">
-        <v>2580</v>
+        <v>51</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
-        <v>20841</v>
+        <v>98392</v>
       </c>
       <c r="B448" s="2">
-        <v>960</v>
+        <v>26</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
-        <v>20846</v>
+        <v>98393</v>
       </c>
       <c r="B449" s="2">
-        <v>200</v>
+        <v>26</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
-        <v>28063</v>
+        <v>98395</v>
       </c>
       <c r="B450" s="2">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
-        <v>34299</v>
+        <v>98396</v>
       </c>
       <c r="B451" s="2">
-        <v>740</v>
+        <v>56</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
-        <v>44701</v>
+        <v>98397</v>
       </c>
       <c r="B452" s="2">
-        <v>480</v>
+        <v>33</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
-        <v>57140</v>
+        <v>98398</v>
       </c>
       <c r="B453" s="2">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
-        <v>60005</v>
+        <v>98399</v>
       </c>
       <c r="B454" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
-        <v>65318</v>
+        <v>98448</v>
       </c>
       <c r="B455" s="2">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
-        <v>68293</v>
+        <v>98449</v>
       </c>
       <c r="B456" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
-        <v>68651</v>
+        <v>98450</v>
       </c>
       <c r="B457" s="2">
-        <v>192</v>
+        <v>13</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
-        <v>69369</v>
+        <v>98453</v>
       </c>
       <c r="B458" s="2">
-        <v>624</v>
+        <v>13</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
-        <v>69372</v>
+        <v>98454</v>
       </c>
       <c r="B459" s="2">
-        <v>2328</v>
+        <v>50</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
-        <v>69373</v>
+        <v>98455</v>
       </c>
       <c r="B460" s="2">
-        <v>2604</v>
+        <v>27</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
-        <v>69378</v>
+        <v>98456</v>
       </c>
       <c r="B461" s="2">
-        <v>384</v>
+        <v>25</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
-        <v>69380</v>
+        <v>98458</v>
       </c>
       <c r="B462" s="2">
-        <v>1764</v>
+        <v>27</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
-        <v>69382</v>
+        <v>98459</v>
       </c>
       <c r="B463" s="2">
-        <v>1224</v>
+        <v>23</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
-        <v>69389</v>
+        <v>98463</v>
       </c>
       <c r="B464" s="2">
-        <v>2376</v>
+        <v>22</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
-        <v>69393</v>
+        <v>98464</v>
       </c>
       <c r="B465" s="2">
-        <v>156</v>
+        <v>26</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
-        <v>69394</v>
+        <v>98465</v>
       </c>
       <c r="B466" s="2">
-        <v>516</v>
+        <v>23</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
-        <v>69948</v>
+        <v>98466</v>
       </c>
       <c r="B467" s="2">
-        <v>864</v>
+        <v>13</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
-        <v>69949</v>
+        <v>98467</v>
       </c>
       <c r="B468" s="2">
-        <v>312</v>
+        <v>12</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
-        <v>71232</v>
+        <v>98468</v>
       </c>
       <c r="B469" s="2">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
-        <v>74158</v>
+        <v>98469</v>
       </c>
       <c r="B470" s="2">
-        <v>1356</v>
+        <v>64</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
-        <v>74160</v>
+        <v>98471</v>
       </c>
       <c r="B471" s="2">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
-        <v>74163</v>
+        <v>98473</v>
       </c>
       <c r="B472" s="2">
-        <v>540</v>
+        <v>18</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
-        <v>83233</v>
+        <v>98474</v>
       </c>
       <c r="B473" s="2">
-        <v>660</v>
+        <v>42</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
-        <v>87171</v>
+        <v>98475</v>
       </c>
       <c r="B474" s="2">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
-        <v>91515</v>
+        <v>98476</v>
       </c>
       <c r="B475" s="2">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
-        <v>91732</v>
+        <v>98477</v>
       </c>
       <c r="B476" s="2">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
-        <v>92742</v>
+        <v>98478</v>
       </c>
       <c r="B477" s="2">
-        <v>144</v>
+        <v>11</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
-        <v>92767</v>
+        <v>98479</v>
       </c>
       <c r="B478" s="2">
-        <v>1971</v>
+        <v>32</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
-        <v>93027</v>
+        <v>98480</v>
       </c>
       <c r="B479" s="2">
-        <v>810</v>
+        <v>12</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
-        <v>93036</v>
+        <v>98481</v>
       </c>
       <c r="B480" s="2">
-        <v>1008</v>
+        <v>8</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
-        <v>94355</v>
+        <v>98482</v>
       </c>
       <c r="B481" s="2">
-        <v>176</v>
+        <v>8</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
-        <v>94356</v>
+        <v>98483</v>
       </c>
       <c r="B482" s="2">
-        <v>380</v>
+        <v>45</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
-        <v>94357</v>
+        <v>98484</v>
       </c>
       <c r="B483" s="2">
-        <v>392</v>
+        <v>43</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
-        <v>94358</v>
+        <v>98485</v>
       </c>
       <c r="B484" s="2">
-        <v>404</v>
+        <v>30</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
-        <v>94404</v>
+        <v>98486</v>
       </c>
       <c r="B485" s="2">
-        <v>884</v>
+        <v>25</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
-        <v>94643</v>
+        <v>98488</v>
       </c>
       <c r="B486" s="2">
-        <v>408</v>
+        <v>59</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
-        <v>94718</v>
+        <v>98489</v>
       </c>
       <c r="B487" s="2">
-        <v>2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
-        <v>95618</v>
+        <v>98490</v>
       </c>
       <c r="B488" s="2">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
-        <v>95667</v>
+        <v>98491</v>
       </c>
       <c r="B489" s="2">
-        <v>168</v>
+        <v>28</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
-        <v>95670</v>
+        <v>98492</v>
       </c>
       <c r="B490" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
-        <v>95924</v>
+        <v>98493</v>
       </c>
       <c r="B491" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
-        <v>95927</v>
+        <v>98494</v>
       </c>
       <c r="B492" s="2">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
-        <v>95929</v>
+        <v>98495</v>
       </c>
       <c r="B493" s="2">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
-        <v>95931</v>
+        <v>98496</v>
       </c>
       <c r="B494" s="2">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
-        <v>96331</v>
+        <v>98497</v>
       </c>
       <c r="B495" s="2">
         <v>4</v>
@@ -4381,695 +4407,695 @@
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
-        <v>96443</v>
+        <v>98498</v>
       </c>
       <c r="B496" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
-        <v>96444</v>
+        <v>98499</v>
       </c>
       <c r="B497" s="2">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
-        <v>96453</v>
+        <v>98500</v>
       </c>
       <c r="B498" s="2">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
-        <v>96496</v>
+        <v>98501</v>
       </c>
       <c r="B499" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
-        <v>96519</v>
+        <v>98502</v>
       </c>
       <c r="B500" s="2">
-        <v>840</v>
+        <v>11</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
-        <v>96710</v>
+        <v>98503</v>
       </c>
       <c r="B501" s="2">
-        <v>4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
-        <v>97126</v>
+        <v>98504</v>
       </c>
       <c r="B502" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
-        <v>97127</v>
+        <v>98505</v>
       </c>
       <c r="B503" s="2">
-        <v>156</v>
+        <v>22</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
-        <v>97129</v>
+        <v>98506</v>
       </c>
       <c r="B504" s="2">
-        <v>128</v>
+        <v>22</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
-        <v>97130</v>
+        <v>98507</v>
       </c>
       <c r="B505" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
-        <v>97131</v>
+        <v>98508</v>
       </c>
       <c r="B506" s="2">
-        <v>144</v>
+        <v>24</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
-        <v>97133</v>
+        <v>98509</v>
       </c>
       <c r="B507" s="2">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
-        <v>97135</v>
+        <v>98510</v>
       </c>
       <c r="B508" s="2">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
-        <v>97552</v>
+        <v>98511</v>
       </c>
       <c r="B509" s="2">
-        <v>106</v>
+        <v>16</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
-        <v>97553</v>
+        <v>98512</v>
       </c>
       <c r="B510" s="2">
-        <v>106</v>
+        <v>12</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
-        <v>97554</v>
+        <v>98514</v>
       </c>
       <c r="B511" s="2">
-        <v>344</v>
+        <v>40</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
-        <v>97555</v>
+        <v>98515</v>
       </c>
       <c r="B512" s="2">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
-        <v>97557</v>
+        <v>98516</v>
       </c>
       <c r="B513" s="2">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
-        <v>97558</v>
+        <v>98517</v>
       </c>
       <c r="B514" s="2">
-        <v>132</v>
+        <v>11</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
-        <v>97559</v>
+        <v>98518</v>
       </c>
       <c r="B515" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
-        <v>97560</v>
+        <v>98519</v>
       </c>
       <c r="B516" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
-        <v>97561</v>
+        <v>98520</v>
       </c>
       <c r="B517" s="2">
-        <v>74</v>
+        <v>25</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
-        <v>97562</v>
+        <v>98521</v>
       </c>
       <c r="B518" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
-        <v>97563</v>
+        <v>98522</v>
       </c>
       <c r="B519" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
-        <v>97564</v>
+        <v>98523</v>
       </c>
       <c r="B520" s="2">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
-        <v>97565</v>
+        <v>98524</v>
       </c>
       <c r="B521" s="2">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
-        <v>97566</v>
+        <v>98525</v>
       </c>
       <c r="B522" s="2">
-        <v>119</v>
+        <v>38</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
-        <v>97567</v>
+        <v>98526</v>
       </c>
       <c r="B523" s="2">
-        <v>202</v>
+        <v>15</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
-        <v>97568</v>
+        <v>98527</v>
       </c>
       <c r="B524" s="2">
-        <v>56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
-        <v>97569</v>
+        <v>98737</v>
       </c>
       <c r="B525" s="2">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
-        <v>97570</v>
+        <v>98738</v>
       </c>
       <c r="B526" s="2">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
-        <v>97571</v>
+        <v>98740</v>
       </c>
       <c r="B527" s="2">
-        <v>102</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
-        <v>97572</v>
+        <v>98743</v>
       </c>
       <c r="B528" s="2">
-        <v>176</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
-        <v>97573</v>
+        <v>98752</v>
       </c>
       <c r="B529" s="2">
-        <v>228</v>
+        <v>44</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
-        <v>97574</v>
+        <v>98753</v>
       </c>
       <c r="B530" s="2">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
-        <v>97575</v>
+        <v>20840</v>
       </c>
       <c r="B531" s="2">
-        <v>3</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
-        <v>97576</v>
+        <v>20841</v>
       </c>
       <c r="B532" s="2">
-        <v>43</v>
+        <v>772</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
-        <v>97577</v>
+        <v>20846</v>
       </c>
       <c r="B533" s="2">
-        <v>86</v>
+        <v>174</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
-        <v>97578</v>
+        <v>34299</v>
       </c>
       <c r="B534" s="2">
-        <v>8</v>
+        <v>660</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
-        <v>97579</v>
+        <v>44701</v>
       </c>
       <c r="B535" s="2">
-        <v>116</v>
+        <v>316</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
-        <v>97587</v>
+        <v>53086</v>
       </c>
       <c r="B536" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
-        <v>97588</v>
+        <v>64252</v>
       </c>
       <c r="B537" s="2">
-        <v>146</v>
+        <v>36</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
-        <v>97590</v>
+        <v>68651</v>
       </c>
       <c r="B538" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
-        <v>97592</v>
+        <v>69369</v>
       </c>
       <c r="B539" s="2">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
-        <v>97595</v>
+        <v>69372</v>
       </c>
       <c r="B540" s="2">
-        <v>2</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
-        <v>97596</v>
+        <v>69373</v>
       </c>
       <c r="B541" s="2">
-        <v>396</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
-        <v>97597</v>
+        <v>69380</v>
       </c>
       <c r="B542" s="2">
-        <v>12</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
-        <v>97598</v>
+        <v>69382</v>
       </c>
       <c r="B543" s="2">
-        <v>66</v>
+        <v>660</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
-        <v>97599</v>
+        <v>69389</v>
       </c>
       <c r="B544" s="2">
-        <v>96</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
-        <v>97600</v>
+        <v>69948</v>
       </c>
       <c r="B545" s="2">
-        <v>171</v>
+        <v>456</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
-        <v>97601</v>
+        <v>69949</v>
       </c>
       <c r="B546" s="2">
-        <v>93</v>
+        <v>60</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
-        <v>97602</v>
+        <v>69956</v>
       </c>
       <c r="B547" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
-        <v>97603</v>
+        <v>74158</v>
       </c>
       <c r="B548" s="2">
-        <v>87</v>
+        <v>732</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
-        <v>97604</v>
+        <v>83233</v>
       </c>
       <c r="B549" s="2">
-        <v>72</v>
+        <v>420</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
-        <v>97605</v>
+        <v>87534</v>
       </c>
       <c r="B550" s="2">
-        <v>24</v>
+        <v>572</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
-        <v>97606</v>
+        <v>91515</v>
       </c>
       <c r="B551" s="2">
-        <v>76</v>
+        <v>6</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
-        <v>97607</v>
+        <v>91732</v>
       </c>
       <c r="B552" s="2">
-        <v>40</v>
+        <v>324</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
-        <v>97608</v>
+        <v>92742</v>
       </c>
       <c r="B553" s="2">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
-        <v>97624</v>
+        <v>92767</v>
       </c>
       <c r="B554" s="2">
-        <v>189</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
-        <v>97625</v>
+        <v>93027</v>
       </c>
       <c r="B555" s="2">
-        <v>64</v>
+        <v>690</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
-        <v>97626</v>
+        <v>93036</v>
       </c>
       <c r="B556" s="2">
-        <v>34</v>
+        <v>212</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
-        <v>97627</v>
+        <v>93051</v>
       </c>
       <c r="B557" s="2">
-        <v>87</v>
+        <v>572</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
-        <v>97628</v>
+        <v>94355</v>
       </c>
       <c r="B558" s="2">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
-        <v>97629</v>
+        <v>94356</v>
       </c>
       <c r="B559" s="2">
-        <v>4</v>
+        <v>244</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
-        <v>97652</v>
+        <v>94357</v>
       </c>
       <c r="B560" s="2">
-        <v>103</v>
+        <v>216</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
-        <v>97653</v>
+        <v>94358</v>
       </c>
       <c r="B561" s="2">
-        <v>131</v>
+        <v>252</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
-        <v>97654</v>
+        <v>94404</v>
       </c>
       <c r="B562" s="2">
-        <v>74</v>
+        <v>684</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
-        <v>97881</v>
+        <v>94643</v>
       </c>
       <c r="B563" s="2">
-        <v>720</v>
+        <v>8</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
-        <v>97882</v>
+        <v>95618</v>
       </c>
       <c r="B564" s="2">
-        <v>688</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
-        <v>7722</v>
+        <v>95667</v>
       </c>
       <c r="B565" s="2">
-        <v>936</v>
+        <v>76</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
-        <v>33427</v>
+        <v>95927</v>
       </c>
       <c r="B566" s="2">
-        <v>780</v>
+        <v>3</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
-        <v>59285</v>
+        <v>96331</v>
       </c>
       <c r="B567" s="2">
-        <v>90</v>
+        <v>4</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
-        <v>78372</v>
+        <v>96453</v>
       </c>
       <c r="B568" s="2">
-        <v>740</v>
+        <v>8</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
-        <v>84540</v>
+        <v>96496</v>
       </c>
       <c r="B569" s="2">
-        <v>4480</v>
+        <v>4</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
-        <v>89097</v>
+        <v>96519</v>
       </c>
       <c r="B570" s="2">
-        <v>515</v>
+        <v>468</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
-        <v>92811</v>
+        <v>96710</v>
       </c>
       <c r="B571" s="2">
-        <v>85</v>
+        <v>4</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
-        <v>94746</v>
+        <v>97126</v>
       </c>
       <c r="B572" s="2">
-        <v>834</v>
+        <v>44</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
-        <v>95346</v>
+        <v>97127</v>
       </c>
       <c r="B573" s="2">
-        <v>2592</v>
+        <v>152</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
-        <v>95588</v>
+        <v>97129</v>
       </c>
       <c r="B574" s="2">
-        <v>90</v>
+        <v>128</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
-        <v>95795</v>
+        <v>97131</v>
       </c>
       <c r="B575" s="2">
-        <v>1452</v>
+        <v>108</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
-        <v>96895</v>
+        <v>97133</v>
       </c>
       <c r="B576" s="2">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
-        <v>96896</v>
+        <v>97552</v>
       </c>
       <c r="B577" s="2">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
-        <v>96898</v>
+        <v>97553</v>
       </c>
       <c r="B578" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
-        <v>96989</v>
+        <v>97554</v>
       </c>
       <c r="B579" s="2">
-        <v>2000</v>
+        <v>272</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
-        <v>97519</v>
+        <v>97555</v>
       </c>
       <c r="B580" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
-        <v>97633</v>
+        <v>97558</v>
       </c>
       <c r="B581" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
-        <v>97635</v>
+        <v>97559</v>
       </c>
       <c r="B582" s="2">
         <v>12</v>
@@ -5077,367 +5103,367 @@
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
-        <v>97639</v>
+        <v>97560</v>
       </c>
       <c r="B583" s="2">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A584" s="1">
-        <v>97640</v>
+        <v>97561</v>
       </c>
       <c r="B584" s="2">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A585" s="1">
-        <v>97642</v>
+        <v>97564</v>
       </c>
       <c r="B585" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
-        <v>97644</v>
+        <v>97565</v>
       </c>
       <c r="B586" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
-        <v>97645</v>
+        <v>97566</v>
       </c>
       <c r="B587" s="2">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
-        <v>97662</v>
+        <v>97567</v>
       </c>
       <c r="B588" s="2">
-        <v>390</v>
+        <v>4</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A589" s="1">
-        <v>97663</v>
+        <v>97568</v>
       </c>
       <c r="B589" s="2">
-        <v>460</v>
+        <v>2</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A590" s="1">
-        <v>97664</v>
+        <v>97569</v>
       </c>
       <c r="B590" s="2">
-        <v>360</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A591" s="1">
-        <v>97665</v>
+        <v>97570</v>
       </c>
       <c r="B591" s="2">
-        <v>6000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A592" s="1">
-        <v>98539</v>
+        <v>97571</v>
       </c>
       <c r="B592" s="2">
-        <v>420</v>
+        <v>54</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A593" s="1">
-        <v>98540</v>
+        <v>97572</v>
       </c>
       <c r="B593" s="2">
-        <v>420</v>
+        <v>16</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A594" s="1">
-        <v>98541</v>
+        <v>97573</v>
       </c>
       <c r="B594" s="2">
-        <v>420</v>
+        <v>116</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A595" s="1">
-        <v>99389</v>
+        <v>97574</v>
       </c>
       <c r="B595" s="2">
-        <v>948</v>
+        <v>8</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A596" s="1">
-        <v>9646</v>
+        <v>97576</v>
       </c>
       <c r="B596" s="2">
-        <v>2424</v>
+        <v>1</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A597" s="1">
-        <v>24874</v>
+        <v>97577</v>
       </c>
       <c r="B597" s="2">
-        <v>1988</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A598" s="1">
-        <v>53546</v>
+        <v>97579</v>
       </c>
       <c r="B598" s="2">
-        <v>1728</v>
+        <v>8</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A599" s="1">
-        <v>59014</v>
+        <v>97580</v>
       </c>
       <c r="B599" s="2">
-        <v>990</v>
+        <v>148</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A600" s="1">
-        <v>65788</v>
+        <v>97581</v>
       </c>
       <c r="B600" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A601" s="1">
-        <v>65800</v>
+        <v>97582</v>
       </c>
       <c r="B601" s="2">
-        <v>308</v>
+        <v>176</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
-        <v>65802</v>
+        <v>97583</v>
       </c>
       <c r="B602" s="2">
-        <v>158</v>
+        <v>188</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A603" s="1">
-        <v>65803</v>
+        <v>97584</v>
       </c>
       <c r="B603" s="2">
-        <v>26</v>
+        <v>160</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A604" s="1">
-        <v>65805</v>
+        <v>97585</v>
       </c>
       <c r="B604" s="2">
-        <v>538</v>
+        <v>184</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A605" s="1">
-        <v>65948</v>
+        <v>97586</v>
       </c>
       <c r="B605" s="2">
-        <v>392</v>
+        <v>180</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A606" s="1">
-        <v>66663</v>
+        <v>97587</v>
       </c>
       <c r="B606" s="2">
-        <v>870</v>
+        <v>18</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A607" s="1">
-        <v>68463</v>
+        <v>97588</v>
       </c>
       <c r="B607" s="2">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A608" s="1">
-        <v>70620</v>
+        <v>97590</v>
       </c>
       <c r="B608" s="2">
-        <v>1008</v>
+        <v>4</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A609" s="1">
-        <v>72153</v>
+        <v>97591</v>
       </c>
       <c r="B609" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A610" s="1">
-        <v>72157</v>
+        <v>97596</v>
       </c>
       <c r="B610" s="2">
-        <v>2</v>
+        <v>324</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A611" s="1">
-        <v>74779</v>
+        <v>97598</v>
       </c>
       <c r="B611" s="2">
-        <v>1864</v>
+        <v>30</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A612" s="1">
-        <v>75920</v>
+        <v>97599</v>
       </c>
       <c r="B612" s="2">
-        <v>880</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A613" s="1">
-        <v>75922</v>
+        <v>97600</v>
       </c>
       <c r="B613" s="2">
-        <v>766</v>
+        <v>99</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A614" s="1">
-        <v>75923</v>
+        <v>97601</v>
       </c>
       <c r="B614" s="2">
-        <v>888</v>
+        <v>9</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A615" s="1">
-        <v>75924</v>
+        <v>97603</v>
       </c>
       <c r="B615" s="2">
-        <v>1038</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A616" s="1">
-        <v>76063</v>
+        <v>97605</v>
       </c>
       <c r="B616" s="2">
-        <v>1030</v>
+        <v>12</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A617" s="1">
-        <v>76064</v>
+        <v>97607</v>
       </c>
       <c r="B617" s="2">
-        <v>1128</v>
+        <v>4</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A618" s="1">
-        <v>76065</v>
+        <v>97624</v>
       </c>
       <c r="B618" s="2">
-        <v>1648</v>
+        <v>155</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A619" s="1">
-        <v>76066</v>
+        <v>97625</v>
       </c>
       <c r="B619" s="2">
-        <v>1864</v>
+        <v>53</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A620" s="1">
-        <v>76067</v>
+        <v>97626</v>
       </c>
       <c r="B620" s="2">
-        <v>1540</v>
+        <v>19</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A621" s="1">
-        <v>77697</v>
+        <v>97627</v>
       </c>
       <c r="B621" s="2">
-        <v>970</v>
+        <v>57</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A622" s="1">
-        <v>78624</v>
+        <v>97628</v>
       </c>
       <c r="B622" s="2">
-        <v>108</v>
+        <v>10</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A623" s="1">
-        <v>78625</v>
+        <v>97653</v>
       </c>
       <c r="B623" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A624" s="1">
-        <v>78626</v>
+        <v>97654</v>
       </c>
       <c r="B624" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A625" s="1">
-        <v>78627</v>
+        <v>97692</v>
       </c>
       <c r="B625" s="2">
-        <v>106</v>
+        <v>308</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A626" s="1">
-        <v>78628</v>
+        <v>97693</v>
       </c>
       <c r="B626" s="2">
-        <v>14</v>
+        <v>308</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A627" s="1">
-        <v>78629</v>
+        <v>97694</v>
       </c>
       <c r="B627" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A628" s="1">
-        <v>78630</v>
+        <v>97695</v>
       </c>
       <c r="B628" s="2">
         <v>100</v>
@@ -5445,727 +5471,727 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A629" s="1">
-        <v>78632</v>
+        <v>97881</v>
       </c>
       <c r="B629" s="2">
-        <v>142</v>
+        <v>380</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A630" s="1">
-        <v>78633</v>
+        <v>97882</v>
       </c>
       <c r="B630" s="2">
-        <v>196</v>
+        <v>344</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A631" s="1">
-        <v>78634</v>
+        <v>98216</v>
       </c>
       <c r="B631" s="2">
-        <v>52</v>
+        <v>272</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A632" s="1">
-        <v>78635</v>
+        <v>98217</v>
       </c>
       <c r="B632" s="2">
-        <v>104</v>
+        <v>620</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A633" s="1">
-        <v>80655</v>
+        <v>98218</v>
       </c>
       <c r="B633" s="2">
-        <v>2</v>
+        <v>272</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A634" s="1">
-        <v>80657</v>
+        <v>98219</v>
       </c>
       <c r="B634" s="2">
-        <v>24</v>
+        <v>214</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A635" s="1">
-        <v>80660</v>
+        <v>98220</v>
       </c>
       <c r="B635" s="2">
-        <v>4</v>
+        <v>144</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A636" s="1">
-        <v>80662</v>
+        <v>98221</v>
       </c>
       <c r="B636" s="2">
-        <v>16</v>
+        <v>212</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A637" s="1">
-        <v>80677</v>
+        <v>98222</v>
       </c>
       <c r="B637" s="2">
-        <v>54</v>
+        <v>212</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A638" s="1">
-        <v>80679</v>
+        <v>98223</v>
       </c>
       <c r="B638" s="2">
-        <v>798</v>
+        <v>212</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A639" s="1">
-        <v>80680</v>
+        <v>98224</v>
       </c>
       <c r="B639" s="2">
-        <v>72</v>
+        <v>32</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A640" s="1">
-        <v>80684</v>
+        <v>98225</v>
       </c>
       <c r="B640" s="2">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A641" s="1">
-        <v>80685</v>
+        <v>98226</v>
       </c>
       <c r="B641" s="2">
-        <v>420</v>
+        <v>296</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A642" s="1">
-        <v>82833</v>
+        <v>98227</v>
       </c>
       <c r="B642" s="2">
-        <v>206</v>
+        <v>876</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A643" s="1">
-        <v>82834</v>
+        <v>98228</v>
       </c>
       <c r="B643" s="2">
-        <v>158</v>
+        <v>296</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A644" s="1">
-        <v>84801</v>
+        <v>98229</v>
       </c>
       <c r="B644" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A645" s="1">
-        <v>84802</v>
+        <v>98231</v>
       </c>
       <c r="B645" s="2">
-        <v>454</v>
+        <v>300</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A646" s="1">
-        <v>84803</v>
+        <v>98232</v>
       </c>
       <c r="B646" s="2">
-        <v>344</v>
+        <v>168</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A647" s="1">
-        <v>84804</v>
+        <v>98233</v>
       </c>
       <c r="B647" s="2">
-        <v>154</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A648" s="1">
-        <v>84807</v>
+        <v>98234</v>
       </c>
       <c r="B648" s="2">
-        <v>68</v>
+        <v>220</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A649" s="1">
-        <v>86538</v>
+        <v>98235</v>
       </c>
       <c r="B649" s="2">
-        <v>486</v>
+        <v>220</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A650" s="1">
-        <v>87263</v>
+        <v>98236</v>
       </c>
       <c r="B650" s="2">
-        <v>330</v>
+        <v>220</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A651" s="1">
-        <v>87325</v>
+        <v>98237</v>
       </c>
       <c r="B651" s="2">
-        <v>900</v>
+        <v>220</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A652" s="1">
-        <v>87326</v>
+        <v>98238</v>
       </c>
       <c r="B652" s="2">
-        <v>936</v>
+        <v>220</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A653" s="1">
-        <v>87901</v>
+        <v>98239</v>
       </c>
       <c r="B653" s="2">
-        <v>1538</v>
+        <v>224</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A654" s="1">
-        <v>87903</v>
+        <v>98538</v>
       </c>
       <c r="B654" s="2">
-        <v>158</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A655" s="1">
-        <v>88350</v>
+        <v>98581</v>
       </c>
       <c r="B655" s="2">
-        <v>838</v>
+        <v>148</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A656" s="1">
-        <v>88360</v>
+        <v>98582</v>
       </c>
       <c r="B656" s="2">
-        <v>1020</v>
+        <v>148</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A657" s="1">
-        <v>88400</v>
+        <v>98583</v>
       </c>
       <c r="B657" s="2">
-        <v>1430</v>
+        <v>148</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A658" s="1">
-        <v>89190</v>
+        <v>98584</v>
       </c>
       <c r="B658" s="2">
-        <v>2</v>
+        <v>148</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A659" s="1">
-        <v>89191</v>
+        <v>98585</v>
       </c>
       <c r="B659" s="2">
-        <v>2</v>
+        <v>148</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A660" s="1">
-        <v>89192</v>
+        <v>98586</v>
       </c>
       <c r="B660" s="2">
-        <v>24</v>
+        <v>148</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A661" s="1">
-        <v>89194</v>
+        <v>98587</v>
       </c>
       <c r="B661" s="2">
-        <v>22</v>
+        <v>148</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A662" s="1">
-        <v>89196</v>
+        <v>98589</v>
       </c>
       <c r="B662" s="2">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A663" s="1">
-        <v>90109</v>
+        <v>98590</v>
       </c>
       <c r="B663" s="2">
-        <v>1864</v>
+        <v>108</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A664" s="1">
-        <v>90497</v>
+        <v>98592</v>
       </c>
       <c r="B664" s="2">
-        <v>316</v>
+        <v>64</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A665" s="1">
-        <v>90973</v>
+        <v>98626</v>
       </c>
       <c r="B665" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A666" s="1">
-        <v>91653</v>
+        <v>98627</v>
       </c>
       <c r="B666" s="2">
-        <v>804</v>
+        <v>168</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A667" s="1">
-        <v>91665</v>
+        <v>98628</v>
       </c>
       <c r="B667" s="2">
-        <v>6</v>
+        <v>168</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A668" s="1">
-        <v>91678</v>
+        <v>98629</v>
       </c>
       <c r="B668" s="2">
-        <v>774</v>
+        <v>168</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A669" s="1">
-        <v>92172</v>
+        <v>98630</v>
       </c>
       <c r="B669" s="2">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A670" s="1">
-        <v>92176</v>
+        <v>98631</v>
       </c>
       <c r="B670" s="2">
-        <v>1490</v>
+        <v>168</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A671" s="1">
-        <v>92184</v>
+        <v>98632</v>
       </c>
       <c r="B671" s="2">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A672" s="1">
-        <v>92463</v>
+        <v>98633</v>
       </c>
       <c r="B672" s="2">
-        <v>244</v>
+        <v>192</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A673" s="1">
-        <v>92815</v>
+        <v>98634</v>
       </c>
       <c r="B673" s="2">
-        <v>608</v>
+        <v>192</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A674" s="1">
-        <v>92822</v>
+        <v>7722</v>
       </c>
       <c r="B674" s="2">
-        <v>220</v>
+        <v>864</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A675" s="1">
-        <v>92823</v>
+        <v>33427</v>
       </c>
       <c r="B675" s="2">
-        <v>220</v>
+        <v>424</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A676" s="1">
-        <v>92836</v>
+        <v>59285</v>
       </c>
       <c r="B676" s="2">
-        <v>300</v>
+        <v>56</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A677" s="1">
-        <v>92959</v>
+        <v>78372</v>
       </c>
       <c r="B677" s="2">
-        <v>6</v>
+        <v>720</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
-        <v>92962</v>
+        <v>84540</v>
       </c>
       <c r="B678" s="2">
-        <v>6</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A679" s="1">
-        <v>92968</v>
+        <v>89097</v>
       </c>
       <c r="B679" s="2">
-        <v>10</v>
+        <v>479</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A680" s="1">
-        <v>92984</v>
+        <v>92811</v>
       </c>
       <c r="B680" s="2">
-        <v>250</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A681" s="1">
-        <v>93016</v>
+        <v>94746</v>
       </c>
       <c r="B681" s="2">
-        <v>756</v>
+        <v>438</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A682" s="1">
-        <v>93067</v>
+        <v>95346</v>
       </c>
       <c r="B682" s="2">
-        <v>1024</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
-        <v>93073</v>
+        <v>95588</v>
       </c>
       <c r="B683" s="2">
-        <v>1370</v>
+        <v>15</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A684" s="1">
-        <v>94314</v>
+        <v>95795</v>
       </c>
       <c r="B684" s="2">
-        <v>54</v>
+        <v>780</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A685" s="1">
-        <v>94317</v>
+        <v>96895</v>
       </c>
       <c r="B685" s="2">
-        <v>2456</v>
+        <v>4</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A686" s="1">
-        <v>94683</v>
+        <v>96896</v>
       </c>
       <c r="B686" s="2">
-        <v>249</v>
+        <v>12</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A687" s="1">
-        <v>94821</v>
+        <v>96989</v>
       </c>
       <c r="B687" s="2">
-        <v>1014</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A688" s="1">
-        <v>94830</v>
+        <v>97519</v>
       </c>
       <c r="B688" s="2">
-        <v>1042</v>
+        <v>8</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A689" s="1">
-        <v>94835</v>
+        <v>97642</v>
       </c>
       <c r="B689" s="2">
-        <v>866</v>
+        <v>8</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A690" s="1">
-        <v>95202</v>
+        <v>97662</v>
       </c>
       <c r="B690" s="2">
-        <v>302</v>
+        <v>390</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A691" s="1">
-        <v>95211</v>
+        <v>97663</v>
       </c>
       <c r="B691" s="2">
-        <v>398</v>
+        <v>460</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A692" s="1">
-        <v>95536</v>
+        <v>97664</v>
       </c>
       <c r="B692" s="2">
-        <v>1228</v>
+        <v>420</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A693" s="1">
-        <v>95538</v>
+        <v>97665</v>
       </c>
       <c r="B693" s="2">
-        <v>1282</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A694" s="1">
-        <v>95715</v>
+        <v>98425</v>
       </c>
       <c r="B694" s="2">
-        <v>2080</v>
+        <v>148</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A695" s="1">
-        <v>95731</v>
+        <v>98434</v>
       </c>
       <c r="B695" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A696" s="1">
-        <v>95732</v>
+        <v>98435</v>
       </c>
       <c r="B696" s="2">
-        <v>900</v>
+        <v>84</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A697" s="1">
-        <v>95739</v>
+        <v>98436</v>
       </c>
       <c r="B697" s="2">
-        <v>52</v>
+        <v>84</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A698" s="1">
-        <v>95740</v>
+        <v>98437</v>
       </c>
       <c r="B698" s="2">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A699" s="1">
-        <v>95741</v>
+        <v>98438</v>
       </c>
       <c r="B699" s="2">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A700" s="1">
-        <v>95765</v>
+        <v>98439</v>
       </c>
       <c r="B700" s="2">
-        <v>634</v>
+        <v>68</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A701" s="1">
-        <v>95768</v>
+        <v>98440</v>
       </c>
       <c r="B701" s="2">
-        <v>534</v>
+        <v>68</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A702" s="1">
-        <v>95769</v>
+        <v>98441</v>
       </c>
       <c r="B702" s="2">
-        <v>1158</v>
+        <v>68</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A703" s="1">
-        <v>95770</v>
+        <v>98442</v>
       </c>
       <c r="B703" s="2">
-        <v>488</v>
+        <v>68</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A704" s="1">
-        <v>95772</v>
+        <v>98443</v>
       </c>
       <c r="B704" s="2">
-        <v>508</v>
+        <v>68</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A705" s="1">
-        <v>95774</v>
+        <v>98444</v>
       </c>
       <c r="B705" s="2">
-        <v>636</v>
+        <v>52</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A706" s="1">
-        <v>95781</v>
+        <v>98445</v>
       </c>
       <c r="B706" s="2">
-        <v>666</v>
+        <v>52</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A707" s="1">
-        <v>95887</v>
+        <v>98446</v>
       </c>
       <c r="B707" s="2">
-        <v>172</v>
+        <v>52</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A708" s="1">
-        <v>95907</v>
+        <v>98447</v>
       </c>
       <c r="B708" s="2">
-        <v>192</v>
+        <v>28</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A709" s="1">
-        <v>95911</v>
+        <v>98539</v>
       </c>
       <c r="B709" s="2">
-        <v>466</v>
+        <v>90</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A710" s="1">
-        <v>96507</v>
+        <v>98540</v>
       </c>
       <c r="B710" s="2">
-        <v>526</v>
+        <v>140</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A711" s="1">
-        <v>96508</v>
+        <v>98541</v>
       </c>
       <c r="B711" s="2">
-        <v>968</v>
+        <v>80</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A712" s="1">
-        <v>96510</v>
+        <v>99389</v>
       </c>
       <c r="B712" s="2">
-        <v>446</v>
+        <v>36</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A713" s="1">
-        <v>96517</v>
+        <v>9646</v>
       </c>
       <c r="B713" s="2">
-        <v>334</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A714" s="1">
-        <v>96539</v>
+        <v>24874</v>
       </c>
       <c r="B714" s="2">
-        <v>1168</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A715" s="1">
-        <v>96611</v>
+        <v>34094</v>
       </c>
       <c r="B715" s="2">
-        <v>6</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A716" s="1">
-        <v>97700</v>
+        <v>53546</v>
       </c>
       <c r="B716" s="2">
-        <v>6</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A717" s="1">
-        <v>97701</v>
+        <v>59014</v>
       </c>
       <c r="B717" s="2">
-        <v>62</v>
+        <v>638</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A718" s="1">
-        <v>97702</v>
+        <v>65805</v>
       </c>
       <c r="B718" s="2">
-        <v>10</v>
+        <v>148</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A719" s="1">
-        <v>97703</v>
+        <v>65948</v>
       </c>
       <c r="B719" s="2">
         <v>112</v>
@@ -6173,375 +6199,375 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A720" s="1">
-        <v>97705</v>
+        <v>66663</v>
       </c>
       <c r="B720" s="2">
-        <v>58</v>
+        <v>626</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A721" s="1">
-        <v>97706</v>
+        <v>68463</v>
       </c>
       <c r="B721" s="2">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A722" s="1">
-        <v>97707</v>
+        <v>70620</v>
       </c>
       <c r="B722" s="2">
-        <v>64</v>
+        <v>644</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A723" s="1">
-        <v>97708</v>
+        <v>70653</v>
       </c>
       <c r="B723" s="2">
-        <v>16</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A724" s="1">
-        <v>97709</v>
+        <v>74779</v>
       </c>
       <c r="B724" s="2">
-        <v>20</v>
+        <v>918</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A725" s="1">
-        <v>97710</v>
+        <v>75922</v>
       </c>
       <c r="B725" s="2">
-        <v>22</v>
+        <v>108</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A726" s="1">
-        <v>97711</v>
+        <v>75923</v>
       </c>
       <c r="B726" s="2">
-        <v>110</v>
+        <v>280</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A727" s="1">
-        <v>97712</v>
+        <v>75924</v>
       </c>
       <c r="B727" s="2">
-        <v>62</v>
+        <v>372</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A728" s="1">
-        <v>97713</v>
+        <v>76063</v>
       </c>
       <c r="B728" s="2">
-        <v>52</v>
+        <v>148</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A729" s="1">
-        <v>97714</v>
+        <v>76064</v>
       </c>
       <c r="B729" s="2">
-        <v>62</v>
+        <v>202</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A730" s="1">
-        <v>97715</v>
+        <v>76065</v>
       </c>
       <c r="B730" s="2">
-        <v>100</v>
+        <v>706</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A731" s="1">
-        <v>97717</v>
+        <v>76066</v>
       </c>
       <c r="B731" s="2">
-        <v>136</v>
+        <v>800</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A732" s="1">
-        <v>97718</v>
+        <v>76067</v>
       </c>
       <c r="B732" s="2">
-        <v>36</v>
+        <v>552</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A733" s="1">
-        <v>97720</v>
+        <v>77697</v>
       </c>
       <c r="B733" s="2">
-        <v>136</v>
+        <v>478</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A734" s="1">
-        <v>97721</v>
+        <v>78625</v>
       </c>
       <c r="B734" s="2">
-        <v>52</v>
+        <v>84</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A735" s="1">
-        <v>97722</v>
+        <v>78630</v>
       </c>
       <c r="B735" s="2">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A736" s="1">
-        <v>97723</v>
+        <v>78633</v>
       </c>
       <c r="B736" s="2">
-        <v>116</v>
+        <v>44</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A737" s="1">
-        <v>97724</v>
+        <v>80660</v>
       </c>
       <c r="B737" s="2">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A738" s="1">
-        <v>97725</v>
+        <v>80679</v>
       </c>
       <c r="B738" s="2">
-        <v>86</v>
+        <v>246</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A739" s="1">
-        <v>97726</v>
+        <v>80680</v>
       </c>
       <c r="B739" s="2">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A740" s="1">
-        <v>97727</v>
+        <v>80685</v>
       </c>
       <c r="B740" s="2">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A741" s="1">
-        <v>97728</v>
+        <v>81763</v>
       </c>
       <c r="B741" s="2">
-        <v>68</v>
+        <v>790</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A742" s="1">
-        <v>97731</v>
+        <v>81764</v>
       </c>
       <c r="B742" s="2">
-        <v>104</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A743" s="1">
-        <v>97732</v>
+        <v>81765</v>
       </c>
       <c r="B743" s="2">
-        <v>34</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A744" s="1">
-        <v>97733</v>
+        <v>82834</v>
       </c>
       <c r="B744" s="2">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A745" s="1">
-        <v>97734</v>
+        <v>83163</v>
       </c>
       <c r="B745" s="2">
-        <v>72</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A746" s="1">
-        <v>97735</v>
+        <v>84801</v>
       </c>
       <c r="B746" s="2">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A747" s="1">
-        <v>97736</v>
+        <v>84802</v>
       </c>
       <c r="B747" s="2">
-        <v>22</v>
+        <v>264</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A748" s="1">
-        <v>97737</v>
+        <v>84803</v>
       </c>
       <c r="B748" s="2">
-        <v>54</v>
+        <v>140</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A749" s="1">
-        <v>97738</v>
+        <v>84804</v>
       </c>
       <c r="B749" s="2">
-        <v>8</v>
+        <v>92</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A750" s="1">
-        <v>97741</v>
+        <v>84807</v>
       </c>
       <c r="B750" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A751" s="1">
-        <v>97742</v>
+        <v>86538</v>
       </c>
       <c r="B751" s="2">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A752" s="1">
-        <v>97743</v>
+        <v>87263</v>
       </c>
       <c r="B752" s="2">
-        <v>6</v>
+        <v>222</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A753" s="1">
-        <v>97744</v>
+        <v>87325</v>
       </c>
       <c r="B753" s="2">
-        <v>96</v>
+        <v>614</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A754" s="1">
-        <v>97745</v>
+        <v>87326</v>
       </c>
       <c r="B754" s="2">
-        <v>14</v>
+        <v>616</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A755" s="1">
-        <v>97746</v>
+        <v>87635</v>
       </c>
       <c r="B755" s="2">
-        <v>18</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A756" s="1">
-        <v>97747</v>
+        <v>87901</v>
       </c>
       <c r="B756" s="2">
-        <v>36</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A757" s="1">
-        <v>97748</v>
+        <v>87903</v>
       </c>
       <c r="B757" s="2">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A758" s="1">
-        <v>97749</v>
+        <v>88350</v>
       </c>
       <c r="B758" s="2">
-        <v>62</v>
+        <v>710</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A759" s="1">
-        <v>97750</v>
+        <v>88360</v>
       </c>
       <c r="B759" s="2">
-        <v>68</v>
+        <v>726</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A760" s="1">
-        <v>97752</v>
+        <v>88400</v>
       </c>
       <c r="B760" s="2">
-        <v>34</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A761" s="1">
-        <v>97754</v>
+        <v>89190</v>
       </c>
       <c r="B761" s="2">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A762" s="1">
-        <v>97755</v>
+        <v>89192</v>
       </c>
       <c r="B762" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A763" s="1">
-        <v>97756</v>
+        <v>89194</v>
       </c>
       <c r="B763" s="2">
-        <v>142</v>
+        <v>2</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A764" s="1">
-        <v>97757</v>
+        <v>90109</v>
       </c>
       <c r="B764" s="2">
-        <v>8</v>
+        <v>874</v>
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A765" s="1">
-        <v>97758</v>
+        <v>90497</v>
       </c>
       <c r="B765" s="2">
-        <v>4</v>
+        <v>196</v>
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
-        <v>97761</v>
+        <v>90972</v>
       </c>
       <c r="B766" s="2">
         <v>2</v>
@@ -6549,186 +6575,1562 @@
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A767" s="1">
-        <v>97764</v>
+        <v>91653</v>
       </c>
       <c r="B767" s="2">
-        <v>2</v>
+        <v>612</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A768" s="1">
-        <v>97765</v>
+        <v>91678</v>
       </c>
       <c r="B768" s="2">
-        <v>18</v>
+        <v>428</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
-        <v>97767</v>
+        <v>92172</v>
       </c>
       <c r="B769" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
-        <v>97768</v>
+        <v>92176</v>
       </c>
       <c r="B770" s="2">
-        <v>150</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A771" s="1">
-        <v>97770</v>
+        <v>92184</v>
       </c>
       <c r="B771" s="2">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
-        <v>97771</v>
+        <v>92463</v>
       </c>
       <c r="B772" s="2">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
-        <v>97773</v>
+        <v>92815</v>
       </c>
       <c r="B773" s="2">
-        <v>6</v>
+        <v>324</v>
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
-        <v>97774</v>
+        <v>92822</v>
       </c>
       <c r="B774" s="2">
-        <v>64</v>
+        <v>204</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A775" s="1">
-        <v>97775</v>
+        <v>92823</v>
       </c>
       <c r="B775" s="2">
-        <v>30</v>
+        <v>182</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A776" s="1">
-        <v>97776</v>
+        <v>92836</v>
       </c>
       <c r="B776" s="2">
-        <v>60</v>
+        <v>132</v>
       </c>
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
-        <v>97777</v>
+        <v>92984</v>
       </c>
       <c r="B777" s="2">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
-        <v>97780</v>
+        <v>93002</v>
       </c>
       <c r="B778" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
-        <v>97781</v>
+        <v>93016</v>
       </c>
       <c r="B779" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A780" s="1">
-        <v>97783</v>
+        <v>93067</v>
       </c>
       <c r="B780" s="2">
-        <v>20</v>
+        <v>858</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
-        <v>97784</v>
+        <v>93073</v>
       </c>
       <c r="B781" s="2">
-        <v>108</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A782" s="1">
-        <v>97785</v>
+        <v>94233</v>
       </c>
       <c r="B782" s="2">
-        <v>124</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
-        <v>97787</v>
+        <v>94314</v>
       </c>
       <c r="B783" s="2">
-        <v>76</v>
+        <v>956</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
-        <v>97788</v>
+        <v>94317</v>
       </c>
       <c r="B784" s="2">
-        <v>158</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
-        <v>97789</v>
+        <v>94683</v>
       </c>
       <c r="B785" s="2">
-        <v>102</v>
+        <v>14</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
-        <v>97790</v>
+        <v>94821</v>
       </c>
       <c r="B786" s="2">
-        <v>126</v>
+        <v>850</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
-        <v>97791</v>
+        <v>94830</v>
       </c>
       <c r="B787" s="2">
-        <v>92</v>
+        <v>552</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
-        <v>97792</v>
+        <v>94835</v>
       </c>
       <c r="B788" s="2">
-        <v>114</v>
+        <v>246</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
+        <v>95202</v>
+      </c>
+      <c r="B789" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A790" s="7">
+        <v>95211</v>
+      </c>
+      <c r="B790" s="5">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A791" s="7">
+        <v>95536</v>
+      </c>
+      <c r="B791" s="5">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A792" s="7">
+        <v>95538</v>
+      </c>
+      <c r="B792" s="5">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A793" s="7">
+        <v>95715</v>
+      </c>
+      <c r="B793" s="5">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A794" s="7">
+        <v>95731</v>
+      </c>
+      <c r="B794" s="5">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A795" s="7">
+        <v>95732</v>
+      </c>
+      <c r="B795" s="5">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A796" s="7">
+        <v>95740</v>
+      </c>
+      <c r="B796" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A797" s="7">
+        <v>95765</v>
+      </c>
+      <c r="B797" s="5">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A798" s="7">
+        <v>95768</v>
+      </c>
+      <c r="B798" s="5">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A799" s="7">
+        <v>95769</v>
+      </c>
+      <c r="B799" s="5">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A800" s="7">
+        <v>95770</v>
+      </c>
+      <c r="B800" s="5">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A801" s="7">
+        <v>95772</v>
+      </c>
+      <c r="B801" s="5">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A802" s="7">
+        <v>95774</v>
+      </c>
+      <c r="B802" s="5">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A803" s="7">
+        <v>95781</v>
+      </c>
+      <c r="B803" s="5">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A804" s="7">
+        <v>95907</v>
+      </c>
+      <c r="B804" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A805" s="7">
+        <v>95911</v>
+      </c>
+      <c r="B805" s="5">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A806" s="7">
+        <v>96507</v>
+      </c>
+      <c r="B806" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A807" s="7">
+        <v>96508</v>
+      </c>
+      <c r="B807" s="5">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A808" s="7">
+        <v>96510</v>
+      </c>
+      <c r="B808" s="5">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A809" s="7">
+        <v>96517</v>
+      </c>
+      <c r="B809" s="5">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A810" s="7">
+        <v>96539</v>
+      </c>
+      <c r="B810" s="5">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A811" s="7">
+        <v>97066</v>
+      </c>
+      <c r="B811" s="5">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A812" s="7">
+        <v>97067</v>
+      </c>
+      <c r="B812" s="5">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A813" s="7">
+        <v>97700</v>
+      </c>
+      <c r="B813" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A814" s="7">
+        <v>97701</v>
+      </c>
+      <c r="B814" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A815" s="7">
+        <v>97702</v>
+      </c>
+      <c r="B815" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A816" s="7">
+        <v>97703</v>
+      </c>
+      <c r="B816" s="5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A817" s="7">
+        <v>97707</v>
+      </c>
+      <c r="B817" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A818" s="7">
+        <v>97711</v>
+      </c>
+      <c r="B818" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A819" s="7">
+        <v>97712</v>
+      </c>
+      <c r="B819" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A820" s="7">
+        <v>97713</v>
+      </c>
+      <c r="B820" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A821" s="7">
+        <v>97715</v>
+      </c>
+      <c r="B821" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A822" s="7">
+        <v>97717</v>
+      </c>
+      <c r="B822" s="5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A823" s="7">
+        <v>97720</v>
+      </c>
+      <c r="B823" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A824" s="7">
+        <v>97721</v>
+      </c>
+      <c r="B824" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A825" s="7">
+        <v>97723</v>
+      </c>
+      <c r="B825" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A826" s="7">
+        <v>97724</v>
+      </c>
+      <c r="B826" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A827" s="7">
+        <v>97725</v>
+      </c>
+      <c r="B827" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A828" s="7">
+        <v>97727</v>
+      </c>
+      <c r="B828" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A829" s="7">
+        <v>97730</v>
+      </c>
+      <c r="B829" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A830" s="7">
+        <v>97731</v>
+      </c>
+      <c r="B830" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A831" s="7">
+        <v>97732</v>
+      </c>
+      <c r="B831" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A832" s="7">
+        <v>97735</v>
+      </c>
+      <c r="B832" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A833" s="7">
+        <v>97736</v>
+      </c>
+      <c r="B833" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A834" s="7">
+        <v>97742</v>
+      </c>
+      <c r="B834" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A835" s="7">
+        <v>97744</v>
+      </c>
+      <c r="B835" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A836" s="7">
+        <v>97747</v>
+      </c>
+      <c r="B836" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A837" s="7">
+        <v>97748</v>
+      </c>
+      <c r="B837" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A838" s="7">
+        <v>97749</v>
+      </c>
+      <c r="B838" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A839" s="7">
+        <v>97750</v>
+      </c>
+      <c r="B839" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A840" s="7">
+        <v>97756</v>
+      </c>
+      <c r="B840" s="5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A841" s="7">
+        <v>97768</v>
+      </c>
+      <c r="B841" s="5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A842" s="7">
+        <v>97770</v>
+      </c>
+      <c r="B842" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A843" s="7">
+        <v>97771</v>
+      </c>
+      <c r="B843" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A844" s="7">
+        <v>97776</v>
+      </c>
+      <c r="B844" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A845" s="7">
+        <v>97777</v>
+      </c>
+      <c r="B845" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A846" s="7">
+        <v>97781</v>
+      </c>
+      <c r="B846" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A847" s="7">
+        <v>97784</v>
+      </c>
+      <c r="B847" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A848" s="7">
+        <v>97785</v>
+      </c>
+      <c r="B848" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A849" s="7">
+        <v>97788</v>
+      </c>
+      <c r="B849" s="5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A850" s="7">
+        <v>97789</v>
+      </c>
+      <c r="B850" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A851" s="7">
+        <v>97790</v>
+      </c>
+      <c r="B851" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A852" s="7">
+        <v>97791</v>
+      </c>
+      <c r="B852" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A853" s="7">
+        <v>97792</v>
+      </c>
+      <c r="B853" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A854" s="7">
         <v>97793</v>
       </c>
-      <c r="B789" s="2">
+      <c r="B854" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A855" s="7">
+        <v>98131</v>
+      </c>
+      <c r="B855" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A856" s="7">
+        <v>98132</v>
+      </c>
+      <c r="B856" s="5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A857" s="7">
+        <v>98133</v>
+      </c>
+      <c r="B857" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A858" s="7">
+        <v>98134</v>
+      </c>
+      <c r="B858" s="5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A859" s="7">
+        <v>98135</v>
+      </c>
+      <c r="B859" s="5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A860" s="7">
+        <v>98136</v>
+      </c>
+      <c r="B860" s="5">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A861" s="7">
+        <v>98137</v>
+      </c>
+      <c r="B861" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A862" s="7">
+        <v>98138</v>
+      </c>
+      <c r="B862" s="5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A863" s="7">
+        <v>98139</v>
+      </c>
+      <c r="B863" s="5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A864" s="7">
+        <v>98140</v>
+      </c>
+      <c r="B864" s="5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A865" s="7">
+        <v>98141</v>
+      </c>
+      <c r="B865" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A866" s="7">
+        <v>98142</v>
+      </c>
+      <c r="B866" s="5">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A867" s="7">
+        <v>98143</v>
+      </c>
+      <c r="B867" s="5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A868" s="7">
+        <v>98144</v>
+      </c>
+      <c r="B868" s="5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A869" s="7">
+        <v>98145</v>
+      </c>
+      <c r="B869" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A870" s="7">
+        <v>98146</v>
+      </c>
+      <c r="B870" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A871" s="7">
+        <v>98147</v>
+      </c>
+      <c r="B871" s="5">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A872" s="7">
+        <v>98148</v>
+      </c>
+      <c r="B872" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A873" s="7">
+        <v>98149</v>
+      </c>
+      <c r="B873" s="5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A874" s="7">
+        <v>98150</v>
+      </c>
+      <c r="B874" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A875" s="7">
+        <v>98151</v>
+      </c>
+      <c r="B875" s="5">
         <v>112</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A876" s="7">
+        <v>98153</v>
+      </c>
+      <c r="B876" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A877" s="7">
+        <v>98154</v>
+      </c>
+      <c r="B877" s="5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A878" s="7">
+        <v>98155</v>
+      </c>
+      <c r="B878" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A879" s="7">
+        <v>98156</v>
+      </c>
+      <c r="B879" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A880" s="7">
+        <v>98157</v>
+      </c>
+      <c r="B880" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A881" s="7">
+        <v>98158</v>
+      </c>
+      <c r="B881" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A882" s="7">
+        <v>98159</v>
+      </c>
+      <c r="B882" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A883" s="7">
+        <v>98161</v>
+      </c>
+      <c r="B883" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A884" s="7">
+        <v>98162</v>
+      </c>
+      <c r="B884" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A885" s="7">
+        <v>98163</v>
+      </c>
+      <c r="B885" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A886" s="7">
+        <v>98164</v>
+      </c>
+      <c r="B886" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A887" s="7">
+        <v>98165</v>
+      </c>
+      <c r="B887" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A888" s="7">
+        <v>98166</v>
+      </c>
+      <c r="B888" s="5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A889" s="7">
+        <v>98167</v>
+      </c>
+      <c r="B889" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A890" s="7">
+        <v>98168</v>
+      </c>
+      <c r="B890" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A891" s="7">
+        <v>98169</v>
+      </c>
+      <c r="B891" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A892" s="7">
+        <v>98170</v>
+      </c>
+      <c r="B892" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A893" s="7">
+        <v>98171</v>
+      </c>
+      <c r="B893" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A894" s="7">
+        <v>98172</v>
+      </c>
+      <c r="B894" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A895" s="7">
+        <v>98173</v>
+      </c>
+      <c r="B895" s="5">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A896" s="7">
+        <v>98174</v>
+      </c>
+      <c r="B896" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A897" s="7">
+        <v>98175</v>
+      </c>
+      <c r="B897" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A898" s="7">
+        <v>98176</v>
+      </c>
+      <c r="B898" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A899" s="7">
+        <v>98177</v>
+      </c>
+      <c r="B899" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A900" s="7">
+        <v>98178</v>
+      </c>
+      <c r="B900" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A901" s="7">
+        <v>98179</v>
+      </c>
+      <c r="B901" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A902" s="7">
+        <v>98180</v>
+      </c>
+      <c r="B902" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A903" s="7">
+        <v>98256</v>
+      </c>
+      <c r="B903" s="5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A904" s="7">
+        <v>98257</v>
+      </c>
+      <c r="B904" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A905" s="7">
+        <v>98258</v>
+      </c>
+      <c r="B905" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A906" s="7">
+        <v>98259</v>
+      </c>
+      <c r="B906" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A907" s="7">
+        <v>98260</v>
+      </c>
+      <c r="B907" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A908" s="7">
+        <v>98261</v>
+      </c>
+      <c r="B908" s="5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A909" s="7">
+        <v>98262</v>
+      </c>
+      <c r="B909" s="5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A910" s="7">
+        <v>98263</v>
+      </c>
+      <c r="B910" s="5">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A911" s="7">
+        <v>98264</v>
+      </c>
+      <c r="B911" s="5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A912" s="7">
+        <v>98265</v>
+      </c>
+      <c r="B912" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A913" s="7">
+        <v>98266</v>
+      </c>
+      <c r="B913" s="5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A914" s="7">
+        <v>98267</v>
+      </c>
+      <c r="B914" s="5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A915" s="7">
+        <v>98268</v>
+      </c>
+      <c r="B915" s="5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A916" s="7">
+        <v>98269</v>
+      </c>
+      <c r="B916" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A917" s="7">
+        <v>98270</v>
+      </c>
+      <c r="B917" s="5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A918" s="7">
+        <v>98271</v>
+      </c>
+      <c r="B918" s="5">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A919" s="7">
+        <v>98545</v>
+      </c>
+      <c r="B919" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A920" s="7">
+        <v>98546</v>
+      </c>
+      <c r="B920" s="5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A921" s="7">
+        <v>98547</v>
+      </c>
+      <c r="B921" s="5">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A922" s="7">
+        <v>98548</v>
+      </c>
+      <c r="B922" s="5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A923" s="7">
+        <v>98549</v>
+      </c>
+      <c r="B923" s="5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A924" s="7">
+        <v>98550</v>
+      </c>
+      <c r="B924" s="5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A925" s="7">
+        <v>98551</v>
+      </c>
+      <c r="B925" s="5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A926" s="7">
+        <v>98552</v>
+      </c>
+      <c r="B926" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A927" s="7">
+        <v>98553</v>
+      </c>
+      <c r="B927" s="5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A928" s="7">
+        <v>98554</v>
+      </c>
+      <c r="B928" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A929" s="7">
+        <v>98555</v>
+      </c>
+      <c r="B929" s="5">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A930" s="7">
+        <v>98556</v>
+      </c>
+      <c r="B930" s="5">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A931" s="7">
+        <v>98557</v>
+      </c>
+      <c r="B931" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A932" s="7">
+        <v>98558</v>
+      </c>
+      <c r="B932" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A933" s="7">
+        <v>98559</v>
+      </c>
+      <c r="B933" s="5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A934" s="7">
+        <v>98560</v>
+      </c>
+      <c r="B934" s="5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A935" s="7">
+        <v>98561</v>
+      </c>
+      <c r="B935" s="5">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A936" s="7">
+        <v>98562</v>
+      </c>
+      <c r="B936" s="5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A937" s="7">
+        <v>98563</v>
+      </c>
+      <c r="B937" s="5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A938" s="7">
+        <v>98564</v>
+      </c>
+      <c r="B938" s="5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A939" s="7">
+        <v>98565</v>
+      </c>
+      <c r="B939" s="5">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A940" s="7">
+        <v>98566</v>
+      </c>
+      <c r="B940" s="5">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A941" s="7">
+        <v>98567</v>
+      </c>
+      <c r="B941" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A942" s="7">
+        <v>98568</v>
+      </c>
+      <c r="B942" s="5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A943" s="7">
+        <v>98569</v>
+      </c>
+      <c r="B943" s="5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A944" s="7">
+        <v>98570</v>
+      </c>
+      <c r="B944" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A945" s="7">
+        <v>98571</v>
+      </c>
+      <c r="B945" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A946" s="7">
+        <v>98572</v>
+      </c>
+      <c r="B946" s="5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A947" s="7">
+        <v>98573</v>
+      </c>
+      <c r="B947" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A948" s="7">
+        <v>98574</v>
+      </c>
+      <c r="B948" s="5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A949" s="7">
+        <v>98575</v>
+      </c>
+      <c r="B949" s="5">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A950" s="7">
+        <v>98576</v>
+      </c>
+      <c r="B950" s="5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A951" s="7">
+        <v>98577</v>
+      </c>
+      <c r="B951" s="5">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A952" s="7">
+        <v>98578</v>
+      </c>
+      <c r="B952" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A953" s="7">
+        <v>98579</v>
+      </c>
+      <c r="B953" s="5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A954" s="7">
+        <v>98580</v>
+      </c>
+      <c r="B954" s="5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A955" s="7">
+        <v>98593</v>
+      </c>
+      <c r="B955" s="5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A956" s="7">
+        <v>98594</v>
+      </c>
+      <c r="B956" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A957" s="7">
+        <v>98595</v>
+      </c>
+      <c r="B957" s="5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A958" s="7">
+        <v>98596</v>
+      </c>
+      <c r="B958" s="5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A959" s="7">
+        <v>98597</v>
+      </c>
+      <c r="B959" s="5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A960" s="7">
+        <v>98598</v>
+      </c>
+      <c r="B960" s="5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A961" s="7">
+        <v>98599</v>
+      </c>
+      <c r="B961" s="5">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Items_for_Replenishment.xlsx
+++ b/assets/Items_for_Replenishment.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{16F6234B-44D5-4D94-94DE-AFD351EDCDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC57D7B9-1BAC-4361-AB3F-D0AC315D0514}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8693808F-07EA-441E-A373-0AE1ED9D7257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B961"/>
+  <dimension ref="A1:B964"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="8" customWidth="1"/>
@@ -458,7 +458,7 @@
         <v>46496</v>
       </c>
       <c r="B2" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,7 +482,7 @@
         <v>74532</v>
       </c>
       <c r="B5" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -527,58 +527,58 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>84559</v>
+        <v>82692</v>
       </c>
       <c r="B11" s="2">
-        <v>2436</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>84662</v>
+        <v>84559</v>
       </c>
       <c r="B12" s="2">
-        <v>6510</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>86979</v>
+        <v>84662</v>
       </c>
       <c r="B13" s="2">
-        <v>166</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>87151</v>
+        <v>86979</v>
       </c>
       <c r="B14" s="2">
-        <v>7700</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>87154</v>
+        <v>87151</v>
       </c>
       <c r="B15" s="2">
-        <v>6600</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>87813</v>
+        <v>87154</v>
       </c>
       <c r="B16" s="2">
-        <v>418</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>87814</v>
+        <v>87813</v>
       </c>
       <c r="B17" s="2">
-        <v>8</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -607,279 +607,279 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>88571</v>
+        <v>88481</v>
       </c>
       <c r="B21" s="2">
-        <v>308</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>88609</v>
+        <v>88571</v>
       </c>
       <c r="B22" s="2">
-        <v>588</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>88810</v>
+        <v>88609</v>
       </c>
       <c r="B23" s="2">
-        <v>624</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>89952</v>
+        <v>88810</v>
       </c>
       <c r="B24" s="2">
-        <v>1342</v>
+        <v>623</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>90828</v>
+        <v>89952</v>
       </c>
       <c r="B25" s="2">
-        <v>110</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>90829</v>
+        <v>90828</v>
       </c>
       <c r="B26" s="2">
-        <v>460</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>90830</v>
+        <v>90829</v>
       </c>
       <c r="B27" s="2">
-        <v>3661</v>
+        <v>460</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>90831</v>
+        <v>90830</v>
       </c>
       <c r="B28" s="2">
-        <v>700</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>91015</v>
+        <v>90831</v>
       </c>
       <c r="B29" s="2">
-        <v>2</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>91290</v>
+        <v>91015</v>
       </c>
       <c r="B30" s="2">
-        <v>6600</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>92425</v>
+        <v>91101</v>
       </c>
       <c r="B31" s="2">
-        <v>686</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>92688</v>
+        <v>91290</v>
       </c>
       <c r="B32" s="2">
-        <v>1040</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>92725</v>
+        <v>92425</v>
       </c>
       <c r="B33" s="2">
-        <v>6500</v>
+        <v>682</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>92728</v>
+        <v>92688</v>
       </c>
       <c r="B34" s="2">
-        <v>320</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>92730</v>
+        <v>92725</v>
       </c>
       <c r="B35" s="2">
-        <v>640</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>92731</v>
+        <v>92728</v>
       </c>
       <c r="B36" s="2">
-        <v>970</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>93286</v>
+        <v>92730</v>
       </c>
       <c r="B37" s="2">
-        <v>26</v>
+        <v>640</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>93311</v>
+        <v>92731</v>
       </c>
       <c r="B38" s="2">
-        <v>116</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>93329</v>
+        <v>93286</v>
       </c>
       <c r="B39" s="2">
-        <v>2422</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>93332</v>
+        <v>93306</v>
       </c>
       <c r="B40" s="2">
-        <v>176</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>93333</v>
+        <v>93311</v>
       </c>
       <c r="B41" s="2">
-        <v>1772</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>94076</v>
+        <v>93329</v>
       </c>
       <c r="B42" s="2">
-        <v>3188</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>94319</v>
+        <v>93332</v>
       </c>
       <c r="B43" s="2">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>94320</v>
+        <v>93333</v>
       </c>
       <c r="B44" s="2">
-        <v>650</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>94321</v>
+        <v>94076</v>
       </c>
       <c r="B45" s="2">
-        <v>80</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>94322</v>
+        <v>94319</v>
       </c>
       <c r="B46" s="2">
-        <v>970</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>94916</v>
+        <v>94320</v>
       </c>
       <c r="B47" s="2">
-        <v>2850</v>
+        <v>650</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>94917</v>
+        <v>94321</v>
       </c>
       <c r="B48" s="2">
-        <v>2496</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>95677</v>
+        <v>94322</v>
       </c>
       <c r="B49" s="2">
-        <v>1936</v>
+        <v>970</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>95815</v>
+        <v>94916</v>
       </c>
       <c r="B50" s="2">
-        <v>1694</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>95947</v>
+        <v>94917</v>
       </c>
       <c r="B51" s="2">
-        <v>1044</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>96269</v>
+        <v>95677</v>
       </c>
       <c r="B52" s="2">
-        <v>4</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>96893</v>
+        <v>95815</v>
       </c>
       <c r="B53" s="2">
-        <v>32</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>96894</v>
+        <v>95947</v>
       </c>
       <c r="B54" s="2">
-        <v>2</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>96901</v>
+        <v>96269</v>
       </c>
       <c r="B55" s="2">
         <v>4</v>
@@ -887,303 +887,303 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>97525</v>
+        <v>96559</v>
       </c>
       <c r="B56" s="2">
-        <v>123</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>97526</v>
+        <v>96893</v>
       </c>
       <c r="B57" s="2">
-        <v>160</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>97527</v>
+        <v>96894</v>
       </c>
       <c r="B58" s="2">
-        <v>200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>97529</v>
+        <v>96901</v>
       </c>
       <c r="B59" s="2">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>97543</v>
+        <v>97525</v>
       </c>
       <c r="B60" s="2">
-        <v>68</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>97544</v>
+        <v>97526</v>
       </c>
       <c r="B61" s="2">
-        <v>24</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>97545</v>
+        <v>97527</v>
       </c>
       <c r="B62" s="2">
-        <v>30</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>97546</v>
+        <v>97528</v>
       </c>
       <c r="B63" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>97547</v>
+        <v>97529</v>
       </c>
       <c r="B64" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>97610</v>
+        <v>97536</v>
       </c>
       <c r="B65" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>97618</v>
+        <v>97542</v>
       </c>
       <c r="B66" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>97631</v>
+        <v>97543</v>
       </c>
       <c r="B67" s="2">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>97669</v>
+        <v>97544</v>
       </c>
       <c r="B68" s="2">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>97678</v>
+        <v>97545</v>
       </c>
       <c r="B69" s="2">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>97680</v>
+        <v>97546</v>
       </c>
       <c r="B70" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>97690</v>
+        <v>97547</v>
       </c>
       <c r="B71" s="2">
-        <v>240</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>97691</v>
+        <v>97610</v>
       </c>
       <c r="B72" s="2">
-        <v>238</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>97696</v>
+        <v>97618</v>
       </c>
       <c r="B73" s="2">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>97699</v>
+        <v>97631</v>
       </c>
       <c r="B74" s="2">
-        <v>136</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>97889</v>
+        <v>97679</v>
       </c>
       <c r="B75" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>97892</v>
+        <v>97681</v>
       </c>
       <c r="B76" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>98211</v>
+        <v>97690</v>
       </c>
       <c r="B77" s="2">
-        <v>80</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>98212</v>
+        <v>97691</v>
       </c>
       <c r="B78" s="2">
-        <v>140</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>98213</v>
+        <v>97696</v>
       </c>
       <c r="B79" s="2">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>98405</v>
+        <v>97699</v>
       </c>
       <c r="B80" s="2">
-        <v>2</v>
+        <v>136</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>98406</v>
+        <v>97889</v>
       </c>
       <c r="B81" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>98408</v>
+        <v>97892</v>
       </c>
       <c r="B82" s="2">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>98409</v>
+        <v>98211</v>
       </c>
       <c r="B83" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>98417</v>
+        <v>98212</v>
       </c>
       <c r="B84" s="2">
-        <v>2</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>98418</v>
+        <v>98213</v>
       </c>
       <c r="B85" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>98419</v>
+        <v>98405</v>
       </c>
       <c r="B86" s="2">
-        <v>74</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>98420</v>
+        <v>98406</v>
       </c>
       <c r="B87" s="2">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>98421</v>
+        <v>98408</v>
       </c>
       <c r="B88" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>98422</v>
+        <v>98409</v>
       </c>
       <c r="B89" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>98423</v>
+        <v>98412</v>
       </c>
       <c r="B90" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>98424</v>
+        <v>98414</v>
       </c>
       <c r="B91" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>98430</v>
+        <v>98416</v>
       </c>
       <c r="B92" s="2">
-        <v>4</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>98432</v>
+        <v>98417</v>
       </c>
       <c r="B93" s="2">
         <v>2</v>
@@ -1191,1327 +1191,1327 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>98600</v>
+        <v>98418</v>
       </c>
       <c r="B94" s="2">
-        <v>280</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>98601</v>
+        <v>98419</v>
       </c>
       <c r="B95" s="2">
-        <v>290</v>
+        <v>74</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>98602</v>
+        <v>98420</v>
       </c>
       <c r="B96" s="2">
-        <v>490</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>98657</v>
+        <v>98421</v>
       </c>
       <c r="B97" s="2">
-        <v>510</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>98658</v>
+        <v>98422</v>
       </c>
       <c r="B98" s="2">
-        <v>1000</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>99392</v>
+        <v>98423</v>
       </c>
       <c r="B99" s="2">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>99393</v>
+        <v>98424</v>
       </c>
       <c r="B100" s="2">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>99394</v>
+        <v>98430</v>
       </c>
       <c r="B101" s="2">
-        <v>141</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>99395</v>
+        <v>98600</v>
       </c>
       <c r="B102" s="2">
-        <v>141</v>
+        <v>280</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>3764</v>
+        <v>98601</v>
       </c>
       <c r="B103" s="2">
-        <v>324</v>
+        <v>290</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>3775</v>
+        <v>98602</v>
       </c>
       <c r="B104" s="2">
-        <v>1614</v>
+        <v>490</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>3786</v>
+        <v>98657</v>
       </c>
       <c r="B105" s="2">
-        <v>18</v>
+        <v>510</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>3798</v>
+        <v>98658</v>
       </c>
       <c r="B106" s="2">
-        <v>18</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>3809</v>
+        <v>99392</v>
       </c>
       <c r="B107" s="2">
-        <v>504</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>3821</v>
+        <v>99393</v>
       </c>
       <c r="B108" s="2">
-        <v>576</v>
+        <v>93</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>3833</v>
+        <v>99394</v>
       </c>
       <c r="B109" s="2">
-        <v>1098</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>16472</v>
+        <v>99395</v>
       </c>
       <c r="B110" s="2">
-        <v>8400</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>36371</v>
+        <v>3764</v>
       </c>
       <c r="B111" s="2">
-        <v>1888</v>
+        <v>324</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>38326</v>
+        <v>3775</v>
       </c>
       <c r="B112" s="2">
-        <v>30</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>54955</v>
+        <v>3798</v>
       </c>
       <c r="B113" s="2">
-        <v>864</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>59296</v>
+        <v>3809</v>
       </c>
       <c r="B114" s="2">
-        <v>164</v>
+        <v>504</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>68947</v>
+        <v>3821</v>
       </c>
       <c r="B115" s="2">
-        <v>690</v>
+        <v>576</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>68950</v>
+        <v>3833</v>
       </c>
       <c r="B116" s="2">
-        <v>12</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>68956</v>
+        <v>16472</v>
       </c>
       <c r="B117" s="2">
-        <v>54</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>68959</v>
+        <v>36371</v>
       </c>
       <c r="B118" s="2">
-        <v>180</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>70451</v>
+        <v>38326</v>
       </c>
       <c r="B119" s="2">
-        <v>3210</v>
+        <v>43</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>73723</v>
+        <v>54955</v>
       </c>
       <c r="B120" s="2">
-        <v>1020</v>
+        <v>864</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>74359</v>
+        <v>59296</v>
       </c>
       <c r="B121" s="2">
-        <v>864</v>
+        <v>168</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>97512</v>
+        <v>68947</v>
       </c>
       <c r="B122" s="2">
-        <v>4</v>
+        <v>690</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>98426</v>
+        <v>68950</v>
       </c>
       <c r="B123" s="2">
-        <v>134</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>98427</v>
+        <v>68956</v>
       </c>
       <c r="B124" s="2">
-        <v>312</v>
+        <v>54</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>6881</v>
+        <v>68959</v>
       </c>
       <c r="B125" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>9858</v>
+        <v>70451</v>
       </c>
       <c r="B126" s="2">
-        <v>33</v>
+        <v>3198</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>9859</v>
+        <v>73723</v>
       </c>
       <c r="B127" s="2">
-        <v>210</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>9963</v>
+        <v>74359</v>
       </c>
       <c r="B128" s="2">
-        <v>258</v>
+        <v>846</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>16075</v>
+        <v>97512</v>
       </c>
       <c r="B129" s="2">
-        <v>278</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>66615</v>
+        <v>98426</v>
       </c>
       <c r="B130" s="2">
-        <v>29</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>66616</v>
+        <v>98427</v>
       </c>
       <c r="B131" s="2">
-        <v>23</v>
+        <v>312</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>68877</v>
+        <v>6881</v>
       </c>
       <c r="B132" s="2">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>68878</v>
+        <v>9858</v>
       </c>
       <c r="B133" s="2">
-        <v>183</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>68879</v>
+        <v>9859</v>
       </c>
       <c r="B134" s="2">
-        <v>364</v>
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>68880</v>
+        <v>9963</v>
       </c>
       <c r="B135" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>80319</v>
+        <v>16075</v>
       </c>
       <c r="B136" s="2">
-        <v>3</v>
+        <v>280</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>84851</v>
+        <v>66615</v>
       </c>
       <c r="B137" s="2">
-        <v>371</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>84852</v>
+        <v>66616</v>
       </c>
       <c r="B138" s="2">
-        <v>355</v>
+        <v>22</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>84853</v>
+        <v>68877</v>
       </c>
       <c r="B139" s="2">
-        <v>198</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>84854</v>
+        <v>68878</v>
       </c>
       <c r="B140" s="2">
-        <v>312</v>
+        <v>182</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>84855</v>
+        <v>68879</v>
       </c>
       <c r="B141" s="2">
-        <v>250</v>
+        <v>362</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>85743</v>
+        <v>68880</v>
       </c>
       <c r="B142" s="2">
-        <v>321</v>
+        <v>267</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>86015</v>
+        <v>80318</v>
       </c>
       <c r="B143" s="2">
-        <v>209</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>86016</v>
+        <v>84851</v>
       </c>
       <c r="B144" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>86265</v>
+        <v>84852</v>
       </c>
       <c r="B145" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>86266</v>
+        <v>84853</v>
       </c>
       <c r="B146" s="2">
-        <v>339</v>
+        <v>198</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>86267</v>
+        <v>84854</v>
       </c>
       <c r="B147" s="2">
-        <v>3</v>
+        <v>311</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>86268</v>
+        <v>84855</v>
       </c>
       <c r="B148" s="2">
-        <v>401</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>86269</v>
+        <v>85743</v>
       </c>
       <c r="B149" s="2">
-        <v>156</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>86285</v>
+        <v>86015</v>
       </c>
       <c r="B150" s="2">
-        <v>59</v>
+        <v>209</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>86286</v>
+        <v>86016</v>
       </c>
       <c r="B151" s="2">
-        <v>623</v>
+        <v>78</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>86287</v>
+        <v>86265</v>
       </c>
       <c r="B152" s="2">
-        <v>660</v>
+        <v>27</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>86288</v>
+        <v>86266</v>
       </c>
       <c r="B153" s="2">
-        <v>493</v>
+        <v>346</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>86289</v>
+        <v>86268</v>
       </c>
       <c r="B154" s="2">
-        <v>237</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>87346</v>
+        <v>86269</v>
       </c>
       <c r="B155" s="2">
-        <v>18</v>
+        <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>87406</v>
+        <v>86285</v>
       </c>
       <c r="B156" s="2">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>87408</v>
+        <v>86286</v>
       </c>
       <c r="B157" s="2">
-        <v>1</v>
+        <v>628</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>87416</v>
+        <v>86287</v>
       </c>
       <c r="B158" s="2">
-        <v>391</v>
+        <v>564</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>87417</v>
+        <v>86288</v>
       </c>
       <c r="B159" s="2">
-        <v>225</v>
+        <v>516</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>87418</v>
+        <v>86289</v>
       </c>
       <c r="B160" s="2">
-        <v>3</v>
+        <v>235</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>87419</v>
+        <v>87346</v>
       </c>
       <c r="B161" s="2">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>87882</v>
+        <v>87407</v>
       </c>
       <c r="B162" s="2">
-        <v>723</v>
+        <v>175</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>87883</v>
+        <v>87408</v>
       </c>
       <c r="B163" s="2">
-        <v>485</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>87884</v>
+        <v>87410</v>
       </c>
       <c r="B164" s="2">
-        <v>125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>87885</v>
+        <v>87416</v>
       </c>
       <c r="B165" s="2">
-        <v>174</v>
+        <v>391</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>87886</v>
+        <v>87417</v>
       </c>
       <c r="B166" s="2">
-        <v>190</v>
+        <v>227</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>87932</v>
+        <v>87418</v>
       </c>
       <c r="B167" s="2">
-        <v>749</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>87933</v>
+        <v>87419</v>
       </c>
       <c r="B168" s="2">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>87934</v>
+        <v>87420</v>
       </c>
       <c r="B169" s="2">
-        <v>503</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>87937</v>
+        <v>87882</v>
       </c>
       <c r="B170" s="2">
-        <v>507</v>
+        <v>723</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>87938</v>
+        <v>87883</v>
       </c>
       <c r="B171" s="2">
-        <v>724</v>
+        <v>485</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>87939</v>
+        <v>87884</v>
       </c>
       <c r="B172" s="2">
-        <v>420</v>
+        <v>125</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>87941</v>
+        <v>87885</v>
       </c>
       <c r="B173" s="2">
-        <v>48</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>88653</v>
+        <v>87886</v>
       </c>
       <c r="B174" s="2">
-        <v>443</v>
+        <v>190</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>88654</v>
+        <v>87932</v>
       </c>
       <c r="B175" s="2">
-        <v>480</v>
+        <v>737</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>88655</v>
+        <v>87933</v>
       </c>
       <c r="B176" s="2">
-        <v>576</v>
+        <v>40</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>88656</v>
+        <v>87934</v>
       </c>
       <c r="B177" s="2">
-        <v>170</v>
+        <v>508</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>88657</v>
+        <v>87937</v>
       </c>
       <c r="B178" s="2">
-        <v>98</v>
+        <v>509</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>89339</v>
+        <v>87938</v>
       </c>
       <c r="B179" s="2">
-        <v>1</v>
+        <v>723</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>89986</v>
+        <v>87939</v>
       </c>
       <c r="B180" s="2">
-        <v>1</v>
+        <v>468</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>90566</v>
+        <v>87941</v>
       </c>
       <c r="B181" s="2">
-        <v>544</v>
+        <v>48</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>90567</v>
+        <v>88653</v>
       </c>
       <c r="B182" s="2">
-        <v>34</v>
+        <v>439</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>90568</v>
+        <v>88654</v>
       </c>
       <c r="B183" s="2">
-        <v>401</v>
+        <v>480</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>90569</v>
+        <v>88655</v>
       </c>
       <c r="B184" s="2">
-        <v>257</v>
+        <v>576</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>90570</v>
+        <v>88656</v>
       </c>
       <c r="B185" s="2">
-        <v>212</v>
+        <v>170</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>90792</v>
+        <v>88657</v>
       </c>
       <c r="B186" s="2">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>90922</v>
+        <v>89339</v>
       </c>
       <c r="B187" s="2">
-        <v>730</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>90923</v>
+        <v>89983</v>
       </c>
       <c r="B188" s="2">
-        <v>684</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>90924</v>
+        <v>89986</v>
       </c>
       <c r="B189" s="2">
-        <v>278</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>90925</v>
+        <v>90566</v>
       </c>
       <c r="B190" s="2">
-        <v>216</v>
+        <v>543</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>90926</v>
+        <v>90567</v>
       </c>
       <c r="B191" s="2">
-        <v>182</v>
+        <v>34</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>91208</v>
+        <v>90568</v>
       </c>
       <c r="B192" s="2">
-        <v>39</v>
+        <v>402</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>91209</v>
+        <v>90569</v>
       </c>
       <c r="B193" s="2">
-        <v>55</v>
+        <v>257</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>91279</v>
+        <v>90570</v>
       </c>
       <c r="B194" s="2">
-        <v>562</v>
+        <v>212</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>91280</v>
+        <v>90922</v>
       </c>
       <c r="B195" s="2">
-        <v>658</v>
+        <v>731</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>91765</v>
+        <v>90923</v>
       </c>
       <c r="B196" s="2">
-        <v>389</v>
+        <v>684</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>91766</v>
+        <v>90924</v>
       </c>
       <c r="B197" s="2">
-        <v>182</v>
+        <v>296</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>91769</v>
+        <v>90925</v>
       </c>
       <c r="B198" s="2">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>91815</v>
+        <v>90926</v>
       </c>
       <c r="B199" s="2">
-        <v>335</v>
+        <v>183</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>91816</v>
+        <v>91208</v>
       </c>
       <c r="B200" s="2">
-        <v>990</v>
+        <v>39</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>91817</v>
+        <v>91209</v>
       </c>
       <c r="B201" s="2">
-        <v>280</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>91818</v>
+        <v>91279</v>
       </c>
       <c r="B202" s="2">
-        <v>22</v>
+        <v>561</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>91819</v>
+        <v>91280</v>
       </c>
       <c r="B203" s="2">
-        <v>37</v>
+        <v>658</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>91895</v>
+        <v>91765</v>
       </c>
       <c r="B204" s="2">
-        <v>3</v>
+        <v>389</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>92284</v>
+        <v>91766</v>
       </c>
       <c r="B205" s="2">
-        <v>29</v>
+        <v>182</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>92285</v>
+        <v>91769</v>
       </c>
       <c r="B206" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>92288</v>
+        <v>91815</v>
       </c>
       <c r="B207" s="2">
-        <v>1080</v>
+        <v>367</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>92289</v>
+        <v>91816</v>
       </c>
       <c r="B208" s="2">
-        <v>936</v>
+        <v>985</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>92290</v>
+        <v>91817</v>
       </c>
       <c r="B209" s="2">
-        <v>611</v>
+        <v>343</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>92291</v>
+        <v>91819</v>
       </c>
       <c r="B210" s="2">
-        <v>461</v>
+        <v>37</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>92292</v>
+        <v>91895</v>
       </c>
       <c r="B211" s="2">
-        <v>222</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>92409</v>
+        <v>92283</v>
       </c>
       <c r="B212" s="2">
-        <v>307</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>92410</v>
+        <v>92284</v>
       </c>
       <c r="B213" s="2">
-        <v>391</v>
+        <v>60</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>92411</v>
+        <v>92285</v>
       </c>
       <c r="B214" s="2">
-        <v>264</v>
+        <v>104</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>92412</v>
+        <v>92288</v>
       </c>
       <c r="B215" s="2">
-        <v>406</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>92413</v>
+        <v>92289</v>
       </c>
       <c r="B216" s="2">
-        <v>141</v>
+        <v>938</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>92542</v>
+        <v>92290</v>
       </c>
       <c r="B217" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>92591</v>
+        <v>92291</v>
       </c>
       <c r="B218" s="2">
-        <v>2</v>
+        <v>461</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>93238</v>
+        <v>92292</v>
       </c>
       <c r="B219" s="2">
-        <v>1287</v>
+        <v>222</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>93239</v>
+        <v>92409</v>
       </c>
       <c r="B220" s="2">
-        <v>1044</v>
+        <v>307</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>93240</v>
+        <v>92410</v>
       </c>
       <c r="B221" s="2">
-        <v>678</v>
+        <v>388</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>93241</v>
+        <v>92411</v>
       </c>
       <c r="B222" s="2">
-        <v>833</v>
+        <v>263</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>93242</v>
+        <v>92412</v>
       </c>
       <c r="B223" s="2">
-        <v>476</v>
+        <v>405</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>94139</v>
+        <v>92413</v>
       </c>
       <c r="B224" s="2">
-        <v>1076</v>
+        <v>140</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>94140</v>
+        <v>92542</v>
       </c>
       <c r="B225" s="2">
-        <v>1356</v>
+        <v>51</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>94141</v>
+        <v>92592</v>
       </c>
       <c r="B226" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>94142</v>
+        <v>93238</v>
       </c>
       <c r="B227" s="2">
-        <v>504</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>94143</v>
+        <v>93239</v>
       </c>
       <c r="B228" s="2">
-        <v>2</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>94592</v>
+        <v>93240</v>
       </c>
       <c r="B229" s="2">
-        <v>394</v>
+        <v>677</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>94593</v>
+        <v>93241</v>
       </c>
       <c r="B230" s="2">
-        <v>349</v>
+        <v>833</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>94594</v>
+        <v>93242</v>
       </c>
       <c r="B231" s="2">
-        <v>308</v>
+        <v>477</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>94595</v>
+        <v>94139</v>
       </c>
       <c r="B232" s="2">
-        <v>249</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>94596</v>
+        <v>94140</v>
       </c>
       <c r="B233" s="2">
-        <v>116</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>95082</v>
+        <v>94141</v>
       </c>
       <c r="B234" s="2">
-        <v>206</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>95083</v>
+        <v>94142</v>
       </c>
       <c r="B235" s="2">
-        <v>185</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>95084</v>
+        <v>94592</v>
       </c>
       <c r="B236" s="2">
-        <v>53</v>
+        <v>392</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>95085</v>
+        <v>94593</v>
       </c>
       <c r="B237" s="2">
-        <v>60</v>
+        <v>350</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>95086</v>
+        <v>94594</v>
       </c>
       <c r="B238" s="2">
-        <v>38</v>
+        <v>307</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>95132</v>
+        <v>94595</v>
       </c>
       <c r="B239" s="2">
-        <v>4</v>
+        <v>249</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>95133</v>
+        <v>94596</v>
       </c>
       <c r="B240" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>95134</v>
+        <v>95082</v>
       </c>
       <c r="B241" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>95135</v>
+        <v>95083</v>
       </c>
       <c r="B242" s="2">
-        <v>14</v>
+        <v>191</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>95136</v>
+        <v>95084</v>
       </c>
       <c r="B243" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>95973</v>
+        <v>95085</v>
       </c>
       <c r="B244" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>95976</v>
+        <v>95086</v>
       </c>
       <c r="B245" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>95977</v>
+        <v>95132</v>
       </c>
       <c r="B246" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>96073</v>
+        <v>95133</v>
       </c>
       <c r="B247" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>96085</v>
+        <v>95134</v>
       </c>
       <c r="B248" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>96086</v>
+        <v>95135</v>
       </c>
       <c r="B249" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>96087</v>
+        <v>95136</v>
       </c>
       <c r="B250" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>96095</v>
+        <v>95976</v>
       </c>
       <c r="B251" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>96096</v>
+        <v>96082</v>
       </c>
       <c r="B252" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>96100</v>
+        <v>96085</v>
       </c>
       <c r="B253" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>96101</v>
+        <v>96086</v>
       </c>
       <c r="B254" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>96105</v>
+        <v>96087</v>
       </c>
       <c r="B255" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>96107</v>
+        <v>96095</v>
       </c>
       <c r="B256" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>96109</v>
+        <v>96096</v>
       </c>
       <c r="B257" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>96114</v>
+        <v>96100</v>
       </c>
       <c r="B258" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>96117</v>
+        <v>96101</v>
       </c>
       <c r="B259" s="2">
         <v>8</v>
@@ -2519,87 +2519,87 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>96120</v>
+        <v>96103</v>
       </c>
       <c r="B260" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>96121</v>
+        <v>96105</v>
       </c>
       <c r="B261" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>96122</v>
+        <v>96107</v>
       </c>
       <c r="B262" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>96123</v>
+        <v>96111</v>
       </c>
       <c r="B263" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>96124</v>
+        <v>96116</v>
       </c>
       <c r="B264" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>96125</v>
+        <v>96117</v>
       </c>
       <c r="B265" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>96126</v>
+        <v>96120</v>
       </c>
       <c r="B266" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>96128</v>
+        <v>96121</v>
       </c>
       <c r="B267" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>96129</v>
+        <v>96122</v>
       </c>
       <c r="B268" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>96130</v>
+        <v>96123</v>
       </c>
       <c r="B269" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>96131</v>
+        <v>96124</v>
       </c>
       <c r="B270" s="2">
         <v>12</v>
@@ -2607,103 +2607,103 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>96133</v>
+        <v>96125</v>
       </c>
       <c r="B271" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>96134</v>
+        <v>96126</v>
       </c>
       <c r="B272" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>96135</v>
+        <v>96128</v>
       </c>
       <c r="B273" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>96136</v>
+        <v>96129</v>
       </c>
       <c r="B274" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>96170</v>
+        <v>96130</v>
       </c>
       <c r="B275" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>96178</v>
+        <v>96131</v>
       </c>
       <c r="B276" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>96788</v>
+        <v>96132</v>
       </c>
       <c r="B277" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>96800</v>
+        <v>96133</v>
       </c>
       <c r="B278" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>96812</v>
+        <v>96134</v>
       </c>
       <c r="B279" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>96813</v>
+        <v>96135</v>
       </c>
       <c r="B280" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>96818</v>
+        <v>96136</v>
       </c>
       <c r="B281" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>96819</v>
+        <v>96788</v>
       </c>
       <c r="B282" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>96821</v>
+        <v>96813</v>
       </c>
       <c r="B283" s="2">
         <v>1</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>96834</v>
+        <v>96819</v>
       </c>
       <c r="B284" s="2">
         <v>1</v>
@@ -2719,87 +2719,87 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>97308</v>
+        <v>96821</v>
       </c>
       <c r="B285" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>97310</v>
+        <v>96822</v>
       </c>
       <c r="B286" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>97312</v>
+        <v>96836</v>
       </c>
       <c r="B287" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>97319</v>
+        <v>97299</v>
       </c>
       <c r="B288" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>97324</v>
+        <v>97303</v>
       </c>
       <c r="B289" s="2">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>97327</v>
+        <v>97308</v>
       </c>
       <c r="B290" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>97330</v>
+        <v>97310</v>
       </c>
       <c r="B291" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>97343</v>
+        <v>97319</v>
       </c>
       <c r="B292" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>97346</v>
+        <v>97324</v>
       </c>
       <c r="B293" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
-        <v>97348</v>
+        <v>97327</v>
       </c>
       <c r="B294" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
-        <v>97352</v>
+        <v>97331</v>
       </c>
       <c r="B295" s="2">
         <v>1</v>
@@ -2807,111 +2807,111 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
-        <v>97353</v>
+        <v>97344</v>
       </c>
       <c r="B296" s="2">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
-        <v>97354</v>
+        <v>97346</v>
       </c>
       <c r="B297" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
-        <v>97355</v>
+        <v>97353</v>
       </c>
       <c r="B298" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
-        <v>97356</v>
+        <v>97354</v>
       </c>
       <c r="B299" s="2">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
-        <v>97357</v>
+        <v>97355</v>
       </c>
       <c r="B300" s="2">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
-        <v>97359</v>
+        <v>97356</v>
       </c>
       <c r="B301" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
-        <v>97360</v>
+        <v>97357</v>
       </c>
       <c r="B302" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
-        <v>97365</v>
+        <v>97358</v>
       </c>
       <c r="B303" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
-        <v>97367</v>
+        <v>97359</v>
       </c>
       <c r="B304" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
-        <v>97382</v>
+        <v>97364</v>
       </c>
       <c r="B305" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
-        <v>97383</v>
+        <v>97369</v>
       </c>
       <c r="B306" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
-        <v>97384</v>
+        <v>97373</v>
       </c>
       <c r="B307" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
-        <v>97389</v>
+        <v>97374</v>
       </c>
       <c r="B308" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>97392</v>
+        <v>97377</v>
       </c>
       <c r="B309" s="2">
         <v>1</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>97393</v>
+        <v>97380</v>
       </c>
       <c r="B310" s="2">
         <v>1</v>
@@ -2927,15 +2927,15 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
-        <v>97430</v>
+        <v>97400</v>
       </c>
       <c r="B311" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
-        <v>97445</v>
+        <v>97405</v>
       </c>
       <c r="B312" s="2">
         <v>1</v>
@@ -2943,31 +2943,31 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
-        <v>97449</v>
+        <v>97437</v>
       </c>
       <c r="B313" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
-        <v>97455</v>
+        <v>97439</v>
       </c>
       <c r="B314" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
-        <v>97472</v>
+        <v>97440</v>
       </c>
       <c r="B315" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
-        <v>97484</v>
+        <v>97441</v>
       </c>
       <c r="B316" s="2">
         <v>1</v>
@@ -2975,1135 +2975,1135 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>97494</v>
+        <v>97444</v>
       </c>
       <c r="B317" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>97496</v>
+        <v>97447</v>
       </c>
       <c r="B318" s="2">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>97497</v>
+        <v>97450</v>
       </c>
       <c r="B319" s="2">
-        <v>87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>97498</v>
+        <v>97451</v>
       </c>
       <c r="B320" s="2">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>97499</v>
+        <v>97491</v>
       </c>
       <c r="B321" s="2">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>97500</v>
+        <v>97493</v>
       </c>
       <c r="B322" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>97504</v>
+        <v>97496</v>
       </c>
       <c r="B323" s="2">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>97505</v>
+        <v>97497</v>
       </c>
       <c r="B324" s="2">
-        <v>3</v>
+        <v>88</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>97797</v>
+        <v>97498</v>
       </c>
       <c r="B325" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>97798</v>
+        <v>97499</v>
       </c>
       <c r="B326" s="2">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>97799</v>
+        <v>97500</v>
       </c>
       <c r="B327" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>97800</v>
+        <v>97503</v>
       </c>
       <c r="B328" s="2">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>97801</v>
+        <v>97504</v>
       </c>
       <c r="B329" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>97803</v>
+        <v>97505</v>
       </c>
       <c r="B330" s="2">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>97804</v>
+        <v>97797</v>
       </c>
       <c r="B331" s="2">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>97805</v>
+        <v>97798</v>
       </c>
       <c r="B332" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>97806</v>
+        <v>97799</v>
       </c>
       <c r="B333" s="2">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>97813</v>
+        <v>97800</v>
       </c>
       <c r="B334" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>97814</v>
+        <v>97801</v>
       </c>
       <c r="B335" s="2">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>97815</v>
+        <v>97813</v>
       </c>
       <c r="B336" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>97817</v>
+        <v>97815</v>
       </c>
       <c r="B337" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>97818</v>
+        <v>97817</v>
       </c>
       <c r="B338" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
-        <v>97819</v>
+        <v>97818</v>
       </c>
       <c r="B339" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>97832</v>
+        <v>97819</v>
       </c>
       <c r="B340" s="2">
-        <v>87</v>
+        <v>26</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>97833</v>
+        <v>97823</v>
       </c>
       <c r="B341" s="2">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>97834</v>
+        <v>97825</v>
       </c>
       <c r="B342" s="2">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>97835</v>
+        <v>97832</v>
       </c>
       <c r="B343" s="2">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>97836</v>
+        <v>97833</v>
       </c>
       <c r="B344" s="2">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>97863</v>
+        <v>97834</v>
       </c>
       <c r="B345" s="2">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>97864</v>
+        <v>97835</v>
       </c>
       <c r="B346" s="2">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>97871</v>
+        <v>97836</v>
       </c>
       <c r="B347" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>97872</v>
+        <v>97863</v>
       </c>
       <c r="B348" s="2">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>97873</v>
+        <v>97864</v>
       </c>
       <c r="B349" s="2">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>97874</v>
+        <v>97871</v>
       </c>
       <c r="B350" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>97875</v>
+        <v>97872</v>
       </c>
       <c r="B351" s="2">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>97876</v>
+        <v>97873</v>
       </c>
       <c r="B352" s="2">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
-        <v>97877</v>
+        <v>97874</v>
       </c>
       <c r="B353" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
-        <v>97878</v>
+        <v>97875</v>
       </c>
       <c r="B354" s="2">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>97879</v>
+        <v>97876</v>
       </c>
       <c r="B355" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
-        <v>97880</v>
+        <v>97877</v>
       </c>
       <c r="B356" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
-        <v>98272</v>
+        <v>97878</v>
       </c>
       <c r="B357" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
-        <v>98273</v>
+        <v>97879</v>
       </c>
       <c r="B358" s="2">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
-        <v>98274</v>
+        <v>97880</v>
       </c>
       <c r="B359" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
-        <v>98275</v>
+        <v>98272</v>
       </c>
       <c r="B360" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
-        <v>98276</v>
+        <v>98273</v>
       </c>
       <c r="B361" s="2">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
-        <v>98277</v>
+        <v>98274</v>
       </c>
       <c r="B362" s="2">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
-        <v>98278</v>
+        <v>98275</v>
       </c>
       <c r="B363" s="2">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
-        <v>98279</v>
+        <v>98276</v>
       </c>
       <c r="B364" s="2">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
-        <v>98280</v>
+        <v>98277</v>
       </c>
       <c r="B365" s="2">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
-        <v>98281</v>
+        <v>98278</v>
       </c>
       <c r="B366" s="2">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
-        <v>98282</v>
+        <v>98279</v>
       </c>
       <c r="B367" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
-        <v>98283</v>
+        <v>98280</v>
       </c>
       <c r="B368" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
-        <v>98284</v>
+        <v>98281</v>
       </c>
       <c r="B369" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
-        <v>98285</v>
+        <v>98282</v>
       </c>
       <c r="B370" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
-        <v>98286</v>
+        <v>98283</v>
       </c>
       <c r="B371" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
-        <v>98287</v>
+        <v>98284</v>
       </c>
       <c r="B372" s="2">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
-        <v>98288</v>
+        <v>98285</v>
       </c>
       <c r="B373" s="2">
-        <v>97</v>
+        <v>13</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
-        <v>98289</v>
+        <v>98286</v>
       </c>
       <c r="B374" s="2">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
-        <v>98290</v>
+        <v>98287</v>
       </c>
       <c r="B375" s="2">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
-        <v>98291</v>
+        <v>98288</v>
       </c>
       <c r="B376" s="2">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
-        <v>98292</v>
+        <v>98289</v>
       </c>
       <c r="B377" s="2">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
-        <v>98293</v>
+        <v>98290</v>
       </c>
       <c r="B378" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
-        <v>98294</v>
+        <v>98291</v>
       </c>
       <c r="B379" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
-        <v>98295</v>
+        <v>98293</v>
       </c>
       <c r="B380" s="2">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
-        <v>98297</v>
+        <v>98294</v>
       </c>
       <c r="B381" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
-        <v>98298</v>
+        <v>98295</v>
       </c>
       <c r="B382" s="2">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
-        <v>98299</v>
+        <v>98297</v>
       </c>
       <c r="B383" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
-        <v>98300</v>
+        <v>98298</v>
       </c>
       <c r="B384" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
-        <v>98301</v>
+        <v>98299</v>
       </c>
       <c r="B385" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
-        <v>98307</v>
+        <v>98300</v>
       </c>
       <c r="B386" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
-        <v>98308</v>
+        <v>98301</v>
       </c>
       <c r="B387" s="2">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
-        <v>98309</v>
+        <v>98307</v>
       </c>
       <c r="B388" s="2">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
-        <v>98310</v>
+        <v>98308</v>
       </c>
       <c r="B389" s="2">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
-        <v>98311</v>
+        <v>98309</v>
       </c>
       <c r="B390" s="2">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
-        <v>98332</v>
+        <v>98310</v>
       </c>
       <c r="B391" s="2">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
-        <v>98333</v>
+        <v>98332</v>
       </c>
       <c r="B392" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
-        <v>98334</v>
+        <v>98333</v>
       </c>
       <c r="B393" s="2">
-        <v>37</v>
+        <v>62</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
-        <v>98335</v>
+        <v>98334</v>
       </c>
       <c r="B394" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
-        <v>98336</v>
+        <v>98335</v>
       </c>
       <c r="B395" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
-        <v>98340</v>
+        <v>98336</v>
       </c>
       <c r="B396" s="2">
-        <v>91</v>
+        <v>4</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
-        <v>98341</v>
+        <v>98340</v>
       </c>
       <c r="B397" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
-        <v>98342</v>
+        <v>98341</v>
       </c>
       <c r="B398" s="2">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
-        <v>98343</v>
+        <v>98342</v>
       </c>
       <c r="B399" s="2">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
-        <v>98344</v>
+        <v>98343</v>
       </c>
       <c r="B400" s="2">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
-        <v>98345</v>
+        <v>98344</v>
       </c>
       <c r="B401" s="2">
-        <v>76</v>
+        <v>20</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
-        <v>98346</v>
+        <v>98345</v>
       </c>
       <c r="B402" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
-        <v>98347</v>
+        <v>98346</v>
       </c>
       <c r="B403" s="2">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
-        <v>98348</v>
+        <v>98347</v>
       </c>
       <c r="B404" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
-        <v>98349</v>
+        <v>98348</v>
       </c>
       <c r="B405" s="2">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
-        <v>98350</v>
+        <v>98349</v>
       </c>
       <c r="B406" s="2">
-        <v>85</v>
+        <v>26</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
-        <v>98351</v>
+        <v>98350</v>
       </c>
       <c r="B407" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
-        <v>98352</v>
+        <v>98351</v>
       </c>
       <c r="B408" s="2">
-        <v>30</v>
+        <v>93</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
-        <v>98353</v>
+        <v>98352</v>
       </c>
       <c r="B409" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
-        <v>98354</v>
+        <v>98353</v>
       </c>
       <c r="B410" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
-        <v>98355</v>
+        <v>98354</v>
       </c>
       <c r="B411" s="2">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
-        <v>98356</v>
+        <v>98355</v>
       </c>
       <c r="B412" s="2">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
-        <v>98357</v>
+        <v>98356</v>
       </c>
       <c r="B413" s="2">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
-        <v>98358</v>
+        <v>98357</v>
       </c>
       <c r="B414" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
-        <v>98359</v>
+        <v>98358</v>
       </c>
       <c r="B415" s="2">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
-        <v>98360</v>
+        <v>98359</v>
       </c>
       <c r="B416" s="2">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
-        <v>98361</v>
+        <v>98360</v>
       </c>
       <c r="B417" s="2">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
-        <v>98362</v>
+        <v>98361</v>
       </c>
       <c r="B418" s="2">
-        <v>67</v>
+        <v>111</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
-        <v>98363</v>
+        <v>98362</v>
       </c>
       <c r="B419" s="2">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
-        <v>98364</v>
+        <v>98363</v>
       </c>
       <c r="B420" s="2">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
-        <v>98365</v>
+        <v>98364</v>
       </c>
       <c r="B421" s="2">
-        <v>91</v>
+        <v>25</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
-        <v>98366</v>
+        <v>98365</v>
       </c>
       <c r="B422" s="2">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
-        <v>98367</v>
+        <v>98366</v>
       </c>
       <c r="B423" s="2">
-        <v>51</v>
+        <v>102</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
-        <v>98368</v>
+        <v>98367</v>
       </c>
       <c r="B424" s="2">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
-        <v>98369</v>
+        <v>98368</v>
       </c>
       <c r="B425" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
-        <v>98370</v>
+        <v>98369</v>
       </c>
       <c r="B426" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
-        <v>98371</v>
+        <v>98370</v>
       </c>
       <c r="B427" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
-        <v>98372</v>
+        <v>98371</v>
       </c>
       <c r="B428" s="2">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
-        <v>98373</v>
+        <v>98372</v>
       </c>
       <c r="B429" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
-        <v>98374</v>
+        <v>98373</v>
       </c>
       <c r="B430" s="2">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
-        <v>98375</v>
+        <v>98374</v>
       </c>
       <c r="B431" s="2">
-        <v>75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
-        <v>98376</v>
+        <v>98375</v>
       </c>
       <c r="B432" s="2">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
-        <v>98377</v>
+        <v>98376</v>
       </c>
       <c r="B433" s="2">
-        <v>53</v>
+        <v>95</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
-        <v>98378</v>
+        <v>98377</v>
       </c>
       <c r="B434" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
-        <v>98379</v>
+        <v>98378</v>
       </c>
       <c r="B435" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
-        <v>98380</v>
+        <v>98379</v>
       </c>
       <c r="B436" s="2">
-        <v>79</v>
+        <v>24</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
-        <v>98381</v>
+        <v>98380</v>
       </c>
       <c r="B437" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
-        <v>98382</v>
+        <v>98381</v>
       </c>
       <c r="B438" s="2">
-        <v>55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
-        <v>98383</v>
+        <v>98382</v>
       </c>
       <c r="B439" s="2">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
-        <v>98384</v>
+        <v>98383</v>
       </c>
       <c r="B440" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
-        <v>98385</v>
+        <v>98384</v>
       </c>
       <c r="B441" s="2">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
-        <v>98386</v>
+        <v>98385</v>
       </c>
       <c r="B442" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
-        <v>98387</v>
+        <v>98386</v>
       </c>
       <c r="B443" s="2">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
-        <v>98388</v>
+        <v>98387</v>
       </c>
       <c r="B444" s="2">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
-        <v>98389</v>
+        <v>98388</v>
       </c>
       <c r="B445" s="2">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
-        <v>98390</v>
+        <v>98389</v>
       </c>
       <c r="B446" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
-        <v>98391</v>
+        <v>98390</v>
       </c>
       <c r="B447" s="2">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
-        <v>98392</v>
+        <v>98391</v>
       </c>
       <c r="B448" s="2">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
-        <v>98393</v>
+        <v>98392</v>
       </c>
       <c r="B449" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
-        <v>98395</v>
+        <v>98393</v>
       </c>
       <c r="B450" s="2">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
-        <v>98396</v>
+        <v>98395</v>
       </c>
       <c r="B451" s="2">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
-        <v>98397</v>
+        <v>98396</v>
       </c>
       <c r="B452" s="2">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
-        <v>98398</v>
+        <v>98397</v>
       </c>
       <c r="B453" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
-        <v>98399</v>
+        <v>98398</v>
       </c>
       <c r="B454" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
-        <v>98448</v>
+        <v>98399</v>
       </c>
       <c r="B455" s="2">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
-        <v>98449</v>
+        <v>98448</v>
       </c>
       <c r="B456" s="2">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
-        <v>98450</v>
+        <v>98449</v>
       </c>
       <c r="B457" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
-        <v>98453</v>
+        <v>98450</v>
       </c>
       <c r="B458" s="2">
         <v>13</v>
@@ -4111,167 +4111,167 @@
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
-        <v>98454</v>
+        <v>98453</v>
       </c>
       <c r="B459" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
-        <v>98455</v>
+        <v>98454</v>
       </c>
       <c r="B460" s="2">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
-        <v>98456</v>
+        <v>98455</v>
       </c>
       <c r="B461" s="2">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
-        <v>98458</v>
+        <v>98456</v>
       </c>
       <c r="B462" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
-        <v>98459</v>
+        <v>98458</v>
       </c>
       <c r="B463" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
-        <v>98463</v>
+        <v>98459</v>
       </c>
       <c r="B464" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
-        <v>98464</v>
+        <v>98460</v>
       </c>
       <c r="B465" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
-        <v>98465</v>
+        <v>98461</v>
       </c>
       <c r="B466" s="2">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
-        <v>98466</v>
+        <v>98463</v>
       </c>
       <c r="B467" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
-        <v>98467</v>
+        <v>98464</v>
       </c>
       <c r="B468" s="2">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
-        <v>98468</v>
+        <v>98465</v>
       </c>
       <c r="B469" s="2">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
-        <v>98469</v>
+        <v>98466</v>
       </c>
       <c r="B470" s="2">
-        <v>64</v>
+        <v>12</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
-        <v>98471</v>
+        <v>98467</v>
       </c>
       <c r="B471" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
-        <v>98473</v>
+        <v>98468</v>
       </c>
       <c r="B472" s="2">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
-        <v>98474</v>
+        <v>98469</v>
       </c>
       <c r="B473" s="2">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
-        <v>98475</v>
+        <v>98471</v>
       </c>
       <c r="B474" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
-        <v>98476</v>
+        <v>98473</v>
       </c>
       <c r="B475" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
-        <v>98477</v>
+        <v>98474</v>
       </c>
       <c r="B476" s="2">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
-        <v>98478</v>
+        <v>98475</v>
       </c>
       <c r="B477" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
-        <v>98479</v>
+        <v>98476</v>
       </c>
       <c r="B478" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
-        <v>98480</v>
+        <v>98478</v>
       </c>
       <c r="B479" s="2">
         <v>12</v>
@@ -4279,711 +4279,711 @@
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
-        <v>98481</v>
+        <v>98479</v>
       </c>
       <c r="B480" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
-        <v>98482</v>
+        <v>98480</v>
       </c>
       <c r="B481" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
-        <v>98483</v>
+        <v>98481</v>
       </c>
       <c r="B482" s="2">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
-        <v>98484</v>
+        <v>98482</v>
       </c>
       <c r="B483" s="2">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
-        <v>98485</v>
+        <v>98483</v>
       </c>
       <c r="B484" s="2">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
-        <v>98486</v>
+        <v>98484</v>
       </c>
       <c r="B485" s="2">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
-        <v>98488</v>
+        <v>98485</v>
       </c>
       <c r="B486" s="2">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
-        <v>98489</v>
+        <v>98486</v>
       </c>
       <c r="B487" s="2">
-        <v>74</v>
+        <v>17</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
-        <v>98490</v>
+        <v>98488</v>
       </c>
       <c r="B488" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
-        <v>98491</v>
+        <v>98489</v>
       </c>
       <c r="B489" s="2">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
-        <v>98492</v>
+        <v>98490</v>
       </c>
       <c r="B490" s="2">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
-        <v>98493</v>
+        <v>98491</v>
       </c>
       <c r="B491" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
-        <v>98494</v>
+        <v>98492</v>
       </c>
       <c r="B492" s="2">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
-        <v>98495</v>
+        <v>98493</v>
       </c>
       <c r="B493" s="2">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
-        <v>98496</v>
+        <v>98494</v>
       </c>
       <c r="B494" s="2">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
-        <v>98497</v>
+        <v>98495</v>
       </c>
       <c r="B495" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
-        <v>98498</v>
+        <v>98496</v>
       </c>
       <c r="B496" s="2">
-        <v>65</v>
+        <v>9</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
-        <v>98499</v>
+        <v>98497</v>
       </c>
       <c r="B497" s="2">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
-        <v>98500</v>
+        <v>98498</v>
       </c>
       <c r="B498" s="2">
-        <v>25</v>
+        <v>65</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
-        <v>98501</v>
+        <v>98499</v>
       </c>
       <c r="B499" s="2">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
-        <v>98502</v>
+        <v>98500</v>
       </c>
       <c r="B500" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
-        <v>98503</v>
+        <v>98501</v>
       </c>
       <c r="B501" s="2">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
-        <v>98504</v>
+        <v>98502</v>
       </c>
       <c r="B502" s="2">
-        <v>69</v>
+        <v>11</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
-        <v>98505</v>
+        <v>98503</v>
       </c>
       <c r="B503" s="2">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
-        <v>98506</v>
+        <v>98504</v>
       </c>
       <c r="B504" s="2">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
-        <v>98507</v>
+        <v>98505</v>
       </c>
       <c r="B505" s="2">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
-        <v>98508</v>
+        <v>98506</v>
       </c>
       <c r="B506" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
-        <v>98509</v>
+        <v>98507</v>
       </c>
       <c r="B507" s="2">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
-        <v>98510</v>
+        <v>98508</v>
       </c>
       <c r="B508" s="2">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
-        <v>98511</v>
+        <v>98509</v>
       </c>
       <c r="B509" s="2">
-        <v>16</v>
+        <v>57</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
-        <v>98512</v>
+        <v>98510</v>
       </c>
       <c r="B510" s="2">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
-        <v>98514</v>
+        <v>98511</v>
       </c>
       <c r="B511" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
-        <v>98515</v>
+        <v>98512</v>
       </c>
       <c r="B512" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
-        <v>98516</v>
+        <v>98514</v>
       </c>
       <c r="B513" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
-        <v>98517</v>
+        <v>98515</v>
       </c>
       <c r="B514" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
-        <v>98518</v>
+        <v>98516</v>
       </c>
       <c r="B515" s="2">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
-        <v>98519</v>
+        <v>98517</v>
       </c>
       <c r="B516" s="2">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
-        <v>98520</v>
+        <v>98518</v>
       </c>
       <c r="B517" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
-        <v>98521</v>
+        <v>98519</v>
       </c>
       <c r="B518" s="2">
-        <v>21</v>
+        <v>76</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
-        <v>98522</v>
+        <v>98520</v>
       </c>
       <c r="B519" s="2">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
-        <v>98523</v>
+        <v>98521</v>
       </c>
       <c r="B520" s="2">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
-        <v>98524</v>
+        <v>98522</v>
       </c>
       <c r="B521" s="2">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
-        <v>98525</v>
+        <v>98523</v>
       </c>
       <c r="B522" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
-        <v>98526</v>
+        <v>98524</v>
       </c>
       <c r="B523" s="2">
-        <v>15</v>
+        <v>52</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
-        <v>98527</v>
+        <v>98525</v>
       </c>
       <c r="B524" s="2">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
-        <v>98737</v>
+        <v>98526</v>
       </c>
       <c r="B525" s="2">
-        <v>67</v>
+        <v>15</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
-        <v>98738</v>
+        <v>98527</v>
       </c>
       <c r="B526" s="2">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
-        <v>98740</v>
+        <v>98737</v>
       </c>
       <c r="B527" s="2">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
-        <v>98743</v>
+        <v>98739</v>
       </c>
       <c r="B528" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
-        <v>98752</v>
+        <v>98741</v>
       </c>
       <c r="B529" s="2">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
-        <v>98753</v>
+        <v>98744</v>
       </c>
       <c r="B530" s="2">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
-        <v>20840</v>
+        <v>98747</v>
       </c>
       <c r="B531" s="2">
-        <v>2478</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
-        <v>20841</v>
+        <v>98750</v>
       </c>
       <c r="B532" s="2">
-        <v>772</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
-        <v>20846</v>
+        <v>98752</v>
       </c>
       <c r="B533" s="2">
-        <v>174</v>
+        <v>33</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
-        <v>34299</v>
+        <v>20840</v>
       </c>
       <c r="B534" s="2">
-        <v>660</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
-        <v>44701</v>
+        <v>20841</v>
       </c>
       <c r="B535" s="2">
-        <v>316</v>
+        <v>755</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
-        <v>53086</v>
+        <v>20846</v>
       </c>
       <c r="B536" s="2">
-        <v>12</v>
+        <v>172</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
-        <v>64252</v>
+        <v>34299</v>
       </c>
       <c r="B537" s="2">
-        <v>36</v>
+        <v>660</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
-        <v>68651</v>
+        <v>44701</v>
       </c>
       <c r="B538" s="2">
-        <v>44</v>
+        <v>316</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
-        <v>69369</v>
+        <v>49926</v>
       </c>
       <c r="B539" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
-        <v>69372</v>
+        <v>53086</v>
       </c>
       <c r="B540" s="2">
-        <v>1704</v>
+        <v>12</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
-        <v>69373</v>
+        <v>64252</v>
       </c>
       <c r="B541" s="2">
-        <v>2112</v>
+        <v>36</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
-        <v>69380</v>
+        <v>68651</v>
       </c>
       <c r="B542" s="2">
-        <v>1236</v>
+        <v>37</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
-        <v>69382</v>
+        <v>69369</v>
       </c>
       <c r="B543" s="2">
-        <v>660</v>
+        <v>48</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
-        <v>69389</v>
+        <v>69372</v>
       </c>
       <c r="B544" s="2">
-        <v>1860</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
-        <v>69948</v>
+        <v>69373</v>
       </c>
       <c r="B545" s="2">
-        <v>456</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
-        <v>69949</v>
+        <v>69380</v>
       </c>
       <c r="B546" s="2">
-        <v>60</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
-        <v>69956</v>
+        <v>69382</v>
       </c>
       <c r="B547" s="2">
-        <v>12</v>
+        <v>660</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
-        <v>74158</v>
+        <v>69389</v>
       </c>
       <c r="B548" s="2">
-        <v>732</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
-        <v>83233</v>
+        <v>69948</v>
       </c>
       <c r="B549" s="2">
-        <v>420</v>
+        <v>468</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
-        <v>87534</v>
+        <v>69949</v>
       </c>
       <c r="B550" s="2">
-        <v>572</v>
+        <v>60</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
-        <v>91515</v>
+        <v>69956</v>
       </c>
       <c r="B551" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
-        <v>91732</v>
+        <v>74158</v>
       </c>
       <c r="B552" s="2">
-        <v>324</v>
+        <v>732</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
-        <v>92742</v>
+        <v>83233</v>
       </c>
       <c r="B553" s="2">
-        <v>107</v>
+        <v>424</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
-        <v>92767</v>
+        <v>87171</v>
       </c>
       <c r="B554" s="2">
-        <v>1812</v>
+        <v>9</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
-        <v>93027</v>
+        <v>87534</v>
       </c>
       <c r="B555" s="2">
-        <v>690</v>
+        <v>572</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
-        <v>93036</v>
+        <v>91515</v>
       </c>
       <c r="B556" s="2">
-        <v>212</v>
+        <v>6</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
-        <v>93051</v>
+        <v>91732</v>
       </c>
       <c r="B557" s="2">
-        <v>572</v>
+        <v>336</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
-        <v>94355</v>
+        <v>92742</v>
       </c>
       <c r="B558" s="2">
-        <v>52</v>
+        <v>106</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
-        <v>94356</v>
+        <v>92767</v>
       </c>
       <c r="B559" s="2">
-        <v>244</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
-        <v>94357</v>
+        <v>93027</v>
       </c>
       <c r="B560" s="2">
-        <v>216</v>
+        <v>693</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
-        <v>94358</v>
+        <v>93036</v>
       </c>
       <c r="B561" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
-        <v>94404</v>
+        <v>93051</v>
       </c>
       <c r="B562" s="2">
-        <v>684</v>
+        <v>568</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
-        <v>94643</v>
+        <v>94355</v>
       </c>
       <c r="B563" s="2">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
-        <v>95618</v>
+        <v>94356</v>
       </c>
       <c r="B564" s="2">
-        <v>1</v>
+        <v>260</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
-        <v>95667</v>
+        <v>94357</v>
       </c>
       <c r="B565" s="2">
-        <v>76</v>
+        <v>224</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
-        <v>95927</v>
+        <v>94358</v>
       </c>
       <c r="B566" s="2">
-        <v>3</v>
+        <v>260</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
-        <v>96331</v>
+        <v>94404</v>
       </c>
       <c r="B567" s="2">
-        <v>4</v>
+        <v>692</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
-        <v>96453</v>
+        <v>94643</v>
       </c>
       <c r="B568" s="2">
         <v>8</v>
@@ -4991,106 +4991,106 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
-        <v>96496</v>
+        <v>95667</v>
       </c>
       <c r="B569" s="2">
-        <v>4</v>
+        <v>76</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
-        <v>96519</v>
+        <v>95927</v>
       </c>
       <c r="B570" s="2">
-        <v>468</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
-        <v>96710</v>
+        <v>95931</v>
       </c>
       <c r="B571" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
-        <v>97126</v>
+        <v>96519</v>
       </c>
       <c r="B572" s="2">
-        <v>44</v>
+        <v>468</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
-        <v>97127</v>
+        <v>96710</v>
       </c>
       <c r="B573" s="2">
-        <v>152</v>
+        <v>4</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
-        <v>97129</v>
+        <v>97126</v>
       </c>
       <c r="B574" s="2">
-        <v>128</v>
+        <v>44</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
-        <v>97131</v>
+        <v>97127</v>
       </c>
       <c r="B575" s="2">
-        <v>108</v>
+        <v>153</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
-        <v>97133</v>
+        <v>97129</v>
       </c>
       <c r="B576" s="2">
-        <v>24</v>
+        <v>132</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
-        <v>97552</v>
+        <v>97131</v>
       </c>
       <c r="B577" s="2">
-        <v>56</v>
+        <v>108</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
-        <v>97553</v>
+        <v>97133</v>
       </c>
       <c r="B578" s="2">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
-        <v>97554</v>
+        <v>97552</v>
       </c>
       <c r="B579" s="2">
-        <v>272</v>
+        <v>56</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
-        <v>97555</v>
+        <v>97553</v>
       </c>
       <c r="B580" s="2">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
-        <v>97558</v>
+        <v>97554</v>
       </c>
       <c r="B581" s="2">
-        <v>4</v>
+        <v>272</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.25">
@@ -5106,7 +5106,7 @@
         <v>97560</v>
       </c>
       <c r="B583" s="2">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.25">
@@ -5114,52 +5114,52 @@
         <v>97561</v>
       </c>
       <c r="B584" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A585" s="1">
-        <v>97564</v>
+        <v>97563</v>
       </c>
       <c r="B585" s="2">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
-        <v>97565</v>
+        <v>97564</v>
       </c>
       <c r="B586" s="2">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
-        <v>97566</v>
+        <v>97565</v>
       </c>
       <c r="B587" s="2">
-        <v>85</v>
+        <v>27</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
-        <v>97567</v>
+        <v>97566</v>
       </c>
       <c r="B588" s="2">
-        <v>4</v>
+        <v>85</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A589" s="1">
-        <v>97568</v>
+        <v>97567</v>
       </c>
       <c r="B589" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A590" s="1">
-        <v>97569</v>
+        <v>97568</v>
       </c>
       <c r="B590" s="2">
         <v>2</v>
@@ -5167,130 +5167,130 @@
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A591" s="1">
-        <v>97570</v>
+        <v>97569</v>
       </c>
       <c r="B591" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A592" s="1">
-        <v>97571</v>
+        <v>97570</v>
       </c>
       <c r="B592" s="2">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A593" s="1">
-        <v>97572</v>
+        <v>97571</v>
       </c>
       <c r="B593" s="2">
-        <v>16</v>
+        <v>54</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A594" s="1">
-        <v>97573</v>
+        <v>97572</v>
       </c>
       <c r="B594" s="2">
-        <v>116</v>
+        <v>12</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A595" s="1">
-        <v>97574</v>
+        <v>97573</v>
       </c>
       <c r="B595" s="2">
-        <v>8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A596" s="1">
-        <v>97576</v>
+        <v>97574</v>
       </c>
       <c r="B596" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A597" s="1">
-        <v>97577</v>
+        <v>97576</v>
       </c>
       <c r="B597" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A598" s="1">
-        <v>97579</v>
+        <v>97577</v>
       </c>
       <c r="B598" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A599" s="1">
-        <v>97580</v>
+        <v>97579</v>
       </c>
       <c r="B599" s="2">
-        <v>148</v>
+        <v>8</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A600" s="1">
-        <v>97581</v>
+        <v>97580</v>
       </c>
       <c r="B600" s="2">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A601" s="1">
-        <v>97582</v>
+        <v>97581</v>
       </c>
       <c r="B601" s="2">
-        <v>176</v>
+        <v>128</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
-        <v>97583</v>
+        <v>97582</v>
       </c>
       <c r="B602" s="2">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A603" s="1">
-        <v>97584</v>
+        <v>97583</v>
       </c>
       <c r="B603" s="2">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A604" s="1">
-        <v>97585</v>
+        <v>97584</v>
       </c>
       <c r="B604" s="2">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A605" s="1">
-        <v>97586</v>
+        <v>97585</v>
       </c>
       <c r="B605" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A606" s="1">
-        <v>97587</v>
+        <v>97586</v>
       </c>
       <c r="B606" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.25">
@@ -5298,12 +5298,12 @@
         <v>97588</v>
       </c>
       <c r="B607" s="2">
-        <v>86</v>
+        <v>44</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A608" s="1">
-        <v>97590</v>
+        <v>97591</v>
       </c>
       <c r="B608" s="2">
         <v>4</v>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A609" s="1">
-        <v>97591</v>
+        <v>97595</v>
       </c>
       <c r="B609" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.25">
@@ -5330,7 +5330,7 @@
         <v>97598</v>
       </c>
       <c r="B611" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.25">
@@ -5346,7 +5346,7 @@
         <v>97600</v>
       </c>
       <c r="B613" s="2">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.25">
@@ -5367,7 +5367,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A616" s="1">
-        <v>97605</v>
+        <v>97606</v>
       </c>
       <c r="B616" s="2">
         <v>12</v>
@@ -5375,71 +5375,71 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A617" s="1">
-        <v>97607</v>
+        <v>97624</v>
       </c>
       <c r="B617" s="2">
-        <v>4</v>
+        <v>153</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A618" s="1">
-        <v>97624</v>
+        <v>97625</v>
       </c>
       <c r="B618" s="2">
-        <v>155</v>
+        <v>46</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A619" s="1">
-        <v>97625</v>
+        <v>97626</v>
       </c>
       <c r="B619" s="2">
-        <v>53</v>
+        <v>18</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A620" s="1">
-        <v>97626</v>
+        <v>97627</v>
       </c>
       <c r="B620" s="2">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A621" s="1">
-        <v>97627</v>
+        <v>97628</v>
       </c>
       <c r="B621" s="2">
-        <v>57</v>
+        <v>10</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A622" s="1">
-        <v>97628</v>
+        <v>97653</v>
       </c>
       <c r="B622" s="2">
-        <v>10</v>
+        <v>91</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A623" s="1">
-        <v>97653</v>
+        <v>97654</v>
       </c>
       <c r="B623" s="2">
-        <v>80</v>
+        <v>32</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A624" s="1">
-        <v>97654</v>
+        <v>97692</v>
       </c>
       <c r="B624" s="2">
-        <v>15</v>
+        <v>308</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A625" s="1">
-        <v>97692</v>
+        <v>97693</v>
       </c>
       <c r="B625" s="2">
         <v>308</v>
@@ -5447,111 +5447,111 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A626" s="1">
-        <v>97693</v>
+        <v>97694</v>
       </c>
       <c r="B626" s="2">
-        <v>308</v>
+        <v>116</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A627" s="1">
-        <v>97694</v>
+        <v>97695</v>
       </c>
       <c r="B627" s="2">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A628" s="1">
-        <v>97695</v>
+        <v>97881</v>
       </c>
       <c r="B628" s="2">
-        <v>100</v>
+        <v>380</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A629" s="1">
-        <v>97881</v>
+        <v>97882</v>
       </c>
       <c r="B629" s="2">
-        <v>380</v>
+        <v>344</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A630" s="1">
-        <v>97882</v>
+        <v>98216</v>
       </c>
       <c r="B630" s="2">
-        <v>344</v>
+        <v>236</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A631" s="1">
-        <v>98216</v>
+        <v>98217</v>
       </c>
       <c r="B631" s="2">
-        <v>272</v>
+        <v>620</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A632" s="1">
-        <v>98217</v>
+        <v>98218</v>
       </c>
       <c r="B632" s="2">
-        <v>620</v>
+        <v>256</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A633" s="1">
-        <v>98218</v>
+        <v>98219</v>
       </c>
       <c r="B633" s="2">
-        <v>272</v>
+        <v>408</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A634" s="1">
-        <v>98219</v>
+        <v>98220</v>
       </c>
       <c r="B634" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A635" s="1">
-        <v>98220</v>
+        <v>98221</v>
       </c>
       <c r="B635" s="2">
-        <v>144</v>
+        <v>224</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A636" s="1">
-        <v>98221</v>
+        <v>98222</v>
       </c>
       <c r="B636" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A637" s="1">
-        <v>98222</v>
+        <v>98223</v>
       </c>
       <c r="B637" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A638" s="1">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="B638" s="2">
-        <v>212</v>
+        <v>40</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A639" s="1">
-        <v>98224</v>
+        <v>98225</v>
       </c>
       <c r="B639" s="2">
         <v>32</v>
@@ -5559,71 +5559,71 @@
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A640" s="1">
-        <v>98225</v>
+        <v>98226</v>
       </c>
       <c r="B640" s="2">
-        <v>32</v>
+        <v>296</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A641" s="1">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="B641" s="2">
-        <v>296</v>
+        <v>876</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A642" s="1">
-        <v>98227</v>
+        <v>98228</v>
       </c>
       <c r="B642" s="2">
-        <v>876</v>
+        <v>300</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A643" s="1">
-        <v>98228</v>
+        <v>98229</v>
       </c>
       <c r="B643" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A644" s="1">
-        <v>98229</v>
+        <v>98231</v>
       </c>
       <c r="B644" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A645" s="1">
-        <v>98231</v>
+        <v>98232</v>
       </c>
       <c r="B645" s="2">
-        <v>300</v>
+        <v>152</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A646" s="1">
-        <v>98232</v>
+        <v>98233</v>
       </c>
       <c r="B646" s="2">
-        <v>168</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A647" s="1">
-        <v>98233</v>
+        <v>98234</v>
       </c>
       <c r="B647" s="2">
-        <v>1560</v>
+        <v>260</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A648" s="1">
-        <v>98234</v>
+        <v>98235</v>
       </c>
       <c r="B648" s="2">
         <v>220</v>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A649" s="1">
-        <v>98235</v>
+        <v>98236</v>
       </c>
       <c r="B649" s="2">
         <v>220</v>
@@ -5639,47 +5639,47 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A650" s="1">
-        <v>98236</v>
+        <v>98237</v>
       </c>
       <c r="B650" s="2">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A651" s="1">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="B651" s="2">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A652" s="1">
-        <v>98238</v>
+        <v>98239</v>
       </c>
       <c r="B652" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A653" s="1">
-        <v>98239</v>
+        <v>98538</v>
       </c>
       <c r="B653" s="2">
-        <v>224</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A654" s="1">
-        <v>98538</v>
+        <v>98581</v>
       </c>
       <c r="B654" s="2">
-        <v>1026</v>
+        <v>144</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A655" s="1">
-        <v>98581</v>
+        <v>98582</v>
       </c>
       <c r="B655" s="2">
         <v>148</v>
@@ -5687,23 +5687,23 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A656" s="1">
-        <v>98582</v>
+        <v>98583</v>
       </c>
       <c r="B656" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A657" s="1">
-        <v>98583</v>
+        <v>98584</v>
       </c>
       <c r="B657" s="2">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A658" s="1">
-        <v>98584</v>
+        <v>98585</v>
       </c>
       <c r="B658" s="2">
         <v>148</v>
@@ -5711,55 +5711,55 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A659" s="1">
-        <v>98585</v>
+        <v>98586</v>
       </c>
       <c r="B659" s="2">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A660" s="1">
-        <v>98586</v>
+        <v>98587</v>
       </c>
       <c r="B660" s="2">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A661" s="1">
-        <v>98587</v>
+        <v>98589</v>
       </c>
       <c r="B661" s="2">
-        <v>148</v>
+        <v>72</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A662" s="1">
-        <v>98589</v>
+        <v>98590</v>
       </c>
       <c r="B662" s="2">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A663" s="1">
-        <v>98590</v>
+        <v>98592</v>
       </c>
       <c r="B663" s="2">
-        <v>108</v>
+        <v>64</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A664" s="1">
-        <v>98592</v>
+        <v>98626</v>
       </c>
       <c r="B664" s="2">
-        <v>64</v>
+        <v>168</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A665" s="1">
-        <v>98626</v>
+        <v>98627</v>
       </c>
       <c r="B665" s="2">
         <v>168</v>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A666" s="1">
-        <v>98627</v>
+        <v>98628</v>
       </c>
       <c r="B666" s="2">
         <v>168</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A667" s="1">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="B667" s="2">
         <v>168</v>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A668" s="1">
-        <v>98629</v>
+        <v>98630</v>
       </c>
       <c r="B668" s="2">
         <v>168</v>
@@ -5791,23 +5791,23 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A669" s="1">
-        <v>98630</v>
+        <v>98631</v>
       </c>
       <c r="B669" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A670" s="1">
-        <v>98631</v>
+        <v>98632</v>
       </c>
       <c r="B670" s="2">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A671" s="1">
-        <v>98632</v>
+        <v>98633</v>
       </c>
       <c r="B671" s="2">
         <v>192</v>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A672" s="1">
-        <v>98633</v>
+        <v>98634</v>
       </c>
       <c r="B672" s="2">
         <v>192</v>
@@ -5823,215 +5823,215 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A673" s="1">
-        <v>98634</v>
+        <v>7722</v>
       </c>
       <c r="B673" s="2">
-        <v>192</v>
+        <v>852</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A674" s="1">
-        <v>7722</v>
+        <v>33427</v>
       </c>
       <c r="B674" s="2">
-        <v>864</v>
+        <v>424</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A675" s="1">
-        <v>33427</v>
+        <v>59285</v>
       </c>
       <c r="B675" s="2">
-        <v>424</v>
+        <v>50</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A676" s="1">
-        <v>59285</v>
+        <v>78372</v>
       </c>
       <c r="B676" s="2">
-        <v>56</v>
+        <v>720</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A677" s="1">
-        <v>78372</v>
+        <v>84540</v>
       </c>
       <c r="B677" s="2">
-        <v>720</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
-        <v>84540</v>
+        <v>89097</v>
       </c>
       <c r="B678" s="2">
-        <v>4050</v>
+        <v>479</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A679" s="1">
-        <v>89097</v>
+        <v>92811</v>
       </c>
       <c r="B679" s="2">
-        <v>479</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A680" s="1">
-        <v>92811</v>
+        <v>94746</v>
       </c>
       <c r="B680" s="2">
-        <v>1660</v>
+        <v>438</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A681" s="1">
-        <v>94746</v>
+        <v>95346</v>
       </c>
       <c r="B681" s="2">
-        <v>438</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A682" s="1">
-        <v>95346</v>
+        <v>95588</v>
       </c>
       <c r="B682" s="2">
-        <v>1062</v>
+        <v>15</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
-        <v>95588</v>
+        <v>95795</v>
       </c>
       <c r="B683" s="2">
-        <v>15</v>
+        <v>790</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A684" s="1">
-        <v>95795</v>
+        <v>96896</v>
       </c>
       <c r="B684" s="2">
-        <v>780</v>
+        <v>12</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A685" s="1">
-        <v>96895</v>
+        <v>96897</v>
       </c>
       <c r="B685" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A686" s="1">
-        <v>96896</v>
+        <v>96989</v>
       </c>
       <c r="B686" s="2">
-        <v>12</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A687" s="1">
-        <v>96989</v>
+        <v>97642</v>
       </c>
       <c r="B687" s="2">
-        <v>1020</v>
+        <v>8</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A688" s="1">
-        <v>97519</v>
+        <v>97662</v>
       </c>
       <c r="B688" s="2">
-        <v>8</v>
+        <v>390</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A689" s="1">
-        <v>97642</v>
+        <v>97663</v>
       </c>
       <c r="B689" s="2">
-        <v>8</v>
+        <v>460</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A690" s="1">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="B690" s="2">
-        <v>390</v>
+        <v>420</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A691" s="1">
-        <v>97663</v>
+        <v>97665</v>
       </c>
       <c r="B691" s="2">
-        <v>460</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A692" s="1">
-        <v>97664</v>
+        <v>98425</v>
       </c>
       <c r="B692" s="2">
-        <v>420</v>
+        <v>148</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A693" s="1">
-        <v>97665</v>
+        <v>98434</v>
       </c>
       <c r="B693" s="2">
-        <v>3750</v>
+        <v>80</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A694" s="1">
-        <v>98425</v>
+        <v>98435</v>
       </c>
       <c r="B694" s="2">
-        <v>148</v>
+        <v>84</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A695" s="1">
-        <v>98434</v>
+        <v>98436</v>
       </c>
       <c r="B695" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A696" s="1">
-        <v>98435</v>
+        <v>98437</v>
       </c>
       <c r="B696" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A697" s="1">
-        <v>98436</v>
+        <v>98438</v>
       </c>
       <c r="B697" s="2">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A698" s="1">
-        <v>98437</v>
+        <v>98439</v>
       </c>
       <c r="B698" s="2">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A699" s="1">
-        <v>98438</v>
+        <v>98440</v>
       </c>
       <c r="B699" s="2">
         <v>68</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A700" s="1">
-        <v>98439</v>
+        <v>98441</v>
       </c>
       <c r="B700" s="2">
         <v>68</v>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A701" s="1">
-        <v>98440</v>
+        <v>98442</v>
       </c>
       <c r="B701" s="2">
         <v>68</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A702" s="1">
-        <v>98441</v>
+        <v>98443</v>
       </c>
       <c r="B702" s="2">
         <v>68</v>
@@ -6063,7 +6063,7 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A703" s="1">
-        <v>98442</v>
+        <v>98444</v>
       </c>
       <c r="B703" s="2">
         <v>68</v>
@@ -6071,463 +6071,463 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A704" s="1">
-        <v>98443</v>
+        <v>98445</v>
       </c>
       <c r="B704" s="2">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A705" s="1">
-        <v>98444</v>
+        <v>98446</v>
       </c>
       <c r="B705" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A706" s="1">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="B706" s="2">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A707" s="1">
-        <v>98446</v>
+        <v>98539</v>
       </c>
       <c r="B707" s="2">
-        <v>52</v>
+        <v>90</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A708" s="1">
-        <v>98447</v>
+        <v>98540</v>
       </c>
       <c r="B708" s="2">
-        <v>28</v>
+        <v>140</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A709" s="1">
-        <v>98539</v>
+        <v>98541</v>
       </c>
       <c r="B709" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A710" s="1">
-        <v>98540</v>
+        <v>99389</v>
       </c>
       <c r="B710" s="2">
-        <v>140</v>
+        <v>36</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A711" s="1">
-        <v>98541</v>
+        <v>9646</v>
       </c>
       <c r="B711" s="2">
-        <v>80</v>
+        <v>924</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A712" s="1">
-        <v>99389</v>
+        <v>24874</v>
       </c>
       <c r="B712" s="2">
-        <v>36</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A713" s="1">
-        <v>9646</v>
+        <v>34094</v>
       </c>
       <c r="B713" s="2">
-        <v>1032</v>
+        <v>5272</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A714" s="1">
-        <v>24874</v>
+        <v>53546</v>
       </c>
       <c r="B714" s="2">
-        <v>1684</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A715" s="1">
-        <v>34094</v>
+        <v>59014</v>
       </c>
       <c r="B715" s="2">
-        <v>5250</v>
+        <v>644</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A716" s="1">
-        <v>53546</v>
+        <v>65805</v>
       </c>
       <c r="B716" s="2">
-        <v>1330</v>
+        <v>148</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A717" s="1">
-        <v>59014</v>
+        <v>65948</v>
       </c>
       <c r="B717" s="2">
-        <v>638</v>
+        <v>112</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A718" s="1">
-        <v>65805</v>
+        <v>66663</v>
       </c>
       <c r="B718" s="2">
-        <v>148</v>
+        <v>624</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A719" s="1">
-        <v>65948</v>
+        <v>68463</v>
       </c>
       <c r="B719" s="2">
-        <v>112</v>
+        <v>6</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A720" s="1">
-        <v>66663</v>
+        <v>70620</v>
       </c>
       <c r="B720" s="2">
-        <v>626</v>
+        <v>644</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A721" s="1">
-        <v>68463</v>
+        <v>70653</v>
       </c>
       <c r="B721" s="2">
-        <v>2</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A722" s="1">
-        <v>70620</v>
+        <v>74779</v>
       </c>
       <c r="B722" s="2">
-        <v>644</v>
+        <v>918</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A723" s="1">
-        <v>70653</v>
+        <v>75922</v>
       </c>
       <c r="B723" s="2">
-        <v>3256</v>
+        <v>112</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A724" s="1">
-        <v>74779</v>
+        <v>75923</v>
       </c>
       <c r="B724" s="2">
-        <v>918</v>
+        <v>280</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A725" s="1">
-        <v>75922</v>
+        <v>75924</v>
       </c>
       <c r="B725" s="2">
-        <v>108</v>
+        <v>372</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A726" s="1">
-        <v>75923</v>
+        <v>76063</v>
       </c>
       <c r="B726" s="2">
-        <v>280</v>
+        <v>148</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A727" s="1">
-        <v>75924</v>
+        <v>76064</v>
       </c>
       <c r="B727" s="2">
-        <v>372</v>
+        <v>202</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A728" s="1">
-        <v>76063</v>
+        <v>76065</v>
       </c>
       <c r="B728" s="2">
-        <v>148</v>
+        <v>704</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A729" s="1">
-        <v>76064</v>
+        <v>76066</v>
       </c>
       <c r="B729" s="2">
-        <v>202</v>
+        <v>782</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A730" s="1">
-        <v>76065</v>
+        <v>76067</v>
       </c>
       <c r="B730" s="2">
-        <v>706</v>
+        <v>554</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A731" s="1">
-        <v>76066</v>
+        <v>76083</v>
       </c>
       <c r="B731" s="2">
-        <v>800</v>
+        <v>2</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A732" s="1">
-        <v>76067</v>
+        <v>77697</v>
       </c>
       <c r="B732" s="2">
-        <v>552</v>
+        <v>478</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A733" s="1">
-        <v>77697</v>
+        <v>78625</v>
       </c>
       <c r="B733" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A734" s="1">
-        <v>78625</v>
+        <v>78630</v>
       </c>
       <c r="B734" s="2">
-        <v>84</v>
+        <v>2</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A735" s="1">
-        <v>78630</v>
+        <v>78633</v>
       </c>
       <c r="B735" s="2">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A736" s="1">
-        <v>78633</v>
+        <v>80660</v>
       </c>
       <c r="B736" s="2">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A737" s="1">
-        <v>80660</v>
+        <v>80679</v>
       </c>
       <c r="B737" s="2">
-        <v>2</v>
+        <v>246</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A738" s="1">
-        <v>80679</v>
+        <v>80680</v>
       </c>
       <c r="B738" s="2">
-        <v>246</v>
+        <v>6</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A739" s="1">
-        <v>80680</v>
+        <v>80685</v>
       </c>
       <c r="B739" s="2">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A740" s="1">
-        <v>80685</v>
+        <v>81763</v>
       </c>
       <c r="B740" s="2">
-        <v>150</v>
+        <v>794</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A741" s="1">
-        <v>81763</v>
+        <v>81764</v>
       </c>
       <c r="B741" s="2">
-        <v>790</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A742" s="1">
-        <v>81764</v>
+        <v>81765</v>
       </c>
       <c r="B742" s="2">
-        <v>1232</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A743" s="1">
-        <v>81765</v>
+        <v>82834</v>
       </c>
       <c r="B743" s="2">
-        <v>1316</v>
+        <v>2</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A744" s="1">
-        <v>82834</v>
+        <v>83163</v>
       </c>
       <c r="B744" s="2">
-        <v>2</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A745" s="1">
-        <v>83163</v>
+        <v>84801</v>
       </c>
       <c r="B745" s="2">
-        <v>1608</v>
+        <v>120</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A746" s="1">
-        <v>84801</v>
+        <v>84802</v>
       </c>
       <c r="B746" s="2">
-        <v>120</v>
+        <v>262</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A747" s="1">
-        <v>84802</v>
+        <v>84803</v>
       </c>
       <c r="B747" s="2">
-        <v>264</v>
+        <v>140</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A748" s="1">
-        <v>84803</v>
+        <v>84804</v>
       </c>
       <c r="B748" s="2">
-        <v>140</v>
+        <v>92</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A749" s="1">
-        <v>84804</v>
+        <v>84807</v>
       </c>
       <c r="B749" s="2">
-        <v>92</v>
+        <v>36</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A750" s="1">
-        <v>84807</v>
+        <v>86538</v>
       </c>
       <c r="B750" s="2">
-        <v>36</v>
+        <v>130</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A751" s="1">
-        <v>86538</v>
+        <v>87263</v>
       </c>
       <c r="B751" s="2">
-        <v>74</v>
+        <v>208</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A752" s="1">
-        <v>87263</v>
+        <v>87325</v>
       </c>
       <c r="B752" s="2">
-        <v>222</v>
+        <v>616</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A753" s="1">
-        <v>87325</v>
+        <v>87326</v>
       </c>
       <c r="B753" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A754" s="1">
-        <v>87326</v>
+        <v>87635</v>
       </c>
       <c r="B754" s="2">
-        <v>616</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A755" s="1">
-        <v>87635</v>
+        <v>87901</v>
       </c>
       <c r="B755" s="2">
-        <v>2384</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A756" s="1">
-        <v>87901</v>
+        <v>87903</v>
       </c>
       <c r="B756" s="2">
-        <v>1379</v>
+        <v>150</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A757" s="1">
-        <v>87903</v>
+        <v>88350</v>
       </c>
       <c r="B757" s="2">
-        <v>150</v>
+        <v>710</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A758" s="1">
-        <v>88350</v>
+        <v>88360</v>
       </c>
       <c r="B758" s="2">
-        <v>710</v>
+        <v>734</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A759" s="1">
-        <v>88360</v>
+        <v>88400</v>
       </c>
       <c r="B759" s="2">
-        <v>726</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A760" s="1">
-        <v>88400</v>
+        <v>89190</v>
       </c>
       <c r="B760" s="2">
-        <v>1120</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A761" s="1">
-        <v>89190</v>
+        <v>89194</v>
       </c>
       <c r="B761" s="2">
         <v>2</v>
@@ -6535,562 +6535,562 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A762" s="1">
-        <v>89192</v>
+        <v>90109</v>
       </c>
       <c r="B762" s="2">
-        <v>2</v>
+        <v>875</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A763" s="1">
-        <v>89194</v>
+        <v>90497</v>
       </c>
       <c r="B763" s="2">
-        <v>2</v>
+        <v>194</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A764" s="1">
-        <v>90109</v>
+        <v>90972</v>
       </c>
       <c r="B764" s="2">
-        <v>874</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A765" s="1">
-        <v>90497</v>
+        <v>91653</v>
       </c>
       <c r="B765" s="2">
-        <v>196</v>
+        <v>614</v>
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
-        <v>90972</v>
+        <v>91678</v>
       </c>
       <c r="B766" s="2">
-        <v>2</v>
+        <v>428</v>
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A767" s="1">
-        <v>91653</v>
+        <v>92172</v>
       </c>
       <c r="B767" s="2">
-        <v>612</v>
+        <v>2</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A768" s="1">
-        <v>91678</v>
+        <v>92176</v>
       </c>
       <c r="B768" s="2">
-        <v>428</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
-        <v>92172</v>
+        <v>92184</v>
       </c>
       <c r="B769" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
-        <v>92176</v>
+        <v>92463</v>
       </c>
       <c r="B770" s="2">
-        <v>1306</v>
+        <v>4</v>
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A771" s="1">
-        <v>92184</v>
+        <v>92815</v>
       </c>
       <c r="B771" s="2">
-        <v>26</v>
+        <v>324</v>
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
-        <v>92463</v>
+        <v>92822</v>
       </c>
       <c r="B772" s="2">
-        <v>4</v>
+        <v>204</v>
       </c>
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
-        <v>92815</v>
+        <v>92823</v>
       </c>
       <c r="B773" s="2">
-        <v>324</v>
+        <v>182</v>
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
-        <v>92822</v>
+        <v>92836</v>
       </c>
       <c r="B774" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A775" s="1">
-        <v>92823</v>
+        <v>92984</v>
       </c>
       <c r="B775" s="2">
-        <v>182</v>
+        <v>94</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A776" s="1">
-        <v>92836</v>
+        <v>93002</v>
       </c>
       <c r="B776" s="2">
-        <v>132</v>
+        <v>2</v>
       </c>
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
-        <v>92984</v>
+        <v>93016</v>
       </c>
       <c r="B777" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
-        <v>93002</v>
+        <v>93067</v>
       </c>
       <c r="B778" s="2">
-        <v>1</v>
+        <v>860</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
-        <v>93016</v>
+        <v>93073</v>
       </c>
       <c r="B779" s="2">
-        <v>20</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A780" s="1">
-        <v>93067</v>
+        <v>94233</v>
       </c>
       <c r="B780" s="2">
-        <v>858</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
-        <v>93073</v>
+        <v>94314</v>
       </c>
       <c r="B781" s="2">
-        <v>1049</v>
+        <v>956</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A782" s="1">
-        <v>94233</v>
+        <v>94317</v>
       </c>
       <c r="B782" s="2">
-        <v>1462</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
-        <v>94314</v>
+        <v>94683</v>
       </c>
       <c r="B783" s="2">
-        <v>956</v>
+        <v>14</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
-        <v>94317</v>
+        <v>94821</v>
       </c>
       <c r="B784" s="2">
-        <v>1740</v>
+        <v>848</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
-        <v>94683</v>
+        <v>94830</v>
       </c>
       <c r="B785" s="2">
-        <v>14</v>
+        <v>556</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
-        <v>94821</v>
+        <v>94835</v>
       </c>
       <c r="B786" s="2">
-        <v>850</v>
+        <v>246</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
-        <v>94830</v>
+        <v>95202</v>
       </c>
       <c r="B787" s="2">
-        <v>552</v>
+        <v>188</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
-        <v>94835</v>
+        <v>95211</v>
       </c>
       <c r="B788" s="2">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
-        <v>95202</v>
+        <v>95536</v>
       </c>
       <c r="B789" s="2">
-        <v>184</v>
+        <v>962</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A790" s="7">
-        <v>95211</v>
+        <v>95538</v>
       </c>
       <c r="B790" s="5">
-        <v>268</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A791" s="7">
-        <v>95536</v>
+        <v>95715</v>
       </c>
       <c r="B791" s="5">
-        <v>948</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A792" s="7">
-        <v>95538</v>
+        <v>95731</v>
       </c>
       <c r="B792" s="5">
-        <v>1092</v>
+        <v>344</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A793" s="7">
-        <v>95715</v>
+        <v>95732</v>
       </c>
       <c r="B793" s="5">
-        <v>1110</v>
+        <v>542</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A794" s="7">
-        <v>95731</v>
+        <v>95765</v>
       </c>
       <c r="B794" s="5">
-        <v>688</v>
+        <v>562</v>
       </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A795" s="7">
-        <v>95732</v>
+        <v>95768</v>
       </c>
       <c r="B795" s="5">
-        <v>540</v>
+        <v>336</v>
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A796" s="7">
-        <v>95740</v>
+        <v>95769</v>
       </c>
       <c r="B796" s="5">
-        <v>4</v>
+        <v>870</v>
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A797" s="7">
-        <v>95765</v>
+        <v>95770</v>
       </c>
       <c r="B797" s="5">
-        <v>460</v>
+        <v>326</v>
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A798" s="7">
-        <v>95768</v>
+        <v>95772</v>
       </c>
       <c r="B798" s="5">
-        <v>336</v>
+        <v>422</v>
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A799" s="7">
-        <v>95769</v>
+        <v>95774</v>
       </c>
       <c r="B799" s="5">
-        <v>866</v>
+        <v>426</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A800" s="7">
-        <v>95770</v>
+        <v>95781</v>
       </c>
       <c r="B800" s="5">
-        <v>328</v>
+        <v>516</v>
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A801" s="7">
-        <v>95772</v>
+        <v>95907</v>
       </c>
       <c r="B801" s="5">
-        <v>422</v>
+        <v>4</v>
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A802" s="7">
-        <v>95774</v>
+        <v>95911</v>
       </c>
       <c r="B802" s="5">
-        <v>426</v>
+        <v>221</v>
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A803" s="7">
-        <v>95781</v>
+        <v>96507</v>
       </c>
       <c r="B803" s="5">
-        <v>516</v>
+        <v>250</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A804" s="7">
-        <v>95907</v>
+        <v>96508</v>
       </c>
       <c r="B804" s="5">
-        <v>4</v>
+        <v>656</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A805" s="7">
-        <v>95911</v>
+        <v>96510</v>
       </c>
       <c r="B805" s="5">
-        <v>221</v>
+        <v>258</v>
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A806" s="7">
-        <v>96507</v>
+        <v>96517</v>
       </c>
       <c r="B806" s="5">
-        <v>250</v>
+        <v>164</v>
       </c>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A807" s="7">
-        <v>96508</v>
+        <v>96526</v>
       </c>
       <c r="B807" s="5">
-        <v>656</v>
+        <v>2</v>
       </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A808" s="7">
-        <v>96510</v>
+        <v>96539</v>
       </c>
       <c r="B808" s="5">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A809" s="7">
-        <v>96517</v>
+        <v>97066</v>
       </c>
       <c r="B809" s="5">
-        <v>164</v>
+        <v>448</v>
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A810" s="7">
-        <v>96539</v>
+        <v>97067</v>
       </c>
       <c r="B810" s="5">
-        <v>246</v>
+        <v>574</v>
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A811" s="7">
-        <v>97066</v>
+        <v>97701</v>
       </c>
       <c r="B811" s="5">
-        <v>448</v>
+        <v>44</v>
       </c>
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A812" s="7">
-        <v>97067</v>
+        <v>97702</v>
       </c>
       <c r="B812" s="5">
-        <v>576</v>
+        <v>26</v>
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A813" s="7">
-        <v>97700</v>
+        <v>97703</v>
       </c>
       <c r="B813" s="5">
-        <v>6</v>
+        <v>132</v>
       </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A814" s="7">
-        <v>97701</v>
+        <v>97705</v>
       </c>
       <c r="B814" s="5">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A815" s="7">
-        <v>97702</v>
+        <v>97707</v>
       </c>
       <c r="B815" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A816" s="7">
-        <v>97703</v>
+        <v>97708</v>
       </c>
       <c r="B816" s="5">
-        <v>132</v>
+        <v>22</v>
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A817" s="7">
-        <v>97707</v>
+        <v>97711</v>
       </c>
       <c r="B817" s="5">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A818" s="7">
-        <v>97711</v>
+        <v>97712</v>
       </c>
       <c r="B818" s="5">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A819" s="7">
-        <v>97712</v>
+        <v>97713</v>
       </c>
       <c r="B819" s="5">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A820" s="7">
-        <v>97713</v>
+        <v>97715</v>
       </c>
       <c r="B820" s="5">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A821" s="7">
-        <v>97715</v>
+        <v>97717</v>
       </c>
       <c r="B821" s="5">
-        <v>36</v>
+        <v>114</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A822" s="7">
-        <v>97717</v>
+        <v>97720</v>
       </c>
       <c r="B822" s="5">
-        <v>118</v>
+        <v>86</v>
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A823" s="7">
-        <v>97720</v>
+        <v>97721</v>
       </c>
       <c r="B823" s="5">
-        <v>86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A824" s="7">
-        <v>97721</v>
+        <v>97723</v>
       </c>
       <c r="B824" s="5">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A825" s="7">
-        <v>97723</v>
+        <v>97724</v>
       </c>
       <c r="B825" s="5">
-        <v>52</v>
+        <v>8</v>
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A826" s="7">
-        <v>97724</v>
+        <v>97725</v>
       </c>
       <c r="B826" s="5">
-        <v>8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A827" s="7">
-        <v>97725</v>
+        <v>97727</v>
       </c>
       <c r="B827" s="5">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A828" s="7">
-        <v>97727</v>
+        <v>97730</v>
       </c>
       <c r="B828" s="5">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A829" s="7">
-        <v>97730</v>
+        <v>97731</v>
       </c>
       <c r="B829" s="5">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A830" s="7">
-        <v>97731</v>
+        <v>97732</v>
       </c>
       <c r="B830" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A831" s="7">
-        <v>97732</v>
+        <v>97734</v>
       </c>
       <c r="B831" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.25">
@@ -7098,7 +7098,7 @@
         <v>97735</v>
       </c>
       <c r="B832" s="5">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.25">
@@ -7114,7 +7114,7 @@
         <v>97742</v>
       </c>
       <c r="B834" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.25">
@@ -7122,76 +7122,76 @@
         <v>97744</v>
       </c>
       <c r="B835" s="5">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A836" s="7">
-        <v>97747</v>
+        <v>97745</v>
       </c>
       <c r="B836" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A837" s="7">
-        <v>97748</v>
+        <v>97747</v>
       </c>
       <c r="B837" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A838" s="7">
-        <v>97749</v>
+        <v>97748</v>
       </c>
       <c r="B838" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A839" s="7">
-        <v>97750</v>
+        <v>97749</v>
       </c>
       <c r="B839" s="5">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A840" s="7">
-        <v>97756</v>
+        <v>97750</v>
       </c>
       <c r="B840" s="5">
-        <v>130</v>
+        <v>40</v>
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A841" s="7">
-        <v>97768</v>
+        <v>97756</v>
       </c>
       <c r="B841" s="5">
-        <v>94</v>
+        <v>130</v>
       </c>
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A842" s="7">
-        <v>97770</v>
+        <v>97757</v>
       </c>
       <c r="B842" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A843" s="7">
-        <v>97771</v>
+        <v>97768</v>
       </c>
       <c r="B843" s="5">
-        <v>2</v>
+        <v>96</v>
       </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A844" s="7">
-        <v>97776</v>
+        <v>97770</v>
       </c>
       <c r="B844" s="5">
         <v>2</v>
@@ -7199,295 +7199,295 @@
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A845" s="7">
-        <v>97777</v>
+        <v>97771</v>
       </c>
       <c r="B845" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A846" s="7">
-        <v>97781</v>
+        <v>97775</v>
       </c>
       <c r="B846" s="5">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A847" s="7">
-        <v>97784</v>
+        <v>97777</v>
       </c>
       <c r="B847" s="5">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A848" s="7">
-        <v>97785</v>
+        <v>97778</v>
       </c>
       <c r="B848" s="5">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A849" s="7">
-        <v>97788</v>
+        <v>97781</v>
       </c>
       <c r="B849" s="5">
-        <v>106</v>
+        <v>14</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A850" s="7">
-        <v>97789</v>
+        <v>97784</v>
       </c>
       <c r="B850" s="5">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A851" s="7">
-        <v>97790</v>
+        <v>97785</v>
       </c>
       <c r="B851" s="5">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A852" s="7">
-        <v>97791</v>
+        <v>97788</v>
       </c>
       <c r="B852" s="5">
-        <v>44</v>
+        <v>106</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A853" s="7">
-        <v>97792</v>
+        <v>97789</v>
       </c>
       <c r="B853" s="5">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A854" s="7">
-        <v>97793</v>
+        <v>97790</v>
       </c>
       <c r="B854" s="5">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A855" s="7">
-        <v>98131</v>
+        <v>97791</v>
       </c>
       <c r="B855" s="5">
-        <v>96</v>
+        <v>44</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A856" s="7">
-        <v>98132</v>
+        <v>97792</v>
       </c>
       <c r="B856" s="5">
-        <v>92</v>
+        <v>36</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A857" s="7">
-        <v>98133</v>
+        <v>97793</v>
       </c>
       <c r="B857" s="5">
-        <v>134</v>
+        <v>58</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A858" s="7">
-        <v>98134</v>
+        <v>98131</v>
       </c>
       <c r="B858" s="5">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A859" s="7">
-        <v>98135</v>
+        <v>98132</v>
       </c>
       <c r="B859" s="5">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A860" s="7">
-        <v>98136</v>
+        <v>98133</v>
       </c>
       <c r="B860" s="5">
-        <v>104</v>
+        <v>134</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A861" s="7">
-        <v>98137</v>
+        <v>98134</v>
       </c>
       <c r="B861" s="5">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A862" s="7">
-        <v>98138</v>
+        <v>98135</v>
       </c>
       <c r="B862" s="5">
-        <v>94</v>
+        <v>114</v>
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A863" s="7">
-        <v>98139</v>
+        <v>98136</v>
       </c>
       <c r="B863" s="5">
-        <v>66</v>
+        <v>104</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A864" s="7">
-        <v>98140</v>
+        <v>98137</v>
       </c>
       <c r="B864" s="5">
-        <v>128</v>
+        <v>72</v>
       </c>
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A865" s="7">
-        <v>98141</v>
+        <v>98138</v>
       </c>
       <c r="B865" s="5">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A866" s="7">
-        <v>98142</v>
+        <v>98139</v>
       </c>
       <c r="B866" s="5">
-        <v>126</v>
+        <v>66</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A867" s="7">
-        <v>98143</v>
+        <v>98140</v>
       </c>
       <c r="B867" s="5">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A868" s="7">
-        <v>98144</v>
+        <v>98141</v>
       </c>
       <c r="B868" s="5">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A869" s="7">
-        <v>98145</v>
+        <v>98142</v>
       </c>
       <c r="B869" s="5">
-        <v>96</v>
+        <v>126</v>
       </c>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A870" s="7">
-        <v>98146</v>
+        <v>98143</v>
       </c>
       <c r="B870" s="5">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A871" s="7">
-        <v>98147</v>
+        <v>98144</v>
       </c>
       <c r="B871" s="5">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A872" s="7">
-        <v>98148</v>
+        <v>98145</v>
       </c>
       <c r="B872" s="5">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A873" s="7">
-        <v>98149</v>
+        <v>98146</v>
       </c>
       <c r="B873" s="5">
-        <v>114</v>
+        <v>60</v>
       </c>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A874" s="7">
-        <v>98150</v>
+        <v>98147</v>
       </c>
       <c r="B874" s="5">
-        <v>80</v>
+        <v>142</v>
       </c>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A875" s="7">
-        <v>98151</v>
+        <v>98148</v>
       </c>
       <c r="B875" s="5">
-        <v>112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A876" s="7">
-        <v>98153</v>
+        <v>98149</v>
       </c>
       <c r="B876" s="5">
-        <v>58</v>
+        <v>114</v>
       </c>
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A877" s="7">
-        <v>98154</v>
+        <v>98150</v>
       </c>
       <c r="B877" s="5">
-        <v>114</v>
+        <v>80</v>
       </c>
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A878" s="7">
-        <v>98155</v>
+        <v>98151</v>
       </c>
       <c r="B878" s="5">
-        <v>70</v>
+        <v>112</v>
       </c>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A879" s="7">
-        <v>98156</v>
+        <v>98153</v>
       </c>
       <c r="B879" s="5">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A880" s="7">
-        <v>98157</v>
+        <v>98154</v>
       </c>
       <c r="B880" s="5">
-        <v>38</v>
+        <v>114</v>
       </c>
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A881" s="7">
-        <v>98158</v>
+        <v>98155</v>
       </c>
       <c r="B881" s="5">
         <v>64</v>
@@ -7495,615 +7495,615 @@
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A882" s="7">
-        <v>98159</v>
+        <v>98156</v>
       </c>
       <c r="B882" s="5">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A883" s="7">
-        <v>98161</v>
+        <v>98157</v>
       </c>
       <c r="B883" s="5">
-        <v>120</v>
+        <v>38</v>
       </c>
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A884" s="7">
-        <v>98162</v>
+        <v>98158</v>
       </c>
       <c r="B884" s="5">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A885" s="7">
-        <v>98163</v>
+        <v>98159</v>
       </c>
       <c r="B885" s="5">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A886" s="7">
-        <v>98164</v>
+        <v>98161</v>
       </c>
       <c r="B886" s="5">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A887" s="7">
-        <v>98165</v>
+        <v>98162</v>
       </c>
       <c r="B887" s="5">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A888" s="7">
-        <v>98166</v>
+        <v>98163</v>
       </c>
       <c r="B888" s="5">
-        <v>128</v>
+        <v>76</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A889" s="7">
-        <v>98167</v>
+        <v>98164</v>
       </c>
       <c r="B889" s="5">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A890" s="7">
-        <v>98168</v>
+        <v>98165</v>
       </c>
       <c r="B890" s="5">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A891" s="7">
-        <v>98169</v>
+        <v>98166</v>
       </c>
       <c r="B891" s="5">
-        <v>54</v>
+        <v>128</v>
       </c>
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A892" s="7">
-        <v>98170</v>
+        <v>98167</v>
       </c>
       <c r="B892" s="5">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A893" s="7">
-        <v>98171</v>
+        <v>98168</v>
       </c>
       <c r="B893" s="5">
-        <v>96</v>
+        <v>56</v>
       </c>
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A894" s="7">
-        <v>98172</v>
+        <v>98169</v>
       </c>
       <c r="B894" s="5">
-        <v>140</v>
+        <v>54</v>
       </c>
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A895" s="7">
-        <v>98173</v>
+        <v>98170</v>
       </c>
       <c r="B895" s="5">
-        <v>116</v>
+        <v>50</v>
       </c>
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A896" s="7">
-        <v>98174</v>
+        <v>98171</v>
       </c>
       <c r="B896" s="5">
-        <v>76</v>
+        <v>96</v>
       </c>
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A897" s="7">
-        <v>98175</v>
+        <v>98172</v>
       </c>
       <c r="B897" s="5">
-        <v>60</v>
+        <v>160</v>
       </c>
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A898" s="7">
-        <v>98176</v>
+        <v>98173</v>
       </c>
       <c r="B898" s="5">
-        <v>34</v>
+        <v>116</v>
       </c>
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A899" s="7">
-        <v>98177</v>
+        <v>98174</v>
       </c>
       <c r="B899" s="5">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A900" s="7">
-        <v>98178</v>
+        <v>98175</v>
       </c>
       <c r="B900" s="5">
-        <v>102</v>
+        <v>60</v>
       </c>
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A901" s="7">
-        <v>98179</v>
+        <v>98176</v>
       </c>
       <c r="B901" s="5">
-        <v>90</v>
+        <v>34</v>
       </c>
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A902" s="7">
-        <v>98180</v>
+        <v>98177</v>
       </c>
       <c r="B902" s="5">
-        <v>12</v>
+        <v>56</v>
       </c>
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A903" s="7">
-        <v>98256</v>
+        <v>98178</v>
       </c>
       <c r="B903" s="5">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A904" s="7">
-        <v>98257</v>
+        <v>98179</v>
       </c>
       <c r="B904" s="5">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A905" s="7">
-        <v>98258</v>
+        <v>98180</v>
       </c>
       <c r="B905" s="5">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A906" s="7">
-        <v>98259</v>
+        <v>98256</v>
       </c>
       <c r="B906" s="5">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A907" s="7">
-        <v>98260</v>
+        <v>98257</v>
       </c>
       <c r="B907" s="5">
-        <v>134</v>
+        <v>96</v>
       </c>
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A908" s="7">
-        <v>98261</v>
+        <v>98258</v>
       </c>
       <c r="B908" s="5">
-        <v>124</v>
+        <v>98</v>
       </c>
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A909" s="7">
-        <v>98262</v>
+        <v>98259</v>
       </c>
       <c r="B909" s="5">
-        <v>74</v>
+        <v>102</v>
       </c>
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A910" s="7">
-        <v>98263</v>
+        <v>98260</v>
       </c>
       <c r="B910" s="5">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A911" s="7">
-        <v>98264</v>
+        <v>98261</v>
       </c>
       <c r="B911" s="5">
-        <v>162</v>
+        <v>124</v>
       </c>
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A912" s="7">
-        <v>98265</v>
+        <v>98262</v>
       </c>
       <c r="B912" s="5">
-        <v>102</v>
+        <v>74</v>
       </c>
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A913" s="7">
-        <v>98266</v>
+        <v>98263</v>
       </c>
       <c r="B913" s="5">
-        <v>64</v>
+        <v>138</v>
       </c>
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A914" s="7">
-        <v>98267</v>
+        <v>98264</v>
       </c>
       <c r="B914" s="5">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A915" s="7">
-        <v>98268</v>
+        <v>98265</v>
       </c>
       <c r="B915" s="5">
-        <v>148</v>
+        <v>100</v>
       </c>
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A916" s="7">
-        <v>98269</v>
+        <v>98266</v>
       </c>
       <c r="B916" s="5">
-        <v>110</v>
+        <v>64</v>
       </c>
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A917" s="7">
-        <v>98270</v>
+        <v>98267</v>
       </c>
       <c r="B917" s="5">
-        <v>162</v>
+        <v>130</v>
       </c>
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A918" s="7">
-        <v>98271</v>
+        <v>98268</v>
       </c>
       <c r="B918" s="5">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A919" s="7">
-        <v>98545</v>
+        <v>98269</v>
       </c>
       <c r="B919" s="5">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A920" s="7">
-        <v>98546</v>
+        <v>98270</v>
       </c>
       <c r="B920" s="5">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A921" s="7">
-        <v>98547</v>
+        <v>98271</v>
       </c>
       <c r="B921" s="5">
-        <v>116</v>
+        <v>142</v>
       </c>
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A922" s="7">
-        <v>98548</v>
+        <v>98545</v>
       </c>
       <c r="B922" s="5">
-        <v>113</v>
+        <v>144</v>
       </c>
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A923" s="7">
-        <v>98549</v>
+        <v>98546</v>
       </c>
       <c r="B923" s="5">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A924" s="7">
-        <v>98550</v>
+        <v>98547</v>
       </c>
       <c r="B924" s="5">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A925" s="7">
-        <v>98551</v>
+        <v>98548</v>
       </c>
       <c r="B925" s="5">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A926" s="7">
-        <v>98552</v>
+        <v>98549</v>
       </c>
       <c r="B926" s="5">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A927" s="7">
-        <v>98553</v>
+        <v>98550</v>
       </c>
       <c r="B927" s="5">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A928" s="7">
-        <v>98554</v>
+        <v>98551</v>
       </c>
       <c r="B928" s="5">
-        <v>96</v>
+        <v>122</v>
       </c>
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A929" s="7">
-        <v>98555</v>
+        <v>98552</v>
       </c>
       <c r="B929" s="5">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A930" s="7">
-        <v>98556</v>
+        <v>98553</v>
       </c>
       <c r="B930" s="5">
-        <v>166</v>
+        <v>130</v>
       </c>
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A931" s="7">
-        <v>98557</v>
+        <v>98554</v>
       </c>
       <c r="B931" s="5">
-        <v>134</v>
+        <v>96</v>
       </c>
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A932" s="7">
-        <v>98558</v>
+        <v>98555</v>
       </c>
       <c r="B932" s="5">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A933" s="7">
-        <v>98559</v>
+        <v>98556</v>
       </c>
       <c r="B933" s="5">
-        <v>108</v>
+        <v>166</v>
       </c>
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A934" s="7">
-        <v>98560</v>
+        <v>98557</v>
       </c>
       <c r="B934" s="5">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A935" s="7">
-        <v>98561</v>
+        <v>98558</v>
       </c>
       <c r="B935" s="5">
-        <v>136</v>
+        <v>90</v>
       </c>
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A936" s="7">
-        <v>98562</v>
+        <v>98559</v>
       </c>
       <c r="B936" s="5">
-        <v>174</v>
+        <v>108</v>
       </c>
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A937" s="7">
-        <v>98563</v>
+        <v>98560</v>
       </c>
       <c r="B937" s="5">
-        <v>128</v>
+        <v>148</v>
       </c>
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A938" s="7">
-        <v>98564</v>
+        <v>98561</v>
       </c>
       <c r="B938" s="5">
-        <v>108</v>
+        <v>136</v>
       </c>
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A939" s="7">
-        <v>98565</v>
+        <v>98562</v>
       </c>
       <c r="B939" s="5">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A940" s="7">
-        <v>98566</v>
+        <v>98563</v>
       </c>
       <c r="B940" s="5">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A941" s="7">
-        <v>98567</v>
+        <v>98564</v>
       </c>
       <c r="B941" s="5">
-        <v>156</v>
+        <v>108</v>
       </c>
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A942" s="7">
-        <v>98568</v>
+        <v>98565</v>
       </c>
       <c r="B942" s="5">
-        <v>146</v>
+        <v>94</v>
       </c>
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A943" s="7">
-        <v>98569</v>
+        <v>98566</v>
       </c>
       <c r="B943" s="5">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A944" s="7">
-        <v>98570</v>
+        <v>98567</v>
       </c>
       <c r="B944" s="5">
-        <v>100</v>
+        <v>152</v>
       </c>
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A945" s="7">
-        <v>98571</v>
+        <v>98568</v>
       </c>
       <c r="B945" s="5">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A946" s="7">
-        <v>98572</v>
+        <v>98569</v>
       </c>
       <c r="B946" s="5">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A947" s="7">
-        <v>98573</v>
+        <v>98570</v>
       </c>
       <c r="B947" s="5">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A948" s="7">
-        <v>98574</v>
+        <v>98571</v>
       </c>
       <c r="B948" s="5">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A949" s="7">
-        <v>98575</v>
+        <v>98572</v>
       </c>
       <c r="B949" s="5">
-        <v>782</v>
+        <v>146</v>
       </c>
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A950" s="7">
-        <v>98576</v>
+        <v>98573</v>
       </c>
       <c r="B950" s="5">
-        <v>88</v>
+        <v>150</v>
       </c>
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A951" s="7">
-        <v>98577</v>
+        <v>98574</v>
       </c>
       <c r="B951" s="5">
-        <v>107</v>
+        <v>130</v>
       </c>
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A952" s="7">
-        <v>98578</v>
+        <v>98575</v>
       </c>
       <c r="B952" s="5">
-        <v>38</v>
+        <v>782</v>
       </c>
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A953" s="7">
-        <v>98579</v>
+        <v>98576</v>
       </c>
       <c r="B953" s="5">
-        <v>122</v>
+        <v>88</v>
       </c>
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A954" s="7">
-        <v>98580</v>
+        <v>98577</v>
       </c>
       <c r="B954" s="5">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A955" s="7">
-        <v>98593</v>
+        <v>98578</v>
       </c>
       <c r="B955" s="5">
-        <v>158</v>
+        <v>38</v>
       </c>
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A956" s="7">
-        <v>98594</v>
+        <v>98579</v>
       </c>
       <c r="B956" s="5">
-        <v>160</v>
+        <v>122</v>
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A957" s="7">
-        <v>98595</v>
+        <v>98580</v>
       </c>
       <c r="B957" s="5">
-        <v>158</v>
+        <v>124</v>
       </c>
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A958" s="7">
-        <v>98596</v>
+        <v>98593</v>
       </c>
       <c r="B958" s="5">
         <v>158</v>
@@ -8111,25 +8111,49 @@
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A959" s="7">
-        <v>98597</v>
+        <v>98594</v>
       </c>
       <c r="B959" s="5">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A960" s="7">
-        <v>98598</v>
+        <v>98595</v>
       </c>
       <c r="B960" s="5">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A961" s="7">
+        <v>98596</v>
+      </c>
+      <c r="B961" s="5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A962" s="7">
+        <v>98597</v>
+      </c>
+      <c r="B962" s="5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A963" s="7">
+        <v>98598</v>
+      </c>
+      <c r="B963" s="5">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A964" s="7">
         <v>98599</v>
       </c>
-      <c r="B961" s="5">
+      <c r="B964" s="5">
         <v>164</v>
       </c>
     </row>
